--- a/EL MIRADOR/Agosto/Agosto - EL MIRADOR .xlsx
+++ b/EL MIRADOR/Agosto/Agosto - EL MIRADOR .xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\EL MIRADOR\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\EL MIRADOR\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F3FABA-1190-43E9-8AFB-0F7AB8B8D2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5824A098-76BF-42A8-A1BB-17DA230A72A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -858,12 +858,6 @@
 </t>
   </si>
   <si>
-    <t>PERÍODO: JULIO</t>
-  </si>
-  <si>
-    <t>ADS - Abono de mantenimiento ascensores JULIO del 2025</t>
-  </si>
-  <si>
     <t>COCHERA 33</t>
   </si>
   <si>
@@ -921,12 +915,6 @@
     <t>Loschi - Provision bomba electrica para carga de combustible</t>
   </si>
   <si>
-    <t>Articulos de limpieza - Mes de Junio</t>
-  </si>
-  <si>
-    <t>Articulos de limpieza - Mes de Julio</t>
-  </si>
-  <si>
     <t>Metrogas - Cliente nro. 40000496339</t>
   </si>
   <si>
@@ -996,9 +984,6 @@
     <t>Transf 05/07</t>
   </si>
   <si>
-    <t>VTO 14/08</t>
-  </si>
-  <si>
     <t>TOTAL A ABONAR 2DO VTO - DESDE EL</t>
   </si>
   <si>
@@ -1054,6 +1039,21 @@
   </si>
   <si>
     <t xml:space="preserve"> Laura Quintas Perez</t>
+  </si>
+  <si>
+    <t>VTO 15/09</t>
+  </si>
+  <si>
+    <t>PERÍODO: AGOSTO</t>
+  </si>
+  <si>
+    <t>ADS - Abono de mantenimiento ascensores AGOSTO del 2025</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza - Mes de AGOSTO</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza - Mes de JULIO</t>
   </si>
 </sst>
 </file>
@@ -1061,14 +1061,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -1645,8 +1645,8 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="210">
@@ -1658,7 +1658,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1666,95 +1666,95 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1763,19 +1763,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1784,8 +1784,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1799,12 +1799,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="8" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="8" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1815,7 +1815,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1827,13 +1827,13 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1843,22 +1843,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="11" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1867,9 +1867,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1905,14 +1905,26 @@
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1920,10 +1932,10 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1946,18 +1958,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2386,23 +2386,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R155"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="129"/>
       <c r="B1" s="139"/>
       <c r="C1" s="150" t="s">
@@ -2416,7 +2416,7 @@
       <c r="I1" s="127"/>
       <c r="J1" s="128"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="130"/>
       <c r="B2" s="140"/>
       <c r="C2" s="140" t="s">
@@ -2430,7 +2430,7 @@
       <c r="I2" s="141"/>
       <c r="J2" s="126"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="130"/>
       <c r="B3" s="140"/>
       <c r="C3" s="140" t="s">
@@ -2446,7 +2446,7 @@
       <c r="I3" s="141"/>
       <c r="J3" s="126"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="130"/>
       <c r="B4" s="140"/>
       <c r="C4" s="140" t="s">
@@ -2460,11 +2460,11 @@
       <c r="I4" s="141"/>
       <c r="J4" s="126"/>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="135"/>
       <c r="B5" s="140"/>
       <c r="C5" s="140" t="s">
-        <v>276</v>
+        <v>338</v>
       </c>
       <c r="D5" s="140"/>
       <c r="E5" s="140" t="s">
@@ -2476,7 +2476,7 @@
       <c r="I5" s="140"/>
       <c r="J5" s="136"/>
     </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="135"/>
       <c r="B6" s="140"/>
       <c r="C6" s="140" t="s">
@@ -2490,7 +2490,7 @@
       <c r="I6" s="140"/>
       <c r="J6" s="136"/>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="137"/>
       <c r="B7" s="138"/>
       <c r="C7" s="138"/>
@@ -2502,11 +2502,11 @@
       <c r="I7" s="138"/>
       <c r="J7" s="142"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="180" t="s">
         <v>269</v>
       </c>
@@ -2520,7 +2520,7 @@
       <c r="I14" s="180"/>
       <c r="J14" s="180"/>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="180"/>
       <c r="B15" s="180"/>
       <c r="C15" s="180"/>
@@ -2532,7 +2532,7 @@
       <c r="I15" s="180"/>
       <c r="J15" s="180"/>
     </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="180"/>
       <c r="B16" s="180"/>
       <c r="C16" s="180"/>
@@ -2544,7 +2544,7 @@
       <c r="I16" s="180"/>
       <c r="J16" s="180"/>
     </row>
-    <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="180"/>
       <c r="B17" s="180"/>
       <c r="C17" s="180"/>
@@ -2556,7 +2556,7 @@
       <c r="I17" s="180"/>
       <c r="J17" s="180"/>
     </row>
-    <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="180"/>
       <c r="B18" s="180"/>
       <c r="C18" s="180"/>
@@ -2568,13 +2568,13 @@
       <c r="I18" s="180"/>
       <c r="J18" s="180"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="H19" s="111"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="190" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="B20" s="190"/>
       <c r="C20" s="190"/>
@@ -2586,7 +2586,7 @@
       <c r="I20" s="190"/>
       <c r="J20" s="190"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="190"/>
       <c r="B21" s="190"/>
       <c r="C21" s="190"/>
@@ -2598,7 +2598,7 @@
       <c r="I21" s="190"/>
       <c r="J21" s="190"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="190"/>
       <c r="B22" s="190"/>
       <c r="C22" s="190"/>
@@ -2610,10 +2610,10 @@
       <c r="I22" s="190"/>
       <c r="J22" s="190"/>
     </row>
-    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="111"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
         <v>20</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="51" t="s">
         <v>241</v>
       </c>
@@ -2653,7 +2653,7 @@
       <c r="I25" s="112"/>
       <c r="J25" s="112"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>46</v>
       </c>
@@ -2669,7 +2669,7 @@
       <c r="I26" s="63"/>
       <c r="J26" s="63"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>244</v>
       </c>
@@ -2685,7 +2685,7 @@
       <c r="I27" s="63"/>
       <c r="J27" s="63"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>242</v>
       </c>
@@ -2701,7 +2701,7 @@
       <c r="I28" s="63"/>
       <c r="J28" s="63"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>243</v>
       </c>
@@ -2717,7 +2717,7 @@
       <c r="I29" s="63"/>
       <c r="J29" s="63"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>245</v>
       </c>
@@ -2733,7 +2733,7 @@
       <c r="I30" s="63"/>
       <c r="J30" s="63"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="110" t="s">
         <v>172</v>
       </c>
@@ -2750,7 +2750,7 @@
       <c r="I31" s="109"/>
       <c r="J31" s="109"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="51" t="s">
         <v>240</v>
       </c>
@@ -2764,7 +2764,7 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>46</v>
       </c>
@@ -2780,7 +2780,7 @@
       <c r="I33" s="63"/>
       <c r="J33" s="63"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>244</v>
       </c>
@@ -2796,7 +2796,7 @@
       <c r="I34" s="63"/>
       <c r="J34" s="63"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>242</v>
       </c>
@@ -2812,7 +2812,7 @@
       <c r="I35" s="63"/>
       <c r="J35" s="63"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>243</v>
       </c>
@@ -2828,7 +2828,7 @@
       <c r="I36" s="63"/>
       <c r="J36" s="63"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>245</v>
       </c>
@@ -2844,7 +2844,7 @@
       <c r="I37" s="63"/>
       <c r="J37" s="63"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="110" t="s">
         <v>172</v>
       </c>
@@ -2861,7 +2861,7 @@
       <c r="I38" s="109"/>
       <c r="J38" s="109"/>
     </row>
-    <row r="39" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="34" t="s">
         <v>1</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33" t="s">
         <v>35</v>
       </c>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="L40" s="74"/>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="L41" s="74"/>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -2961,7 +2961,7 @@
       <c r="J42" s="6"/>
       <c r="L42" s="74"/>
     </row>
-    <row r="43" spans="1:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -2974,7 +2974,7 @@
       <c r="J43" s="6"/>
       <c r="L43" s="74"/>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="34" t="s">
         <v>41</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="33" t="s">
         <v>256</v>
       </c>
@@ -3026,13 +3026,13 @@
       </c>
       <c r="L45" s="74"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>257</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D46" s="96">
         <v>37011.99</v>
@@ -3048,13 +3048,13 @@
       <c r="J46" s="63"/>
       <c r="L46" s="74"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>257</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D47" s="96">
         <v>65006.06</v>
@@ -3070,13 +3070,13 @@
       <c r="J47" s="63"/>
       <c r="L47" s="74"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>257</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D48" s="96">
         <v>26019.040000000001</v>
@@ -3092,13 +3092,13 @@
       <c r="J48" s="63"/>
       <c r="L48" s="74"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>257</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D49" s="96">
         <v>23000</v>
@@ -3114,13 +3114,13 @@
       <c r="J49" s="63"/>
       <c r="L49" s="74"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>257</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D50" s="96">
         <v>27002.95</v>
@@ -3136,7 +3136,7 @@
       <c r="J50" s="63"/>
       <c r="L50" s="74"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="33"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="L51" s="74"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="34" t="s">
         <v>36</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="33" t="s">
         <v>250</v>
       </c>
@@ -3198,7 +3198,7 @@
       <c r="J53" s="50"/>
       <c r="L53" s="74"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="36" t="s">
         <v>253</v>
       </c>
@@ -3213,13 +3213,13 @@
       <c r="J54" s="50"/>
       <c r="L54" s="74"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="36" t="s">
         <v>255</v>
       </c>
       <c r="B55" s="36"/>
       <c r="C55" s="36" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D55" s="96">
         <v>643422</v>
@@ -3232,13 +3232,13 @@
       <c r="J55" s="50"/>
       <c r="L55" s="74"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="36" t="s">
         <v>254</v>
       </c>
       <c r="B56" s="36"/>
       <c r="C56" s="36" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D56" s="96">
         <v>643422</v>
@@ -3251,7 +3251,7 @@
       <c r="J56" s="50"/>
       <c r="L56" s="74"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="34" t="s">
         <v>252</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="33" t="s">
         <v>2</v>
       </c>
@@ -3309,13 +3309,13 @@
       <c r="J58" s="6"/>
       <c r="L58" s="74"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>246</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D59" s="45">
         <v>49257.04</v>
@@ -3328,13 +3328,13 @@
       <c r="J59" s="6"/>
       <c r="L59" s="74"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="D60" s="45">
         <v>56422.63</v>
@@ -3347,7 +3347,7 @@
       <c r="J60" s="6"/>
       <c r="L60" s="74"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="34" t="s">
         <v>251</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="33" t="s">
         <v>233</v>
       </c>
@@ -3405,13 +3405,13 @@
       <c r="J62" s="37"/>
       <c r="L62" s="74"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>237</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D63" s="45">
         <v>160913</v>
@@ -3446,13 +3446,13 @@
       </c>
       <c r="L63" s="74"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>238</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D64" s="45">
         <v>7907</v>
@@ -3487,13 +3487,13 @@
       </c>
       <c r="L64" s="74"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>239</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D65" s="45">
         <v>7907</v>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="L65" s="74"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="34" t="s">
         <v>3</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="33" t="s">
         <v>4</v>
       </c>
@@ -3586,13 +3586,13 @@
       <c r="J67" s="6"/>
       <c r="L67" s="74"/>
     </row>
-    <row r="68" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="79" t="s">
         <v>247</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D68" s="147">
         <v>161756.56</v>
@@ -3638,13 +3638,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>248</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D69" s="147">
         <v>1233986.03</v>
@@ -3690,13 +3690,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>249</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D70" s="45">
         <v>100525.5</v>
@@ -3727,13 +3727,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>277</v>
+        <v>339</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D71" s="45">
         <v>263223.14</v>
@@ -3758,9 +3758,9 @@
       <c r="M71" s="95"/>
       <c r="N71" s="95"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="36" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B72" s="36"/>
       <c r="C72" s="36"/>
@@ -3793,13 +3793,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="36" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B73" s="36"/>
       <c r="C73" s="36" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D73" s="45">
         <v>25666.87</v>
@@ -3845,13 +3845,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="36" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B74" s="36"/>
       <c r="C74" s="36" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D74" s="45">
         <v>32660.43</v>
@@ -3897,9 +3897,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="79" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B75" s="132"/>
       <c r="C75" s="132"/>
@@ -3932,9 +3932,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="173" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B76" s="173"/>
       <c r="C76" s="174"/>
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="79"/>
       <c r="B77" s="80"/>
       <c r="C77" s="80"/>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="34" t="s">
         <v>5</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -4045,7 +4045,7 @@
       <c r="J79" s="6"/>
       <c r="L79" s="74"/>
     </row>
-    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -4058,7 +4058,7 @@
       <c r="J80" s="6"/>
       <c r="L80" s="74"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="33" t="s">
         <v>234</v>
       </c>
@@ -4073,9 +4073,9 @@
       <c r="J81" s="6"/>
       <c r="L81" s="74"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="B82" s="36"/>
       <c r="C82" s="6"/>
@@ -4110,9 +4110,9 @@
       <c r="K82" s="82"/>
       <c r="L82" s="74"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>298</v>
+        <v>340</v>
       </c>
       <c r="B83" s="36"/>
       <c r="C83" s="6"/>
@@ -4146,9 +4146,9 @@
       <c r="K83" s="82"/>
       <c r="L83" s="74"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B84" s="36"/>
       <c r="C84" s="6"/>
@@ -4182,9 +4182,9 @@
       <c r="K84" s="82"/>
       <c r="L84" s="74"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B85" s="36"/>
       <c r="C85" s="6"/>
@@ -4218,9 +4218,9 @@
       <c r="K85" s="82"/>
       <c r="L85" s="74"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B86" s="36"/>
       <c r="C86" s="6"/>
@@ -4254,9 +4254,9 @@
       <c r="K86" s="82"/>
       <c r="L86" s="74"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B87" s="36"/>
       <c r="C87" s="6"/>
@@ -4275,7 +4275,7 @@
       <c r="K87" s="82"/>
       <c r="L87" s="74"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -4289,7 +4289,7 @@
       <c r="L88" s="74"/>
       <c r="M88" s="44"/>
     </row>
-    <row r="89" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="34" t="s">
         <v>235</v>
       </c>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="N89" s="44"/>
     </row>
-    <row r="90" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -4346,7 +4346,7 @@
       <c r="J90" s="6"/>
       <c r="L90" s="74"/>
     </row>
-    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -4359,7 +4359,7 @@
       <c r="J91" s="6"/>
       <c r="L91" s="74"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="33" t="s">
         <v>6</v>
       </c>
@@ -4374,7 +4374,7 @@
       <c r="J92" s="6"/>
       <c r="L92" s="74"/>
     </row>
-    <row r="93" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
         <v>7</v>
       </c>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="L93" s="74"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="33"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -4425,7 +4425,7 @@
       <c r="L94" s="74"/>
       <c r="N94" s="45"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -4439,7 +4439,7 @@
       <c r="L95" s="74"/>
       <c r="N95" s="44"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="34" t="s">
         <v>8</v>
       </c>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="N96" s="44"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C97" s="6"/>
       <c r="D97" s="45"/>
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L97" s="74"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C98" s="52"/>
       <c r="D98" s="45"/>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="L98" s="74"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="34" t="s">
         <v>236</v>
       </c>
@@ -4596,7 +4596,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="115"/>
       <c r="B100" s="115"/>
       <c r="C100" s="115"/>
@@ -4609,7 +4609,7 @@
       <c r="J100" s="115"/>
       <c r="L100" s="74"/>
     </row>
-    <row r="101" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="117" t="s">
         <v>47</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="120"/>
       <c r="B102" s="121"/>
       <c r="C102" s="121"/>
@@ -4665,7 +4665,7 @@
       <c r="K102" s="44"/>
       <c r="L102" s="74"/>
     </row>
-    <row r="103" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>31</v>
       </c>
@@ -4712,7 +4712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D104" s="98"/>
       <c r="E104" s="44"/>
       <c r="F104" s="44"/>
@@ -4720,7 +4720,7 @@
       <c r="H104" s="44"/>
       <c r="I104" s="44"/>
     </row>
-    <row r="105" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="69" t="s">
         <v>42</v>
       </c>
@@ -4732,9 +4732,9 @@
       <c r="H105" s="44"/>
       <c r="I105" s="44"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C106" s="149">
         <f>21780*2</f>
@@ -4746,9 +4746,9 @@
       <c r="H106" s="44"/>
       <c r="I106" s="44"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C107" s="149">
         <v>21780</v>
@@ -4759,9 +4759,9 @@
       <c r="H107" s="44"/>
       <c r="I107" s="44"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C108" s="149">
         <v>18000</v>
@@ -4772,9 +4772,9 @@
       <c r="H108" s="44"/>
       <c r="I108" s="44"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C109" s="149">
         <v>9000</v>
@@ -4785,9 +4785,9 @@
       <c r="H109" s="44"/>
       <c r="I109" s="44"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C110" s="149">
         <v>18000</v>
@@ -4798,9 +4798,9 @@
       <c r="H110" s="44"/>
       <c r="I110" s="44"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C111" s="149">
         <v>18000</v>
@@ -4811,9 +4811,9 @@
       <c r="H111" s="44"/>
       <c r="I111" s="44"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C112" s="149">
         <v>9000</v>
@@ -4824,9 +4824,9 @@
       <c r="H112" s="44"/>
       <c r="I112" s="44"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C113" s="149">
         <v>9000</v>
@@ -4837,9 +4837,9 @@
       <c r="H113" s="44"/>
       <c r="I113" s="44"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C114" s="149">
         <v>9000</v>
@@ -4850,9 +4850,9 @@
       <c r="H114" s="44"/>
       <c r="I114" s="44"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C115" s="149">
         <v>9000</v>
@@ -4863,7 +4863,7 @@
       <c r="H115" s="44"/>
       <c r="I115" s="44"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="C116" s="175"/>
       <c r="E116" s="44"/>
@@ -4872,7 +4872,7 @@
       <c r="H116" s="44"/>
       <c r="I116" s="44"/>
     </row>
-    <row r="117" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1"/>
       <c r="C117" s="175"/>
       <c r="E117" s="44"/>
@@ -4881,7 +4881,7 @@
       <c r="H117" s="44"/>
       <c r="I117" s="44"/>
     </row>
-    <row r="118" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="70" t="s">
         <v>18</v>
       </c>
@@ -4896,21 +4896,21 @@
       <c r="H118" s="44"/>
       <c r="I118" s="44"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E119" s="44"/>
       <c r="F119" s="44"/>
       <c r="G119" s="44"/>
       <c r="H119" s="44"/>
       <c r="I119" s="44"/>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E120" s="65"/>
       <c r="F120" s="65"/>
       <c r="G120" s="65"/>
       <c r="H120" s="65"/>
       <c r="I120" s="65"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="186" t="s">
         <v>37</v>
       </c>
@@ -4936,7 +4936,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="188"/>
       <c r="B122" s="189"/>
       <c r="C122" s="92"/>
@@ -4951,7 +4951,7 @@
       <c r="I122" s="73"/>
       <c r="J122" s="63"/>
     </row>
-    <row r="123" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="188"/>
       <c r="B123" s="189"/>
       <c r="C123" s="92"/>
@@ -4963,7 +4963,7 @@
       <c r="I123" s="73"/>
       <c r="J123" s="63"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="183" t="s">
         <v>18</v>
       </c>
@@ -4994,14 +4994,14 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E126" s="44"/>
       <c r="F126" s="44"/>
       <c r="G126" s="44"/>
       <c r="H126" s="44"/>
       <c r="I126" s="44"/>
     </row>
-    <row r="127" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="39" t="s">
         <v>32</v>
       </c>
@@ -5010,7 +5010,7 @@
         <v>9142586.040000001</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="41" t="s">
         <v>34</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>7642586.040000001</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D129" s="182"/>
       <c r="E129" s="182"/>
       <c r="F129" s="102"/>
@@ -5027,7 +5027,7 @@
       <c r="H129" s="102"/>
       <c r="I129" s="102"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="17" t="s">
         <v>21</v>
       </c>
@@ -5040,7 +5040,7 @@
       <c r="H130" s="102"/>
       <c r="I130" s="102"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="20" t="s">
         <v>22</v>
       </c>
@@ -5055,7 +5055,7 @@
       <c r="H131" s="102"/>
       <c r="I131" s="102"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="22" t="s">
         <v>23</v>
       </c>
@@ -5073,7 +5073,7 @@
       <c r="H132" s="102"/>
       <c r="I132" s="102"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="22" t="s">
         <v>39</v>
       </c>
@@ -5090,7 +5090,7 @@
       <c r="I133" s="102"/>
       <c r="K133" s="45"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="22" t="s">
         <v>38</v>
       </c>
@@ -5107,7 +5107,7 @@
       <c r="I134" s="102"/>
       <c r="K134" s="55"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="22" t="s">
         <v>33</v>
       </c>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="C135" s="23"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="22" t="s">
         <v>42</v>
       </c>
@@ -5127,12 +5127,12 @@
       </c>
       <c r="C136" s="23"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="22"/>
       <c r="B137" s="18"/>
       <c r="C137" s="23"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="20" t="s">
         <v>25</v>
       </c>
@@ -5142,12 +5142,12 @@
       </c>
       <c r="C138" s="78"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="23"/>
       <c r="C139" s="19"/>
       <c r="D139" s="26"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C140" s="19"/>
       <c r="D140" s="44"/>
       <c r="E140" s="95"/>
@@ -5156,7 +5156,7 @@
       <c r="H140" s="95"/>
       <c r="I140" s="95"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="17" t="s">
         <v>26</v>
       </c>
@@ -5172,7 +5172,7 @@
       <c r="I141" s="95"/>
       <c r="J141" s="95"/>
     </row>
-    <row r="142" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="20" t="s">
         <v>264</v>
       </c>
@@ -5185,7 +5185,7 @@
       <c r="H142" s="103"/>
       <c r="I142" s="103"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="20"/>
       <c r="B143" s="94"/>
       <c r="C143" s="25"/>
@@ -5195,7 +5195,7 @@
       <c r="H143" s="44"/>
       <c r="I143" s="44"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="37" t="s">
         <v>18</v>
       </c>
@@ -5205,18 +5205,18 @@
       </c>
       <c r="C144" s="25"/>
     </row>
-    <row r="145" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:18" x14ac:dyDescent="0.3">
       <c r="C145" s="26"/>
       <c r="D145" s="95"/>
     </row>
-    <row r="146" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B146" s="23"/>
       <c r="C146" s="19"/>
     </row>
-    <row r="148" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:18" x14ac:dyDescent="0.3">
       <c r="R148" s="10"/>
     </row>
-    <row r="151" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B151" s="181"/>
       <c r="C151" s="181"/>
       <c r="D151" s="181"/>
@@ -5226,7 +5226,7 @@
       <c r="H151" s="106"/>
       <c r="I151" s="106"/>
     </row>
-    <row r="152" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B152" s="181"/>
       <c r="C152" s="181"/>
       <c r="D152" s="181"/>
@@ -5236,7 +5236,7 @@
       <c r="H152" s="106"/>
       <c r="I152" s="106"/>
     </row>
-    <row r="153" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B153" s="181"/>
       <c r="C153" s="181"/>
       <c r="D153" s="181"/>
@@ -5246,7 +5246,7 @@
       <c r="H153" s="106"/>
       <c r="I153" s="106"/>
     </row>
-    <row r="154" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B154" s="181"/>
       <c r="C154" s="181"/>
       <c r="D154" s="181"/>
@@ -5256,7 +5256,7 @@
       <c r="H154" s="106"/>
       <c r="I154" s="106"/>
     </row>
-    <row r="155" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B155" s="181"/>
       <c r="C155" s="181"/>
       <c r="D155" s="181"/>
@@ -5286,27 +5286,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R148"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="43.5703125" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
+    <col min="4" max="4" width="43.5546875" customWidth="1"/>
+    <col min="5" max="5" width="39.6640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5322,15 +5322,15 @@
       <c r="K1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="196">
+      <c r="L1" s="200">
         <f>RESUMEN!D103-RESUMEN!D101</f>
         <v>7642586.040000001</v>
       </c>
-      <c r="M1" s="197"/>
+      <c r="M1" s="201"/>
       <c r="N1" s="76"/>
       <c r="O1" s="64"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -5351,10 +5351,10 @@
       <c r="N2" s="77"/>
       <c r="O2" s="64"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="str">
         <f>RESUMEN!C5</f>
-        <v>PERÍODO: JULIO</v>
+        <v>PERÍODO: AGOSTO</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -5371,7 +5371,7 @@
       <c r="N3" s="75"/>
       <c r="O3" s="16"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -5394,89 +5394,89 @@
         <v>-1240893.8416399993</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="192" t="s">
+    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="191" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="205" t="s">
+      <c r="B5" s="193" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="192" t="s">
+      <c r="C5" s="191" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="207" t="s">
+      <c r="D5" s="195" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="207" t="s">
-        <v>281</v>
-      </c>
-      <c r="F5" s="192" t="s">
+      <c r="E5" s="195" t="s">
+        <v>279</v>
+      </c>
+      <c r="F5" s="191" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="192" t="s">
+      <c r="G5" s="191" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="192" t="s">
+      <c r="H5" s="191" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="198" t="s">
+      <c r="I5" s="202" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="204" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="200" t="s">
+      <c r="K5" s="204" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="203" t="s">
+      <c r="L5" s="207" t="s">
         <v>43</v>
       </c>
-      <c r="M5" s="200" t="s">
-        <v>324</v>
-      </c>
-      <c r="N5" s="200" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="193"/>
-      <c r="B6" s="206"/>
-      <c r="C6" s="193"/>
-      <c r="D6" s="208"/>
-      <c r="E6" s="208"/>
-      <c r="F6" s="193"/>
-      <c r="G6" s="193"/>
-      <c r="H6" s="193"/>
-      <c r="I6" s="199"/>
-      <c r="J6" s="201"/>
-      <c r="K6" s="201"/>
-      <c r="L6" s="204"/>
-      <c r="M6" s="201"/>
-      <c r="N6" s="201"/>
-    </row>
-    <row r="7" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="193"/>
-      <c r="B7" s="206"/>
-      <c r="C7" s="193"/>
-      <c r="D7" s="208"/>
-      <c r="E7" s="208"/>
-      <c r="F7" s="193"/>
-      <c r="G7" s="193"/>
-      <c r="H7" s="193"/>
-      <c r="I7" s="199"/>
-      <c r="J7" s="201"/>
-      <c r="K7" s="202"/>
-      <c r="L7" s="204"/>
+      <c r="M5" s="204" t="s">
+        <v>319</v>
+      </c>
+      <c r="N5" s="204" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="192"/>
+      <c r="B6" s="194"/>
+      <c r="C6" s="192"/>
+      <c r="D6" s="196"/>
+      <c r="E6" s="196"/>
+      <c r="F6" s="192"/>
+      <c r="G6" s="192"/>
+      <c r="H6" s="192"/>
+      <c r="I6" s="203"/>
+      <c r="J6" s="205"/>
+      <c r="K6" s="205"/>
+      <c r="L6" s="208"/>
+      <c r="M6" s="205"/>
+      <c r="N6" s="205"/>
+    </row>
+    <row r="7" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="192"/>
+      <c r="B7" s="194"/>
+      <c r="C7" s="192"/>
+      <c r="D7" s="196"/>
+      <c r="E7" s="196"/>
+      <c r="F7" s="192"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="192"/>
+      <c r="I7" s="203"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="206"/>
+      <c r="L7" s="208"/>
       <c r="M7" s="153" t="str">
         <f>RESUMEN!A20</f>
-        <v>VTO 14/08</v>
+        <v>VTO 15/09</v>
       </c>
       <c r="N7" s="152" t="str">
         <f>RESUMEN!A20</f>
-        <v>VTO 14/08</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+        <v>VTO 15/09</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>122</v>
       </c>
@@ -5521,12 +5521,12 @@
         <v>86445.848309040011</v>
       </c>
       <c r="O8" s="133"/>
-      <c r="Q8" s="191" t="s">
+      <c r="Q8" s="197" t="s">
         <v>263</v>
       </c>
-      <c r="R8" s="191"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R8" s="197"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
@@ -5569,10 +5569,10 @@
         <v>102454.33873664</v>
       </c>
       <c r="O9" s="133"/>
-      <c r="Q9" s="191"/>
-      <c r="R9" s="191"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q9" s="197"/>
+      <c r="R9" s="197"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>122</v>
       </c>
@@ -5581,7 +5581,7 @@
         <v>118</v>
       </c>
       <c r="D10" s="62" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E10" s="62"/>
       <c r="F10" s="105">
@@ -5625,7 +5625,7 @@
         <v>82162.051487999997</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>122</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>97377.246207999997</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>122</v>
       </c>
@@ -5687,7 +5687,7 @@
         <v>120</v>
       </c>
       <c r="D12" s="169" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E12" s="169"/>
       <c r="F12" s="163">
@@ -5731,7 +5731,7 @@
         <v>92051.928055999975</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="62" t="s">
         <v>124</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>113353.200664</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="62" t="s">
         <v>125</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>132372.19406399998</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="62" t="s">
         <v>124</v>
       </c>
@@ -5896,7 +5896,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="62" t="s">
         <v>126</v>
       </c>
@@ -5944,7 +5944,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="62" t="s">
         <v>126</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="62" t="s">
         <v>126</v>
       </c>
@@ -6006,7 +6006,7 @@
         <v>186</v>
       </c>
       <c r="E18" s="172" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F18" s="104">
         <v>9.4999999999999998E-3</v>
@@ -6043,7 +6043,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="62" t="s">
         <v>124</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="62" t="s">
         <v>125</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>55</v>
       </c>
       <c r="D20" s="62" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E20" s="172"/>
       <c r="F20" s="104">
@@ -6142,7 +6142,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="62" t="s">
         <v>124</v>
       </c>
@@ -6190,7 +6190,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="62" t="s">
         <v>126</v>
       </c>
@@ -6241,7 +6241,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="62" t="s">
         <v>126</v>
       </c>
@@ -6292,7 +6292,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="62" t="s">
         <v>126</v>
       </c>
@@ -6343,7 +6343,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="62" t="s">
         <v>124</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="62" t="s">
         <v>125</v>
       </c>
@@ -6406,7 +6406,7 @@
         <v>265</v>
       </c>
       <c r="E26" s="172" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F26" s="104">
         <v>7.1999999999999998E-3</v>
@@ -6444,7 +6444,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="62" t="s">
         <v>124</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="62" t="s">
         <v>126</v>
       </c>
@@ -6546,7 +6546,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="62" t="s">
         <v>126</v>
       </c>
@@ -6597,7 +6597,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="62" t="s">
         <v>126</v>
       </c>
@@ -6648,7 +6648,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="62" t="s">
         <v>124</v>
       </c>
@@ -6699,7 +6699,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="62" t="s">
         <v>125</v>
       </c>
@@ -6750,7 +6750,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="62" t="s">
         <v>124</v>
       </c>
@@ -6798,7 +6798,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="62" t="s">
         <v>126</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>69</v>
       </c>
       <c r="D34" s="62" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E34" s="172"/>
       <c r="F34" s="104">
@@ -6849,7 +6849,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="62" t="s">
         <v>126</v>
       </c>
@@ -6900,7 +6900,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="62" t="s">
         <v>126</v>
       </c>
@@ -6909,7 +6909,7 @@
         <v>71</v>
       </c>
       <c r="D36" s="62" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E36" s="172"/>
       <c r="F36" s="104">
@@ -6951,7 +6951,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="62" t="s">
         <v>124</v>
       </c>
@@ -7002,7 +7002,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="62" t="s">
         <v>125</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>193</v>
       </c>
       <c r="E38" s="172" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F38" s="104">
         <v>7.1999999999999998E-3</v>
@@ -7054,7 +7054,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="62" t="s">
         <v>124</v>
       </c>
@@ -7104,13 +7104,13 @@
         <v>0.27000000000000007</v>
       </c>
       <c r="P39" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="Q39" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="62" t="s">
         <v>126</v>
       </c>
@@ -7164,7 +7164,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="62" t="s">
         <v>126</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="62" t="s">
         <v>126</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="62" t="s">
         <v>124</v>
       </c>
@@ -7316,7 +7316,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="62" t="s">
         <v>125</v>
       </c>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="62" t="s">
         <v>124</v>
       </c>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="62" t="s">
         <v>126</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="62" t="s">
         <v>126</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="62" t="s">
         <v>126</v>
       </c>
@@ -7569,7 +7569,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="62" t="s">
         <v>124</v>
       </c>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="Q49" s="64"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="62" t="s">
         <v>125</v>
       </c>
@@ -7633,7 +7633,7 @@
         <v>201</v>
       </c>
       <c r="E50" s="172" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F50" s="104">
         <v>7.1999999999999998E-3</v>
@@ -7673,7 +7673,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="62" t="s">
         <v>124</v>
       </c>
@@ -7724,7 +7724,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="62" t="s">
         <v>126</v>
       </c>
@@ -7772,7 +7772,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="62" t="s">
         <v>126</v>
       </c>
@@ -7826,7 +7826,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="62" t="s">
         <v>126</v>
       </c>
@@ -7874,10 +7874,10 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="P54" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="62" t="s">
         <v>124</v>
       </c>
@@ -7927,7 +7927,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="62" t="s">
         <v>125</v>
       </c>
@@ -7978,7 +7978,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="62" t="s">
         <v>124</v>
       </c>
@@ -8029,7 +8029,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="62" t="s">
         <v>126</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>207</v>
       </c>
       <c r="E58" s="172" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F58" s="104">
         <v>9.4000000000000004E-3</v>
@@ -8079,7 +8079,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="62" t="s">
         <v>126</v>
       </c>
@@ -8129,7 +8129,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="62" t="s">
         <v>126</v>
       </c>
@@ -8179,7 +8179,7 @@
         <v>0.48000000000000026</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="62" t="s">
         <v>124</v>
       </c>
@@ -8230,7 +8230,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="62" t="s">
         <v>125</v>
       </c>
@@ -8278,7 +8278,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="62" t="s">
         <v>124</v>
       </c>
@@ -8329,7 +8329,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="62" t="s">
         <v>126</v>
       </c>
@@ -8377,7 +8377,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="62" t="s">
         <v>126</v>
       </c>
@@ -8431,7 +8431,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="62" t="s">
         <v>126</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="62" t="s">
         <v>127</v>
       </c>
@@ -8532,7 +8532,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="62" t="s">
         <v>124</v>
       </c>
@@ -8583,7 +8583,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="62" t="s">
         <v>126</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="62" t="s">
         <v>126</v>
       </c>
@@ -8679,7 +8679,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="62" t="s">
         <v>126</v>
       </c>
@@ -8729,7 +8729,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="62" t="s">
         <v>127</v>
       </c>
@@ -8780,7 +8780,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="62" t="s">
         <v>124</v>
       </c>
@@ -8831,7 +8831,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="62" t="s">
         <v>126</v>
       </c>
@@ -8882,7 +8882,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="62" t="s">
         <v>126</v>
       </c>
@@ -8894,7 +8894,7 @@
         <v>222</v>
       </c>
       <c r="E75" s="172" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F75" s="104">
         <v>8.6999999999999994E-3</v>
@@ -8935,7 +8935,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="62" t="s">
         <v>126</v>
       </c>
@@ -8985,10 +8985,10 @@
         <v>0.64000000000000035</v>
       </c>
       <c r="P76" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="62" t="s">
         <v>127</v>
       </c>
@@ -9038,7 +9038,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="62" t="s">
         <v>124</v>
       </c>
@@ -9089,7 +9089,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="62" t="s">
         <v>126</v>
       </c>
@@ -9139,7 +9139,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="62" t="s">
         <v>126</v>
       </c>
@@ -9189,7 +9189,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="125" t="s">
         <v>126</v>
       </c>
@@ -9239,7 +9239,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="125"/>
       <c r="B82" s="36"/>
       <c r="C82" s="36" t="s">
@@ -9288,7 +9288,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="125"/>
       <c r="B83" s="36"/>
       <c r="C83" s="36" t="s">
@@ -9337,7 +9337,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="125"/>
       <c r="B84" s="36"/>
       <c r="C84" s="36" t="s">
@@ -9386,7 +9386,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="125"/>
       <c r="B85" s="36"/>
       <c r="C85" s="36" t="s">
@@ -9435,7 +9435,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="125"/>
       <c r="B86" s="36"/>
       <c r="C86" s="36" t="s">
@@ -9484,10 +9484,10 @@
         <v>0.74000000000000044</v>
       </c>
       <c r="P86" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="125"/>
       <c r="B87" s="36"/>
       <c r="C87" s="36" t="s">
@@ -9533,7 +9533,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="125"/>
       <c r="B88" s="36"/>
       <c r="C88" s="36" t="s">
@@ -9582,7 +9582,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="125"/>
       <c r="B89" s="36"/>
       <c r="C89" s="36" t="s">
@@ -9631,7 +9631,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="125"/>
       <c r="B90" s="36"/>
       <c r="C90" s="36" t="s">
@@ -9677,7 +9677,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="125"/>
       <c r="B91" s="36"/>
       <c r="C91" s="36" t="s">
@@ -9723,7 +9723,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="125"/>
       <c r="B92" s="36"/>
       <c r="C92" s="36" t="s">
@@ -9772,7 +9772,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="125"/>
       <c r="B93" s="36"/>
       <c r="C93" s="36" t="s">
@@ -9821,7 +9821,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" s="125"/>
       <c r="B94" s="36"/>
       <c r="C94" s="36" t="s">
@@ -9870,7 +9870,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="125"/>
       <c r="B95" s="36"/>
       <c r="C95" s="36" t="s">
@@ -9919,7 +9919,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="96" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="125"/>
       <c r="B96" s="36"/>
       <c r="C96" s="36" t="s">
@@ -9968,7 +9968,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="125"/>
       <c r="B97" s="36"/>
       <c r="C97" s="36" t="s">
@@ -10017,7 +10017,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="125"/>
       <c r="B98" s="36"/>
       <c r="C98" s="36" t="s">
@@ -10066,7 +10066,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="125"/>
       <c r="B99" s="36"/>
       <c r="C99" s="36" t="s">
@@ -10112,7 +10112,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="125"/>
       <c r="B100" s="36"/>
       <c r="C100" s="36" t="s">
@@ -10158,7 +10158,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="101" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="125"/>
       <c r="B101" s="36"/>
       <c r="C101" s="36" t="s">
@@ -10206,7 +10206,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="125"/>
       <c r="B102" s="36"/>
       <c r="C102" s="36" t="s">
@@ -10254,7 +10254,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="125"/>
       <c r="B103" s="36"/>
       <c r="C103" s="36" t="s">
@@ -10303,7 +10303,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="125"/>
       <c r="B104" s="36"/>
       <c r="C104" s="36" t="s">
@@ -10352,7 +10352,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="125"/>
       <c r="B105" s="36"/>
       <c r="C105" s="36" t="s">
@@ -10401,7 +10401,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="125"/>
       <c r="B106" s="36"/>
       <c r="C106" s="36" t="s">
@@ -10447,7 +10447,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="125"/>
       <c r="B107" s="36"/>
       <c r="C107" s="36" t="s">
@@ -10496,7 +10496,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" s="125"/>
       <c r="B108" s="36"/>
       <c r="C108" s="36" t="s">
@@ -10545,7 +10545,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="125"/>
       <c r="B109" s="36"/>
       <c r="C109" s="36" t="s">
@@ -10594,7 +10594,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="125"/>
       <c r="B110" s="36"/>
       <c r="C110" s="36" t="s">
@@ -10643,7 +10643,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="125"/>
       <c r="B111" s="36"/>
       <c r="C111" s="36" t="s">
@@ -10692,7 +10692,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="125"/>
       <c r="B112" s="36"/>
       <c r="C112" s="36" t="s">
@@ -10741,7 +10741,7 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="148"/>
       <c r="B113" s="36"/>
       <c r="C113" s="36" t="s">
@@ -10790,7 +10790,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="148"/>
       <c r="B114" s="36"/>
       <c r="C114" s="36" t="s">
@@ -10839,7 +10839,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="148"/>
       <c r="B115" s="36"/>
       <c r="C115" s="36" t="s">
@@ -10888,7 +10888,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="148"/>
       <c r="B116" s="36"/>
       <c r="C116" s="36" t="s">
@@ -10937,7 +10937,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" s="148"/>
       <c r="B117" s="36"/>
       <c r="C117" s="36" t="s">
@@ -10983,7 +10983,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="148"/>
       <c r="B118" s="36"/>
       <c r="C118" s="36" t="s">
@@ -11032,7 +11032,7 @@
         <v>1.0600000000000007</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="148"/>
       <c r="B119" s="36"/>
       <c r="C119" s="36" t="s">
@@ -11081,7 +11081,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="148"/>
       <c r="B120" s="36"/>
       <c r="C120" s="36" t="s">
@@ -11130,7 +11130,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" s="148"/>
       <c r="B121" s="36"/>
       <c r="C121" s="36" t="s">
@@ -11179,7 +11179,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" s="148"/>
       <c r="B122" s="36"/>
       <c r="C122" s="36" t="s">
@@ -11228,7 +11228,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" s="148"/>
       <c r="B123" s="36"/>
       <c r="C123" s="36" t="s">
@@ -11277,7 +11277,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="148" t="s">
         <v>27</v>
       </c>
@@ -11328,7 +11328,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" s="148" t="s">
         <v>27</v>
       </c>
@@ -11379,7 +11379,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" s="56" t="s">
         <v>27</v>
       </c>
@@ -11397,7 +11397,7 @@
       <c r="M126" s="5"/>
       <c r="N126" s="9"/>
     </row>
-    <row r="127" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="28"/>
       <c r="B127" s="28"/>
       <c r="C127" s="28"/>
@@ -11438,41 +11438,41 @@
       </c>
       <c r="P127" s="64"/>
     </row>
-    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K128" s="66">
         <f>K127-L1</f>
         <v>1240893.8416399993</v>
       </c>
     </row>
-    <row r="129" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C129" s="195"/>
-      <c r="D129" s="195"/>
-      <c r="E129" s="195"/>
-      <c r="F129" s="195"/>
-      <c r="G129" s="195"/>
-      <c r="H129" s="195"/>
-      <c r="I129" s="195"/>
-      <c r="J129" s="195"/>
-      <c r="K129" s="195"/>
-      <c r="L129" s="195"/>
-      <c r="M129" s="195"/>
-      <c r="N129" s="195"/>
-    </row>
-    <row r="130" spans="3:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C130" s="195"/>
-      <c r="D130" s="195"/>
-      <c r="E130" s="195"/>
-      <c r="F130" s="195"/>
-      <c r="G130" s="195"/>
-      <c r="H130" s="195"/>
-      <c r="I130" s="195"/>
-      <c r="J130" s="195"/>
-      <c r="K130" s="195"/>
-      <c r="L130" s="195"/>
-      <c r="M130" s="195"/>
-      <c r="N130" s="195"/>
-    </row>
-    <row r="131" spans="3:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C129" s="199"/>
+      <c r="D129" s="199"/>
+      <c r="E129" s="199"/>
+      <c r="F129" s="199"/>
+      <c r="G129" s="199"/>
+      <c r="H129" s="199"/>
+      <c r="I129" s="199"/>
+      <c r="J129" s="199"/>
+      <c r="K129" s="199"/>
+      <c r="L129" s="199"/>
+      <c r="M129" s="199"/>
+      <c r="N129" s="199"/>
+    </row>
+    <row r="130" spans="3:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C130" s="199"/>
+      <c r="D130" s="199"/>
+      <c r="E130" s="199"/>
+      <c r="F130" s="199"/>
+      <c r="G130" s="199"/>
+      <c r="H130" s="199"/>
+      <c r="I130" s="199"/>
+      <c r="J130" s="199"/>
+      <c r="K130" s="199"/>
+      <c r="L130" s="199"/>
+      <c r="M130" s="199"/>
+      <c r="N130" s="199"/>
+    </row>
+    <row r="131" spans="3:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C131" s="87"/>
       <c r="D131" s="87"/>
       <c r="E131" s="87"/>
@@ -11486,121 +11486,121 @@
       <c r="M131" s="87"/>
       <c r="N131" s="87"/>
     </row>
-    <row r="132" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C132" s="195" t="s">
+    <row r="132" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C132" s="199" t="s">
         <v>269</v>
       </c>
-      <c r="D132" s="195"/>
-      <c r="E132" s="195"/>
-      <c r="F132" s="195"/>
-      <c r="G132" s="195"/>
-      <c r="H132" s="195"/>
-      <c r="I132" s="195"/>
-      <c r="J132" s="195"/>
-      <c r="K132" s="195"/>
-      <c r="L132" s="195"/>
-      <c r="M132" s="195"/>
-      <c r="N132" s="195"/>
-    </row>
-    <row r="133" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C133" s="195"/>
-      <c r="D133" s="195"/>
-      <c r="E133" s="195"/>
-      <c r="F133" s="195"/>
-      <c r="G133" s="195"/>
-      <c r="H133" s="195"/>
-      <c r="I133" s="195"/>
-      <c r="J133" s="195"/>
-      <c r="K133" s="195"/>
-      <c r="L133" s="195"/>
-      <c r="M133" s="195"/>
-      <c r="N133" s="195"/>
-    </row>
-    <row r="134" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C134" s="195"/>
-      <c r="D134" s="195"/>
-      <c r="E134" s="195"/>
-      <c r="F134" s="195"/>
-      <c r="G134" s="195"/>
-      <c r="H134" s="195"/>
-      <c r="I134" s="195"/>
-      <c r="J134" s="195"/>
-      <c r="K134" s="195"/>
-      <c r="L134" s="195"/>
-      <c r="M134" s="195"/>
-      <c r="N134" s="195"/>
-    </row>
-    <row r="135" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C135" s="195"/>
-      <c r="D135" s="195"/>
-      <c r="E135" s="195"/>
-      <c r="F135" s="195"/>
-      <c r="G135" s="195"/>
-      <c r="H135" s="195"/>
-      <c r="I135" s="195"/>
-      <c r="J135" s="195"/>
-      <c r="K135" s="195"/>
-      <c r="L135" s="195"/>
-      <c r="M135" s="195"/>
-      <c r="N135" s="195"/>
-    </row>
-    <row r="136" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C136" s="195"/>
-      <c r="D136" s="195"/>
-      <c r="E136" s="195"/>
-      <c r="F136" s="195"/>
-      <c r="G136" s="195"/>
-      <c r="H136" s="195"/>
-      <c r="I136" s="195"/>
-      <c r="J136" s="195"/>
-      <c r="K136" s="195"/>
-      <c r="L136" s="195"/>
-      <c r="M136" s="195"/>
-      <c r="N136" s="195"/>
-    </row>
-    <row r="137" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C137" s="195"/>
-      <c r="D137" s="195"/>
-      <c r="E137" s="195"/>
-      <c r="F137" s="195"/>
-      <c r="G137" s="195"/>
-      <c r="H137" s="195"/>
-      <c r="I137" s="195"/>
-      <c r="J137" s="195"/>
-      <c r="K137" s="195"/>
-      <c r="L137" s="195"/>
-      <c r="M137" s="195"/>
-      <c r="N137" s="195"/>
-    </row>
-    <row r="138" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C138" s="195"/>
-      <c r="D138" s="195"/>
-      <c r="E138" s="195"/>
-      <c r="F138" s="195"/>
-      <c r="G138" s="195"/>
-      <c r="H138" s="195"/>
-      <c r="I138" s="195"/>
-      <c r="J138" s="195"/>
-      <c r="K138" s="195"/>
-      <c r="L138" s="195"/>
-      <c r="M138" s="195"/>
-      <c r="N138" s="195"/>
-    </row>
-    <row r="139" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C139" s="195"/>
-      <c r="D139" s="195"/>
-      <c r="E139" s="195"/>
-      <c r="F139" s="195"/>
-      <c r="G139" s="195"/>
-      <c r="H139" s="195"/>
-      <c r="I139" s="195"/>
-      <c r="J139" s="195"/>
-      <c r="K139" s="195"/>
-      <c r="L139" s="195"/>
-      <c r="M139" s="195"/>
-      <c r="N139" s="195"/>
-    </row>
-    <row r="140" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D132" s="199"/>
+      <c r="E132" s="199"/>
+      <c r="F132" s="199"/>
+      <c r="G132" s="199"/>
+      <c r="H132" s="199"/>
+      <c r="I132" s="199"/>
+      <c r="J132" s="199"/>
+      <c r="K132" s="199"/>
+      <c r="L132" s="199"/>
+      <c r="M132" s="199"/>
+      <c r="N132" s="199"/>
+    </row>
+    <row r="133" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C133" s="199"/>
+      <c r="D133" s="199"/>
+      <c r="E133" s="199"/>
+      <c r="F133" s="199"/>
+      <c r="G133" s="199"/>
+      <c r="H133" s="199"/>
+      <c r="I133" s="199"/>
+      <c r="J133" s="199"/>
+      <c r="K133" s="199"/>
+      <c r="L133" s="199"/>
+      <c r="M133" s="199"/>
+      <c r="N133" s="199"/>
+    </row>
+    <row r="134" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C134" s="199"/>
+      <c r="D134" s="199"/>
+      <c r="E134" s="199"/>
+      <c r="F134" s="199"/>
+      <c r="G134" s="199"/>
+      <c r="H134" s="199"/>
+      <c r="I134" s="199"/>
+      <c r="J134" s="199"/>
+      <c r="K134" s="199"/>
+      <c r="L134" s="199"/>
+      <c r="M134" s="199"/>
+      <c r="N134" s="199"/>
+    </row>
+    <row r="135" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C135" s="199"/>
+      <c r="D135" s="199"/>
+      <c r="E135" s="199"/>
+      <c r="F135" s="199"/>
+      <c r="G135" s="199"/>
+      <c r="H135" s="199"/>
+      <c r="I135" s="199"/>
+      <c r="J135" s="199"/>
+      <c r="K135" s="199"/>
+      <c r="L135" s="199"/>
+      <c r="M135" s="199"/>
+      <c r="N135" s="199"/>
+    </row>
+    <row r="136" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C136" s="199"/>
+      <c r="D136" s="199"/>
+      <c r="E136" s="199"/>
+      <c r="F136" s="199"/>
+      <c r="G136" s="199"/>
+      <c r="H136" s="199"/>
+      <c r="I136" s="199"/>
+      <c r="J136" s="199"/>
+      <c r="K136" s="199"/>
+      <c r="L136" s="199"/>
+      <c r="M136" s="199"/>
+      <c r="N136" s="199"/>
+    </row>
+    <row r="137" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C137" s="199"/>
+      <c r="D137" s="199"/>
+      <c r="E137" s="199"/>
+      <c r="F137" s="199"/>
+      <c r="G137" s="199"/>
+      <c r="H137" s="199"/>
+      <c r="I137" s="199"/>
+      <c r="J137" s="199"/>
+      <c r="K137" s="199"/>
+      <c r="L137" s="199"/>
+      <c r="M137" s="199"/>
+      <c r="N137" s="199"/>
+    </row>
+    <row r="138" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C138" s="199"/>
+      <c r="D138" s="199"/>
+      <c r="E138" s="199"/>
+      <c r="F138" s="199"/>
+      <c r="G138" s="199"/>
+      <c r="H138" s="199"/>
+      <c r="I138" s="199"/>
+      <c r="J138" s="199"/>
+      <c r="K138" s="199"/>
+      <c r="L138" s="199"/>
+      <c r="M138" s="199"/>
+      <c r="N138" s="199"/>
+    </row>
+    <row r="139" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C139" s="199"/>
+      <c r="D139" s="199"/>
+      <c r="E139" s="199"/>
+      <c r="F139" s="199"/>
+      <c r="G139" s="199"/>
+      <c r="H139" s="199"/>
+      <c r="I139" s="199"/>
+      <c r="J139" s="199"/>
+      <c r="K139" s="199"/>
+      <c r="L139" s="199"/>
+      <c r="M139" s="199"/>
+      <c r="N139" s="199"/>
+    </row>
+    <row r="140" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C140" s="87"/>
       <c r="D140" s="87"/>
       <c r="E140" s="87"/>
@@ -11614,7 +11614,7 @@
       <c r="M140" s="87"/>
       <c r="N140" s="87"/>
     </row>
-    <row r="141" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C141" s="87"/>
       <c r="D141" s="87"/>
       <c r="E141" s="87"/>
@@ -11628,118 +11628,112 @@
       <c r="M141" s="87"/>
       <c r="N141" s="87"/>
     </row>
-    <row r="142" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C142" s="194" t="s">
+    <row r="142" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C142" s="198" t="s">
         <v>268</v>
       </c>
-      <c r="D142" s="194"/>
-      <c r="E142" s="194"/>
-      <c r="F142" s="194"/>
-      <c r="G142" s="194"/>
-      <c r="H142" s="194"/>
-      <c r="I142" s="194"/>
-      <c r="J142" s="194"/>
-      <c r="K142" s="194"/>
-      <c r="L142" s="194"/>
-      <c r="M142" s="194"/>
-      <c r="N142" s="194"/>
-    </row>
-    <row r="143" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C143" s="194"/>
-      <c r="D143" s="194"/>
-      <c r="E143" s="194"/>
-      <c r="F143" s="194"/>
-      <c r="G143" s="194"/>
-      <c r="H143" s="194"/>
-      <c r="I143" s="194"/>
-      <c r="J143" s="194"/>
-      <c r="K143" s="194"/>
-      <c r="L143" s="194"/>
-      <c r="M143" s="194"/>
-      <c r="N143" s="194"/>
-    </row>
-    <row r="144" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C144" s="194"/>
-      <c r="D144" s="194"/>
-      <c r="E144" s="194"/>
-      <c r="F144" s="194"/>
-      <c r="G144" s="194"/>
-      <c r="H144" s="194"/>
-      <c r="I144" s="194"/>
-      <c r="J144" s="194"/>
-      <c r="K144" s="194"/>
-      <c r="L144" s="194"/>
-      <c r="M144" s="194"/>
-      <c r="N144" s="194"/>
+      <c r="D142" s="198"/>
+      <c r="E142" s="198"/>
+      <c r="F142" s="198"/>
+      <c r="G142" s="198"/>
+      <c r="H142" s="198"/>
+      <c r="I142" s="198"/>
+      <c r="J142" s="198"/>
+      <c r="K142" s="198"/>
+      <c r="L142" s="198"/>
+      <c r="M142" s="198"/>
+      <c r="N142" s="198"/>
+    </row>
+    <row r="143" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C143" s="198"/>
+      <c r="D143" s="198"/>
+      <c r="E143" s="198"/>
+      <c r="F143" s="198"/>
+      <c r="G143" s="198"/>
+      <c r="H143" s="198"/>
+      <c r="I143" s="198"/>
+      <c r="J143" s="198"/>
+      <c r="K143" s="198"/>
+      <c r="L143" s="198"/>
+      <c r="M143" s="198"/>
+      <c r="N143" s="198"/>
+    </row>
+    <row r="144" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C144" s="198"/>
+      <c r="D144" s="198"/>
+      <c r="E144" s="198"/>
+      <c r="F144" s="198"/>
+      <c r="G144" s="198"/>
+      <c r="H144" s="198"/>
+      <c r="I144" s="198"/>
+      <c r="J144" s="198"/>
+      <c r="K144" s="198"/>
+      <c r="L144" s="198"/>
+      <c r="M144" s="198"/>
+      <c r="N144" s="198"/>
       <c r="P144" s="95">
         <f>L1-K127</f>
         <v>-1240893.8416399993</v>
       </c>
     </row>
-    <row r="145" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C145" s="194"/>
-      <c r="D145" s="194"/>
-      <c r="E145" s="194"/>
-      <c r="F145" s="194"/>
-      <c r="G145" s="194"/>
-      <c r="H145" s="194"/>
-      <c r="I145" s="194"/>
-      <c r="J145" s="194"/>
-      <c r="K145" s="194"/>
-      <c r="L145" s="194"/>
-      <c r="M145" s="194"/>
-      <c r="N145" s="194"/>
-    </row>
-    <row r="146" spans="3:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C146" s="194"/>
-      <c r="D146" s="194"/>
-      <c r="E146" s="194"/>
-      <c r="F146" s="194"/>
-      <c r="G146" s="194"/>
-      <c r="H146" s="194"/>
-      <c r="I146" s="194"/>
-      <c r="J146" s="194"/>
-      <c r="K146" s="194"/>
-      <c r="L146" s="194"/>
-      <c r="M146" s="194"/>
-      <c r="N146" s="194"/>
-    </row>
-    <row r="147" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C147" s="194"/>
-      <c r="D147" s="194"/>
-      <c r="E147" s="194"/>
-      <c r="F147" s="194"/>
-      <c r="G147" s="194"/>
-      <c r="H147" s="194"/>
-      <c r="I147" s="194"/>
-      <c r="J147" s="194"/>
-      <c r="K147" s="194"/>
-      <c r="L147" s="194"/>
-      <c r="M147" s="194"/>
-      <c r="N147" s="194"/>
-    </row>
-    <row r="148" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C148" s="194"/>
-      <c r="D148" s="194"/>
-      <c r="E148" s="194"/>
-      <c r="F148" s="194"/>
-      <c r="G148" s="194"/>
-      <c r="H148" s="194"/>
-      <c r="I148" s="194"/>
-      <c r="J148" s="194"/>
-      <c r="K148" s="194"/>
-      <c r="L148" s="194"/>
-      <c r="M148" s="194"/>
-      <c r="N148" s="194"/>
+    <row r="145" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C145" s="198"/>
+      <c r="D145" s="198"/>
+      <c r="E145" s="198"/>
+      <c r="F145" s="198"/>
+      <c r="G145" s="198"/>
+      <c r="H145" s="198"/>
+      <c r="I145" s="198"/>
+      <c r="J145" s="198"/>
+      <c r="K145" s="198"/>
+      <c r="L145" s="198"/>
+      <c r="M145" s="198"/>
+      <c r="N145" s="198"/>
+    </row>
+    <row r="146" spans="3:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C146" s="198"/>
+      <c r="D146" s="198"/>
+      <c r="E146" s="198"/>
+      <c r="F146" s="198"/>
+      <c r="G146" s="198"/>
+      <c r="H146" s="198"/>
+      <c r="I146" s="198"/>
+      <c r="J146" s="198"/>
+      <c r="K146" s="198"/>
+      <c r="L146" s="198"/>
+      <c r="M146" s="198"/>
+      <c r="N146" s="198"/>
+    </row>
+    <row r="147" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C147" s="198"/>
+      <c r="D147" s="198"/>
+      <c r="E147" s="198"/>
+      <c r="F147" s="198"/>
+      <c r="G147" s="198"/>
+      <c r="H147" s="198"/>
+      <c r="I147" s="198"/>
+      <c r="J147" s="198"/>
+      <c r="K147" s="198"/>
+      <c r="L147" s="198"/>
+      <c r="M147" s="198"/>
+      <c r="N147" s="198"/>
+    </row>
+    <row r="148" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C148" s="198"/>
+      <c r="D148" s="198"/>
+      <c r="E148" s="198"/>
+      <c r="F148" s="198"/>
+      <c r="G148" s="198"/>
+      <c r="H148" s="198"/>
+      <c r="I148" s="198"/>
+      <c r="J148" s="198"/>
+      <c r="K148" s="198"/>
+      <c r="L148" s="198"/>
+      <c r="M148" s="198"/>
+      <c r="N148" s="198"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="E5:E7"/>
     <mergeCell ref="Q8:R9"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="C142:N148"/>
@@ -11753,6 +11747,12 @@
     <mergeCell ref="C132:N139"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="E5:E7"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11764,11 +11764,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
   <dimension ref="B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" s="179" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -11779,90 +11779,90 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A8B3D07-243A-48F3-942B-AB44D486DEC8}">
   <dimension ref="C4:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C4" s="209" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D4" s="209"/>
     </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C5" s="177">
         <v>52141.08</v>
       </c>
       <c r="D5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C6" s="177">
         <v>67140.100000000006</v>
       </c>
       <c r="D6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C7" s="177">
         <v>52121.11</v>
       </c>
       <c r="D7" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C8" s="177">
         <v>67885.119999999995</v>
       </c>
       <c r="D8" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C9" s="177">
         <v>67140.160000000003</v>
       </c>
       <c r="D9" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C10" s="177">
         <v>62141.17</v>
       </c>
       <c r="D10" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C11" s="177">
         <v>67855.179999999993</v>
       </c>
       <c r="D11" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C12" s="177">
         <v>62141.23</v>
       </c>
       <c r="D12" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C13" s="177">
         <v>67855.240000000005</v>
       </c>
       <c r="D13" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C14" s="177">
         <f>SUM(C5:C13)</f>
         <v>566420.39</v>

--- a/EL MIRADOR/Agosto/Agosto - EL MIRADOR .xlsx
+++ b/EL MIRADOR/Agosto/Agosto - EL MIRADOR .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\EL MIRADOR\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5824A098-76BF-42A8-A1BB-17DA230A72A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6997E415-DF74-4050-BBAE-F2C4507EF5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,14 +20,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$149</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$145</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$146</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="340">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -894,18 +894,6 @@
     <t>Efect 24/07</t>
   </si>
   <si>
-    <t>Efect 28/07</t>
-  </si>
-  <si>
-    <t>Efect 31/07</t>
-  </si>
-  <si>
-    <t>Mercado P. 09/07</t>
-  </si>
-  <si>
-    <t>Efect. 18/07</t>
-  </si>
-  <si>
     <t>Efect. 29/07</t>
   </si>
   <si>
@@ -975,9 +963,6 @@
     <t>Baez Veronica Anabella - Compra limpiadores de acero y pilas</t>
   </si>
   <si>
-    <t>Victor Martinez - Abono mantenimiento control de accesos - No llego factura</t>
-  </si>
-  <si>
     <t>No hay cuenta aun</t>
   </si>
   <si>
@@ -1023,9 +1008,6 @@
     <t>5F</t>
   </si>
   <si>
-    <t>Efect 26/07</t>
-  </si>
-  <si>
     <t>Monotributo Sra. Miriam</t>
   </si>
   <si>
@@ -1054,6 +1036,18 @@
   </si>
   <si>
     <t>Articulos de limpieza - Mes de JULIO</t>
+  </si>
+  <si>
+    <t>Victor Martinez - Abono mantenimiento control de accesos</t>
+  </si>
+  <si>
+    <t>Mes de Julio</t>
+  </si>
+  <si>
+    <t>Mes de Agosto</t>
+  </si>
+  <si>
+    <t>Mercado P. 05/08</t>
   </si>
 </sst>
 </file>
@@ -1649,7 +1643,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="210">
+  <cellXfs count="214">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1831,7 +1825,6 @@
     <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1905,26 +1898,14 @@
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1959,9 +1940,26 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2385,7 +2383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R155"/>
+  <dimension ref="A1:R156"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.44140625" customWidth="1"/>
@@ -2405,12 +2403,12 @@
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="129"/>
       <c r="B1" s="139"/>
-      <c r="C1" s="150" t="s">
+      <c r="C1" s="149" t="s">
         <v>275</v>
       </c>
-      <c r="D1" s="150"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="151"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
       <c r="G1" s="127"/>
       <c r="H1" s="127"/>
       <c r="I1" s="127"/>
@@ -2464,7 +2462,7 @@
       <c r="A5" s="135"/>
       <c r="B5" s="140"/>
       <c r="C5" s="140" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="D5" s="140"/>
       <c r="E5" s="140" t="s">
@@ -2507,108 +2505,108 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="180" t="s">
+      <c r="A14" s="179" t="s">
         <v>269</v>
       </c>
-      <c r="B14" s="180"/>
-      <c r="C14" s="180"/>
-      <c r="D14" s="180"/>
-      <c r="E14" s="180"/>
-      <c r="F14" s="180"/>
-      <c r="G14" s="180"/>
-      <c r="H14" s="180"/>
-      <c r="I14" s="180"/>
-      <c r="J14" s="180"/>
+      <c r="B14" s="179"/>
+      <c r="C14" s="179"/>
+      <c r="D14" s="179"/>
+      <c r="E14" s="179"/>
+      <c r="F14" s="179"/>
+      <c r="G14" s="179"/>
+      <c r="H14" s="179"/>
+      <c r="I14" s="179"/>
+      <c r="J14" s="179"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="180"/>
-      <c r="B15" s="180"/>
-      <c r="C15" s="180"/>
-      <c r="D15" s="180"/>
-      <c r="E15" s="180"/>
-      <c r="F15" s="180"/>
-      <c r="G15" s="180"/>
-      <c r="H15" s="180"/>
-      <c r="I15" s="180"/>
-      <c r="J15" s="180"/>
+      <c r="A15" s="179"/>
+      <c r="B15" s="179"/>
+      <c r="C15" s="179"/>
+      <c r="D15" s="179"/>
+      <c r="E15" s="179"/>
+      <c r="F15" s="179"/>
+      <c r="G15" s="179"/>
+      <c r="H15" s="179"/>
+      <c r="I15" s="179"/>
+      <c r="J15" s="179"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="180"/>
-      <c r="B16" s="180"/>
-      <c r="C16" s="180"/>
-      <c r="D16" s="180"/>
-      <c r="E16" s="180"/>
-      <c r="F16" s="180"/>
-      <c r="G16" s="180"/>
-      <c r="H16" s="180"/>
-      <c r="I16" s="180"/>
-      <c r="J16" s="180"/>
+      <c r="A16" s="179"/>
+      <c r="B16" s="179"/>
+      <c r="C16" s="179"/>
+      <c r="D16" s="179"/>
+      <c r="E16" s="179"/>
+      <c r="F16" s="179"/>
+      <c r="G16" s="179"/>
+      <c r="H16" s="179"/>
+      <c r="I16" s="179"/>
+      <c r="J16" s="179"/>
     </row>
     <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="180"/>
-      <c r="B17" s="180"/>
-      <c r="C17" s="180"/>
-      <c r="D17" s="180"/>
-      <c r="E17" s="180"/>
-      <c r="F17" s="180"/>
-      <c r="G17" s="180"/>
-      <c r="H17" s="180"/>
-      <c r="I17" s="180"/>
-      <c r="J17" s="180"/>
+      <c r="A17" s="179"/>
+      <c r="B17" s="179"/>
+      <c r="C17" s="179"/>
+      <c r="D17" s="179"/>
+      <c r="E17" s="179"/>
+      <c r="F17" s="179"/>
+      <c r="G17" s="179"/>
+      <c r="H17" s="179"/>
+      <c r="I17" s="179"/>
+      <c r="J17" s="179"/>
     </row>
     <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="180"/>
-      <c r="B18" s="180"/>
-      <c r="C18" s="180"/>
-      <c r="D18" s="180"/>
-      <c r="E18" s="180"/>
-      <c r="F18" s="180"/>
-      <c r="G18" s="180"/>
-      <c r="H18" s="180"/>
-      <c r="I18" s="180"/>
-      <c r="J18" s="180"/>
+      <c r="A18" s="179"/>
+      <c r="B18" s="179"/>
+      <c r="C18" s="179"/>
+      <c r="D18" s="179"/>
+      <c r="E18" s="179"/>
+      <c r="F18" s="179"/>
+      <c r="G18" s="179"/>
+      <c r="H18" s="179"/>
+      <c r="I18" s="179"/>
+      <c r="J18" s="179"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="H19" s="111"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="190" t="s">
-        <v>337</v>
-      </c>
-      <c r="B20" s="190"/>
-      <c r="C20" s="190"/>
-      <c r="D20" s="190"/>
-      <c r="E20" s="190"/>
-      <c r="F20" s="190"/>
-      <c r="G20" s="190"/>
-      <c r="H20" s="190"/>
-      <c r="I20" s="190"/>
-      <c r="J20" s="190"/>
+      <c r="A20" s="189" t="s">
+        <v>331</v>
+      </c>
+      <c r="B20" s="189"/>
+      <c r="C20" s="189"/>
+      <c r="D20" s="189"/>
+      <c r="E20" s="189"/>
+      <c r="F20" s="189"/>
+      <c r="G20" s="189"/>
+      <c r="H20" s="189"/>
+      <c r="I20" s="189"/>
+      <c r="J20" s="189"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="190"/>
-      <c r="B21" s="190"/>
-      <c r="C21" s="190"/>
-      <c r="D21" s="190"/>
-      <c r="E21" s="190"/>
-      <c r="F21" s="190"/>
-      <c r="G21" s="190"/>
-      <c r="H21" s="190"/>
-      <c r="I21" s="190"/>
-      <c r="J21" s="190"/>
+      <c r="A21" s="189"/>
+      <c r="B21" s="189"/>
+      <c r="C21" s="189"/>
+      <c r="D21" s="189"/>
+      <c r="E21" s="189"/>
+      <c r="F21" s="189"/>
+      <c r="G21" s="189"/>
+      <c r="H21" s="189"/>
+      <c r="I21" s="189"/>
+      <c r="J21" s="189"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="190"/>
-      <c r="B22" s="190"/>
-      <c r="C22" s="190"/>
-      <c r="D22" s="190"/>
-      <c r="E22" s="190"/>
-      <c r="F22" s="190"/>
-      <c r="G22" s="190"/>
-      <c r="H22" s="190"/>
-      <c r="I22" s="190"/>
-      <c r="J22" s="190"/>
+      <c r="A22" s="189"/>
+      <c r="B22" s="189"/>
+      <c r="C22" s="189"/>
+      <c r="D22" s="189"/>
+      <c r="E22" s="189"/>
+      <c r="F22" s="189"/>
+      <c r="G22" s="189"/>
+      <c r="H22" s="189"/>
+      <c r="I22" s="189"/>
+      <c r="J22" s="189"/>
     </row>
     <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="111"/>
@@ -3034,12 +3032,12 @@
       <c r="C46" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="D46" s="96">
-        <v>37011.99</v>
+      <c r="D46" s="210">
+        <v>30000.04</v>
       </c>
       <c r="E46" s="63">
         <f>D46</f>
-        <v>37011.99</v>
+        <v>30000.04</v>
       </c>
       <c r="F46" s="63"/>
       <c r="G46" s="63"/>
@@ -3056,12 +3054,12 @@
       <c r="C47" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="D47" s="96">
-        <v>65006.06</v>
+      <c r="D47" s="210">
+        <v>29003.98</v>
       </c>
       <c r="E47" s="63">
         <f t="shared" ref="E47:E50" si="1">D47</f>
-        <v>65006.06</v>
+        <v>29003.98</v>
       </c>
       <c r="F47" s="63"/>
       <c r="G47" s="63"/>
@@ -3075,15 +3073,11 @@
         <v>257</v>
       </c>
       <c r="B48" s="6"/>
-      <c r="C48" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="D48" s="96">
-        <v>26019.040000000001</v>
-      </c>
+      <c r="C48" s="6"/>
+      <c r="D48" s="96"/>
       <c r="E48" s="63">
         <f t="shared" si="1"/>
-        <v>26019.040000000001</v>
+        <v>0</v>
       </c>
       <c r="F48" s="63"/>
       <c r="G48" s="63"/>
@@ -3097,15 +3091,11 @@
         <v>257</v>
       </c>
       <c r="B49" s="6"/>
-      <c r="C49" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="D49" s="96">
-        <v>23000</v>
-      </c>
+      <c r="C49" s="6"/>
+      <c r="D49" s="96"/>
       <c r="E49" s="63">
         <f t="shared" si="1"/>
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="F49" s="63"/>
       <c r="G49" s="63"/>
@@ -3119,15 +3109,11 @@
         <v>257</v>
       </c>
       <c r="B50" s="6"/>
-      <c r="C50" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="D50" s="96">
-        <v>27002.95</v>
-      </c>
+      <c r="C50" s="6"/>
+      <c r="D50" s="96"/>
       <c r="E50" s="63">
         <f t="shared" si="1"/>
-        <v>27002.95</v>
+        <v>0</v>
       </c>
       <c r="F50" s="63"/>
       <c r="G50" s="63"/>
@@ -3163,11 +3149,11 @@
       <c r="C52" s="34"/>
       <c r="D52" s="43">
         <f>SUM(D41:D51)</f>
-        <v>178040.04</v>
+        <v>59004.020000000004</v>
       </c>
       <c r="E52" s="43">
         <f t="shared" ref="E52" si="4">SUM(E41:E51)</f>
-        <v>178040.04</v>
+        <v>59004.020000000004</v>
       </c>
       <c r="F52" s="43"/>
       <c r="G52" s="43"/>
@@ -3176,7 +3162,7 @@
       <c r="J52" s="49"/>
       <c r="K52" s="44">
         <f>E52+J52+F52+G52+H52+I52</f>
-        <v>178040.04</v>
+        <v>59004.020000000004</v>
       </c>
       <c r="L52" s="74" t="str">
         <f>IF(D52=K52, "", "Error")</f>
@@ -3204,7 +3190,9 @@
       </c>
       <c r="B54" s="36"/>
       <c r="C54" s="36"/>
-      <c r="D54" s="96"/>
+      <c r="D54" s="210">
+        <v>129575</v>
+      </c>
       <c r="E54" s="50"/>
       <c r="F54" s="50"/>
       <c r="G54" s="50"/>
@@ -3219,9 +3207,9 @@
       </c>
       <c r="B55" s="36"/>
       <c r="C55" s="36" t="s">
-        <v>300</v>
-      </c>
-      <c r="D55" s="96">
+        <v>296</v>
+      </c>
+      <c r="D55" s="210">
         <v>643422</v>
       </c>
       <c r="E55" s="50"/>
@@ -3238,9 +3226,9 @@
       </c>
       <c r="B56" s="36"/>
       <c r="C56" s="36" t="s">
-        <v>300</v>
-      </c>
-      <c r="D56" s="96">
+        <v>296</v>
+      </c>
+      <c r="D56" s="210">
         <v>643422</v>
       </c>
       <c r="E56" s="50"/>
@@ -3259,35 +3247,35 @@
       <c r="C57" s="34"/>
       <c r="D57" s="145">
         <f>SUM(D54:D56)</f>
-        <v>1286844</v>
+        <v>1416419</v>
       </c>
       <c r="E57" s="43">
         <f>D57*93.2%</f>
-        <v>1199338.608</v>
+        <v>1320102.5080000001</v>
       </c>
       <c r="F57" s="88">
         <f>$D57*1.08%</f>
-        <v>13897.915200000001</v>
+        <v>15297.325200000001</v>
       </c>
       <c r="G57" s="88">
         <f>$D57*1.28%</f>
-        <v>16471.603200000001</v>
+        <v>18130.163199999999</v>
       </c>
       <c r="H57" s="88">
         <f>$D57*1.21%</f>
-        <v>15570.812399999999</v>
+        <v>17138.669900000001</v>
       </c>
       <c r="I57" s="88">
         <f>$D57*1.49%</f>
-        <v>19173.975600000002</v>
+        <v>21104.643100000001</v>
       </c>
       <c r="J57" s="88">
         <f>D57*1.74%</f>
-        <v>22391.085599999999</v>
+        <v>24645.690599999998</v>
       </c>
       <c r="K57" s="44">
         <f>E57+J57+F57+G57+H57+I57</f>
-        <v>1286844</v>
+        <v>1416419.0000000005</v>
       </c>
       <c r="L57" s="74" t="str">
         <f>IF(D57=K57, "", "Error")</f>
@@ -3315,7 +3303,7 @@
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D59" s="45">
         <v>49257.04</v>
@@ -3330,11 +3318,11 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D60" s="45">
         <v>56422.63</v>
@@ -3411,9 +3399,9 @@
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="D63" s="45">
+        <v>339</v>
+      </c>
+      <c r="D63" s="209">
         <v>160913</v>
       </c>
       <c r="E63" s="63">
@@ -3452,9 +3440,9 @@
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="D64" s="45">
+        <v>339</v>
+      </c>
+      <c r="D64" s="209">
         <v>7907</v>
       </c>
       <c r="E64" s="63">
@@ -3493,9 +3481,9 @@
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="D65" s="45">
+        <v>339</v>
+      </c>
+      <c r="D65" s="209">
         <v>7907</v>
       </c>
       <c r="E65" s="63">
@@ -3592,9 +3580,9 @@
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="D68" s="147">
+        <v>288</v>
+      </c>
+      <c r="D68" s="213">
         <v>161756.56</v>
       </c>
       <c r="E68" s="73">
@@ -3644,42 +3632,42 @@
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="D69" s="147">
-        <v>1233986.03</v>
+        <v>339</v>
+      </c>
+      <c r="D69" s="212">
+        <v>1292639.07</v>
       </c>
       <c r="E69" s="73">
         <f>D69*93.2%</f>
-        <v>1150074.9799600001</v>
+        <v>1204739.6132400001</v>
       </c>
       <c r="F69" s="63">
         <f>$D69*1.08%</f>
-        <v>13327.049124000001</v>
+        <v>13960.501956000002</v>
       </c>
       <c r="G69" s="63">
         <f>$D69*1.28%</f>
-        <v>15795.021184000001</v>
+        <v>16545.780096000002</v>
       </c>
       <c r="H69" s="63">
         <f>$D69*1.21%</f>
-        <v>14931.230963</v>
+        <v>15640.932747000001</v>
       </c>
       <c r="I69" s="63">
         <f>$D69*1.49%</f>
-        <v>18386.391846999999</v>
+        <v>19260.322143000001</v>
       </c>
       <c r="J69" s="63">
         <f>D69*1.74%</f>
-        <v>21471.356921999999</v>
+        <v>22491.919817999998</v>
       </c>
       <c r="K69" s="44">
-        <f t="shared" ref="K69:K76" si="8">D69</f>
-        <v>1233986.03</v>
+        <f t="shared" ref="K69:K77" si="8">D69</f>
+        <v>1292639.07</v>
       </c>
       <c r="L69" s="83">
         <f>E69+J69+I69+H69+G69+F69</f>
-        <v>1233986.03</v>
+        <v>1292639.07</v>
       </c>
       <c r="M69" s="95">
         <f>L69-D69</f>
@@ -3696,7 +3684,7 @@
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D70" s="45">
         <v>100525.5</v>
@@ -3729,13 +3717,13 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="D71" s="45">
+        <v>312</v>
+      </c>
+      <c r="D71" s="209">
         <v>263223.14</v>
       </c>
       <c r="E71" s="73">
@@ -3760,16 +3748,18 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="36" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="B72" s="36"/>
-      <c r="C72" s="36"/>
-      <c r="D72" s="45">
-        <v>0</v>
+      <c r="C72" s="36" t="s">
+        <v>337</v>
+      </c>
+      <c r="D72" s="209">
+        <v>30000</v>
       </c>
       <c r="E72" s="73">
         <f>D72</f>
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="F72" s="63"/>
       <c r="G72" s="63"/>
@@ -3778,11 +3768,11 @@
       <c r="J72" s="63"/>
       <c r="K72" s="44">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="L72" s="83">
-        <f t="shared" ref="L72:L76" si="9">E72+J72+I72+H72+G72+F72</f>
-        <v>0</v>
+        <f t="shared" ref="L72:L77" si="9">E72+J72+I72+H72+G72+F72</f>
+        <v>30000</v>
       </c>
       <c r="M72" s="95">
         <f>L72-D72</f>
@@ -3795,98 +3785,68 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="36" t="s">
-        <v>295</v>
+        <v>336</v>
       </c>
       <c r="B73" s="36"/>
       <c r="C73" s="36" t="s">
-        <v>296</v>
-      </c>
-      <c r="D73" s="45">
-        <v>25666.87</v>
-      </c>
-      <c r="E73" s="73">
-        <f>D73*93.2%</f>
-        <v>23921.522840000001</v>
-      </c>
-      <c r="F73" s="63">
-        <f>$D73*1.08%</f>
-        <v>277.20219600000001</v>
-      </c>
-      <c r="G73" s="63">
-        <f>$D73*1.28%</f>
-        <v>328.53593599999999</v>
-      </c>
-      <c r="H73" s="63">
-        <f>$D73*1.21%</f>
-        <v>310.56912699999998</v>
-      </c>
-      <c r="I73" s="63">
-        <f>$D73*1.49%</f>
-        <v>382.43636299999997</v>
-      </c>
-      <c r="J73" s="63">
-        <f>D73*1.74%</f>
-        <v>446.60353799999996</v>
-      </c>
-      <c r="K73" s="44">
-        <f t="shared" si="8"/>
-        <v>25666.87</v>
-      </c>
-      <c r="L73" s="83">
-        <f t="shared" si="9"/>
-        <v>25666.87</v>
-      </c>
-      <c r="M73" s="95">
-        <f>L73-D73</f>
-        <v>0</v>
-      </c>
-      <c r="N73" s="95">
-        <f>K73-D73</f>
-        <v>0</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="D73" s="209">
+        <v>30000</v>
+      </c>
+      <c r="E73" s="73"/>
+      <c r="F73" s="63"/>
+      <c r="G73" s="63"/>
+      <c r="H73" s="63"/>
+      <c r="I73" s="63"/>
+      <c r="J73" s="63"/>
+      <c r="K73" s="44"/>
+      <c r="L73" s="83"/>
+      <c r="M73" s="95"/>
+      <c r="N73" s="95"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="36" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B74" s="36"/>
       <c r="C74" s="36" t="s">
-        <v>296</v>
-      </c>
-      <c r="D74" s="45">
-        <v>32660.43</v>
+        <v>292</v>
+      </c>
+      <c r="D74" s="211">
+        <v>4869.91</v>
       </c>
       <c r="E74" s="73">
         <f>D74*93.2%</f>
-        <v>30439.520760000003</v>
+        <v>4538.75612</v>
       </c>
       <c r="F74" s="63">
         <f>$D74*1.08%</f>
-        <v>352.73264399999999</v>
+        <v>52.595027999999999</v>
       </c>
       <c r="G74" s="63">
         <f>$D74*1.28%</f>
-        <v>418.05350400000003</v>
+        <v>62.334848000000001</v>
       </c>
       <c r="H74" s="63">
         <f>$D74*1.21%</f>
-        <v>395.19120299999997</v>
+        <v>58.925910999999999</v>
       </c>
       <c r="I74" s="63">
         <f>$D74*1.49%</f>
-        <v>486.64040699999998</v>
+        <v>72.561658999999992</v>
       </c>
       <c r="J74" s="63">
         <f>D74*1.74%</f>
-        <v>568.29148199999997</v>
+        <v>84.736433999999988</v>
       </c>
       <c r="K74" s="44">
         <f t="shared" si="8"/>
-        <v>32660.43</v>
+        <v>4869.91</v>
       </c>
       <c r="L74" s="83">
         <f t="shared" si="9"/>
-        <v>32660.43</v>
+        <v>4869.9100000000008</v>
       </c>
       <c r="M74" s="95">
         <f>L74-D74</f>
@@ -3898,30 +3858,47 @@
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="79" t="s">
+      <c r="A75" s="36" t="s">
         <v>293</v>
       </c>
-      <c r="B75" s="132"/>
-      <c r="C75" s="132"/>
-      <c r="D75" s="45">
-        <v>100000</v>
+      <c r="B75" s="36"/>
+      <c r="C75" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="D75" s="211">
+        <v>821212.48</v>
       </c>
       <c r="E75" s="73">
-        <f t="shared" ref="E75:E76" si="10">D75</f>
-        <v>100000</v>
-      </c>
-      <c r="F75" s="73"/>
-      <c r="G75" s="73"/>
-      <c r="H75" s="73"/>
-      <c r="I75" s="73"/>
-      <c r="J75" s="63"/>
+        <f>D75*93.2%</f>
+        <v>765370.03136000002</v>
+      </c>
+      <c r="F75" s="63">
+        <f>$D75*1.08%</f>
+        <v>8869.0947840000008</v>
+      </c>
+      <c r="G75" s="63">
+        <f>$D75*1.28%</f>
+        <v>10511.519744000001</v>
+      </c>
+      <c r="H75" s="63">
+        <f>$D75*1.21%</f>
+        <v>9936.6710079999993</v>
+      </c>
+      <c r="I75" s="63">
+        <f>$D75*1.49%</f>
+        <v>12236.065951999999</v>
+      </c>
+      <c r="J75" s="63">
+        <f>D75*1.74%</f>
+        <v>14289.097151999998</v>
+      </c>
       <c r="K75" s="44">
         <f t="shared" si="8"/>
-        <v>100000</v>
+        <v>821212.48</v>
       </c>
       <c r="L75" s="83">
         <f t="shared" si="9"/>
-        <v>100000</v>
+        <v>821212.48</v>
       </c>
       <c r="M75" s="95">
         <f>L75-D75</f>
@@ -3932,18 +3909,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="173" t="s">
-        <v>294</v>
-      </c>
-      <c r="B76" s="173"/>
-      <c r="C76" s="174"/>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A76" s="79" t="s">
+        <v>289</v>
+      </c>
+      <c r="B76" s="132"/>
+      <c r="C76" s="132"/>
       <c r="D76" s="45">
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="E76" s="73">
-        <f t="shared" si="10"/>
-        <v>80000</v>
+        <f t="shared" ref="E76:E77" si="10">D76</f>
+        <v>100000</v>
       </c>
       <c r="F76" s="73"/>
       <c r="G76" s="73"/>
@@ -3952,11 +3929,11 @@
       <c r="J76" s="63"/>
       <c r="K76" s="44">
         <f t="shared" si="8"/>
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="L76" s="83">
         <f t="shared" si="9"/>
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="M76" s="95">
         <f>L76-D76</f>
@@ -3967,101 +3944,121 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="79"/>
-      <c r="B77" s="80"/>
-      <c r="C77" s="80"/>
-      <c r="D77" s="86"/>
-      <c r="E77" s="73"/>
+    <row r="77" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="172" t="s">
+        <v>290</v>
+      </c>
+      <c r="B77" s="172"/>
+      <c r="C77" s="173"/>
+      <c r="D77" s="45">
+        <v>80000</v>
+      </c>
+      <c r="E77" s="73">
+        <f t="shared" si="10"/>
+        <v>80000</v>
+      </c>
       <c r="F77" s="73"/>
       <c r="G77" s="73"/>
       <c r="H77" s="73"/>
       <c r="I77" s="73"/>
       <c r="J77" s="63"/>
-      <c r="K77" s="44"/>
-      <c r="L77" s="83"/>
-      <c r="M77" t="str">
-        <f>IF(K77=L77, "", "Error")</f>
+      <c r="K77" s="44">
+        <f t="shared" si="8"/>
+        <v>80000</v>
+      </c>
+      <c r="L77" s="83">
+        <f t="shared" si="9"/>
+        <v>80000</v>
+      </c>
+      <c r="M77" s="95">
+        <f>L77-D77</f>
+        <v>0</v>
+      </c>
+      <c r="N77" s="95">
+        <f>K77-D77</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A78" s="79"/>
+      <c r="B78" s="80"/>
+      <c r="C78" s="80"/>
+      <c r="D78" s="86"/>
+      <c r="E78" s="73"/>
+      <c r="F78" s="73"/>
+      <c r="G78" s="73"/>
+      <c r="H78" s="73"/>
+      <c r="I78" s="73"/>
+      <c r="J78" s="63"/>
+      <c r="K78" s="44"/>
+      <c r="L78" s="83"/>
+      <c r="M78" t="str">
+        <f>IF(K78=L78, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="34" t="s">
+    <row r="79" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B78" s="35"/>
-      <c r="C78" s="35"/>
-      <c r="D78" s="43">
-        <f t="shared" ref="D78:J78" si="11">SUM(D68:D77)</f>
-        <v>1997818.53</v>
-      </c>
-      <c r="E78" s="43">
+      <c r="B79" s="35"/>
+      <c r="C79" s="35"/>
+      <c r="D79" s="43">
+        <f t="shared" ref="D79:J79" si="11">SUM(D68:D78)</f>
+        <v>2884226.66</v>
+      </c>
+      <c r="E79" s="43">
         <f t="shared" si="11"/>
-        <v>1898941.7774800002</v>
-      </c>
-      <c r="F78" s="43">
+        <v>2699154.1546399998</v>
+      </c>
+      <c r="F79" s="43">
         <f t="shared" si="11"/>
-        <v>15703.954812000002</v>
-      </c>
-      <c r="G78" s="43">
+        <v>24629.162616000001</v>
+      </c>
+      <c r="G79" s="43">
         <f t="shared" si="11"/>
-        <v>18612.094592000001</v>
-      </c>
-      <c r="H78" s="43">
+        <v>29190.118656000002</v>
+      </c>
+      <c r="H79" s="43">
         <f t="shared" si="11"/>
-        <v>17594.245668999996</v>
-      </c>
-      <c r="I78" s="43">
+        <v>27593.784041999999</v>
+      </c>
+      <c r="I79" s="43">
         <f t="shared" si="11"/>
-        <v>21665.641360999998</v>
-      </c>
-      <c r="J78" s="43">
+        <v>33979.122497999997</v>
+      </c>
+      <c r="J79" s="43">
         <f t="shared" si="11"/>
-        <v>25300.816085999999</v>
-      </c>
-      <c r="K78" s="44">
-        <f>E78+J78+F78+G78+H78+I78</f>
-        <v>1997818.5300000003</v>
-      </c>
-      <c r="L78" s="74" t="str">
-        <f>IF(D78=K78, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="M78" s="95">
-        <f>D78-K78</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="99"/>
-      <c r="E79" s="47"/>
-      <c r="F79" s="47"/>
-      <c r="G79" s="47"/>
-      <c r="H79" s="47"/>
-      <c r="I79" s="47"/>
-      <c r="J79" s="6"/>
-      <c r="L79" s="74"/>
+        <v>39680.317547999992</v>
+      </c>
+      <c r="K79" s="44">
+        <f>E79+J79+F79+G79+H79+I79</f>
+        <v>2854226.6599999997</v>
+      </c>
+      <c r="L79" s="74" t="str">
+        <f>IF(D79=K79, "", "Error")</f>
+        <v>Error</v>
+      </c>
+      <c r="M79" s="95">
+        <f>D79-K79</f>
+        <v>30000.000000000466</v>
+      </c>
     </row>
     <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
       <c r="D80" s="99"/>
-      <c r="E80" s="46"/>
-      <c r="F80" s="46"/>
-      <c r="G80" s="46"/>
-      <c r="H80" s="46"/>
-      <c r="I80" s="46"/>
+      <c r="E80" s="47"/>
+      <c r="F80" s="47"/>
+      <c r="G80" s="47"/>
+      <c r="H80" s="47"/>
+      <c r="I80" s="47"/>
       <c r="J80" s="6"/>
       <c r="L80" s="74"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="33" t="s">
-        <v>234</v>
-      </c>
+    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
       <c r="D81" s="99"/>
@@ -4074,295 +4071,295 @@
       <c r="L81" s="74"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B82" s="36"/>
+      <c r="A82" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="B82" s="6"/>
       <c r="C82" s="6"/>
-      <c r="D82" s="45">
-        <f>184000</f>
-        <v>184000</v>
-      </c>
-      <c r="E82" s="73">
-        <f>D82*93.2%</f>
-        <v>171488</v>
-      </c>
-      <c r="F82" s="63">
-        <f>$D82*1.08%</f>
-        <v>1987.2</v>
-      </c>
-      <c r="G82" s="63">
-        <f>$D82*1.28%</f>
-        <v>2355.2000000000003</v>
-      </c>
-      <c r="H82" s="63">
-        <f>$D82*1.21%</f>
-        <v>2226.4</v>
-      </c>
-      <c r="I82" s="63">
-        <f>$D82*1.49%</f>
-        <v>2741.6</v>
-      </c>
-      <c r="J82" s="63">
-        <f>D82*1.74%</f>
-        <v>3201.6</v>
-      </c>
-      <c r="K82" s="82"/>
+      <c r="D82" s="99"/>
+      <c r="E82" s="46"/>
+      <c r="F82" s="46"/>
+      <c r="G82" s="46"/>
+      <c r="H82" s="46"/>
+      <c r="I82" s="46"/>
+      <c r="J82" s="6"/>
       <c r="L82" s="74"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B83" s="36"/>
       <c r="C83" s="6"/>
       <c r="D83" s="45">
-        <v>191550</v>
+        <f>184000</f>
+        <v>184000</v>
       </c>
       <c r="E83" s="73">
         <f>D83*93.2%</f>
-        <v>178524.6</v>
+        <v>171488</v>
       </c>
       <c r="F83" s="63">
         <f>$D83*1.08%</f>
-        <v>2068.7400000000002</v>
+        <v>1987.2</v>
       </c>
       <c r="G83" s="63">
         <f>$D83*1.28%</f>
-        <v>2451.84</v>
+        <v>2355.2000000000003</v>
       </c>
       <c r="H83" s="63">
         <f>$D83*1.21%</f>
-        <v>2317.7550000000001</v>
+        <v>2226.4</v>
       </c>
       <c r="I83" s="63">
         <f>$D83*1.49%</f>
-        <v>2854.0949999999998</v>
+        <v>2741.6</v>
       </c>
       <c r="J83" s="63">
         <f>D83*1.74%</f>
-        <v>3332.97</v>
+        <v>3201.6</v>
       </c>
       <c r="K83" s="82"/>
       <c r="L83" s="74"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>299</v>
+        <v>334</v>
       </c>
       <c r="B84" s="36"/>
       <c r="C84" s="6"/>
       <c r="D84" s="45">
-        <v>9800</v>
+        <v>191550</v>
       </c>
       <c r="E84" s="73">
         <f>D84*93.2%</f>
-        <v>9133.6</v>
+        <v>178524.6</v>
       </c>
       <c r="F84" s="63">
         <f>$D84*1.08%</f>
-        <v>105.84</v>
+        <v>2068.7400000000002</v>
       </c>
       <c r="G84" s="63">
         <f>$D84*1.28%</f>
-        <v>125.44000000000001</v>
+        <v>2451.84</v>
       </c>
       <c r="H84" s="63">
         <f>$D84*1.21%</f>
-        <v>118.58</v>
+        <v>2317.7550000000001</v>
       </c>
       <c r="I84" s="63">
         <f>$D84*1.49%</f>
-        <v>146.02000000000001</v>
+        <v>2854.0949999999998</v>
       </c>
       <c r="J84" s="63">
         <f>D84*1.74%</f>
-        <v>170.51999999999998</v>
+        <v>3332.97</v>
       </c>
       <c r="K84" s="82"/>
       <c r="L84" s="74"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="B85" s="36"/>
       <c r="C85" s="6"/>
       <c r="D85" s="45">
-        <v>21780</v>
+        <v>9800</v>
       </c>
       <c r="E85" s="73">
         <f>D85*93.2%</f>
-        <v>20298.960000000003</v>
+        <v>9133.6</v>
       </c>
       <c r="F85" s="63">
         <f>$D85*1.08%</f>
-        <v>235.22400000000002</v>
+        <v>105.84</v>
       </c>
       <c r="G85" s="63">
         <f>$D85*1.28%</f>
-        <v>278.78399999999999</v>
+        <v>125.44000000000001</v>
       </c>
       <c r="H85" s="63">
         <f>$D85*1.21%</f>
-        <v>263.53800000000001</v>
+        <v>118.58</v>
       </c>
       <c r="I85" s="63">
         <f>$D85*1.49%</f>
-        <v>324.52199999999999</v>
+        <v>146.02000000000001</v>
       </c>
       <c r="J85" s="63">
         <f>D85*1.74%</f>
-        <v>378.97199999999998</v>
+        <v>170.51999999999998</v>
       </c>
       <c r="K85" s="82"/>
       <c r="L85" s="74"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="B86" s="36"/>
       <c r="C86" s="6"/>
       <c r="D86" s="45">
-        <v>78800</v>
+        <v>21780</v>
       </c>
       <c r="E86" s="73">
         <f>D86*93.2%</f>
-        <v>73441.600000000006</v>
+        <v>20298.960000000003</v>
       </c>
       <c r="F86" s="63">
         <f>$D86*1.08%</f>
-        <v>851.04000000000008</v>
+        <v>235.22400000000002</v>
       </c>
       <c r="G86" s="63">
         <f>$D86*1.28%</f>
-        <v>1008.6400000000001</v>
+        <v>278.78399999999999</v>
       </c>
       <c r="H86" s="63">
         <f>$D86*1.21%</f>
-        <v>953.48</v>
+        <v>263.53800000000001</v>
       </c>
       <c r="I86" s="63">
         <f>$D86*1.49%</f>
-        <v>1174.1199999999999</v>
+        <v>324.52199999999999</v>
       </c>
       <c r="J86" s="63">
         <f>D86*1.74%</f>
-        <v>1371.12</v>
+        <v>378.97199999999998</v>
       </c>
       <c r="K86" s="82"/>
       <c r="L86" s="74"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B87" s="36"/>
       <c r="C87" s="6"/>
       <c r="D87" s="45">
-        <v>813200</v>
-      </c>
-      <c r="E87" s="84">
-        <f>D87</f>
-        <v>813200</v>
-      </c>
-      <c r="F87" s="84"/>
-      <c r="G87" s="84"/>
-      <c r="H87" s="84"/>
-      <c r="I87" s="84"/>
-      <c r="J87" s="63"/>
+        <v>78800</v>
+      </c>
+      <c r="E87" s="73">
+        <f>D87*93.2%</f>
+        <v>73441.600000000006</v>
+      </c>
+      <c r="F87" s="63">
+        <f>$D87*1.08%</f>
+        <v>851.04000000000008</v>
+      </c>
+      <c r="G87" s="63">
+        <f>$D87*1.28%</f>
+        <v>1008.6400000000001</v>
+      </c>
+      <c r="H87" s="63">
+        <f>$D87*1.21%</f>
+        <v>953.48</v>
+      </c>
+      <c r="I87" s="63">
+        <f>$D87*1.49%</f>
+        <v>1174.1199999999999</v>
+      </c>
+      <c r="J87" s="63">
+        <f>D87*1.74%</f>
+        <v>1371.12</v>
+      </c>
       <c r="K87" s="82"/>
       <c r="L87" s="74"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A88" s="6"/>
-      <c r="B88" s="6"/>
+      <c r="A88" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B88" s="36"/>
       <c r="C88" s="6"/>
-      <c r="D88" s="45"/>
-      <c r="E88" s="73"/>
-      <c r="F88" s="63"/>
-      <c r="G88" s="63"/>
-      <c r="H88" s="63"/>
-      <c r="I88" s="63"/>
+      <c r="D88" s="45">
+        <v>813200</v>
+      </c>
+      <c r="E88" s="84">
+        <f>D88</f>
+        <v>813200</v>
+      </c>
+      <c r="F88" s="84"/>
+      <c r="G88" s="84"/>
+      <c r="H88" s="84"/>
+      <c r="I88" s="84"/>
       <c r="J88" s="63"/>
+      <c r="K88" s="82"/>
       <c r="L88" s="74"/>
-      <c r="M88" s="44"/>
-    </row>
-    <row r="89" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="34" t="s">
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A89" s="6"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="45"/>
+      <c r="E89" s="73"/>
+      <c r="F89" s="63"/>
+      <c r="G89" s="63"/>
+      <c r="H89" s="63"/>
+      <c r="I89" s="63"/>
+      <c r="J89" s="63"/>
+      <c r="L89" s="74"/>
+      <c r="M89" s="44"/>
+    </row>
+    <row r="90" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="34" t="s">
         <v>235</v>
       </c>
-      <c r="B89" s="34"/>
-      <c r="C89" s="34"/>
-      <c r="D89" s="43">
-        <f t="shared" ref="D89:J89" si="12">SUM(D82:D88)</f>
+      <c r="B90" s="34"/>
+      <c r="C90" s="34"/>
+      <c r="D90" s="43">
+        <f t="shared" ref="D90:J90" si="12">SUM(D83:D89)</f>
         <v>1299130</v>
       </c>
-      <c r="E89" s="43">
+      <c r="E90" s="43">
         <f t="shared" si="12"/>
         <v>1266086.76</v>
       </c>
-      <c r="F89" s="43">
+      <c r="F90" s="43">
         <f t="shared" si="12"/>
         <v>5248.0440000000008</v>
       </c>
-      <c r="G89" s="43">
+      <c r="G90" s="43">
         <f t="shared" si="12"/>
         <v>6219.9040000000005</v>
       </c>
-      <c r="H89" s="43">
+      <c r="H90" s="43">
         <f t="shared" si="12"/>
         <v>5879.7530000000006</v>
       </c>
-      <c r="I89" s="43">
+      <c r="I90" s="43">
         <f t="shared" si="12"/>
         <v>7240.357</v>
       </c>
-      <c r="J89" s="43">
+      <c r="J90" s="43">
         <f t="shared" si="12"/>
         <v>8455.1820000000007</v>
       </c>
-      <c r="K89" s="44">
-        <f>E89+J89+F89+G89+H89+I89</f>
+      <c r="K90" s="44">
+        <f>E90+J90+F90+G90+H90+I90</f>
         <v>1299130.0000000002</v>
       </c>
-      <c r="L89" s="74" t="str">
-        <f>IF(D89=K89, "", "Error")</f>
+      <c r="L90" s="74" t="str">
+        <f>IF(D90=K90, "", "Error")</f>
         <v/>
       </c>
-      <c r="N89" s="44"/>
-    </row>
-    <row r="90" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="99"/>
-      <c r="E90" s="47"/>
-      <c r="F90" s="47"/>
-      <c r="G90" s="47"/>
-      <c r="H90" s="47"/>
-      <c r="I90" s="47"/>
-      <c r="J90" s="6"/>
-      <c r="L90" s="74"/>
+      <c r="N90" s="44"/>
     </row>
     <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
       <c r="D91" s="99"/>
-      <c r="E91" s="46"/>
-      <c r="F91" s="46"/>
-      <c r="G91" s="46"/>
-      <c r="H91" s="46"/>
-      <c r="I91" s="46"/>
+      <c r="E91" s="47"/>
+      <c r="F91" s="47"/>
+      <c r="G91" s="47"/>
+      <c r="H91" s="47"/>
+      <c r="I91" s="47"/>
       <c r="J91" s="6"/>
       <c r="L91" s="74"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A92" s="33" t="s">
-        <v>6</v>
-      </c>
+    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
       <c r="D92" s="99"/>
@@ -4374,158 +4371,138 @@
       <c r="J92" s="6"/>
       <c r="L92" s="74"/>
     </row>
-    <row r="93" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="6" t="s">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A93" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="99"/>
+      <c r="E93" s="46"/>
+      <c r="F93" s="46"/>
+      <c r="G93" s="46"/>
+      <c r="H93" s="46"/>
+      <c r="I93" s="46"/>
+      <c r="J93" s="6"/>
+      <c r="L93" s="74"/>
+    </row>
+    <row r="94" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B93" s="6" t="s">
+      <c r="B94" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C93" s="6"/>
-      <c r="D93" s="45">
+      <c r="C94" s="6"/>
+      <c r="D94" s="45">
         <v>700000</v>
       </c>
-      <c r="E93" s="73">
-        <f>D93*93.2%</f>
+      <c r="E94" s="73">
+        <f>D94*93.2%</f>
         <v>652400</v>
       </c>
-      <c r="F93" s="63">
-        <f>$D93*1.08%</f>
+      <c r="F94" s="63">
+        <f>$D94*1.08%</f>
         <v>7560</v>
       </c>
-      <c r="G93" s="63">
-        <f>$D93*1.28%</f>
+      <c r="G94" s="63">
+        <f>$D94*1.28%</f>
         <v>8960</v>
       </c>
-      <c r="H93" s="63">
-        <f>$D93*1.21%</f>
+      <c r="H94" s="63">
+        <f>$D94*1.21%</f>
         <v>8470</v>
       </c>
-      <c r="I93" s="63">
-        <f>$D93*1.49%</f>
+      <c r="I94" s="63">
+        <f>$D94*1.49%</f>
         <v>10430</v>
       </c>
-      <c r="J93" s="63">
-        <f>D93*1.74%</f>
+      <c r="J94" s="63">
+        <f>D94*1.74%</f>
         <v>12180</v>
       </c>
-      <c r="L93" s="74"/>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A94" s="33"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="45"/>
-      <c r="E94" s="73"/>
-      <c r="F94" s="73"/>
-      <c r="G94" s="73"/>
-      <c r="H94" s="73"/>
-      <c r="I94" s="73"/>
-      <c r="J94" s="63"/>
       <c r="L94" s="74"/>
-      <c r="N94" s="45"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A95" s="6"/>
+      <c r="A95" s="33"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
-      <c r="D95" s="99"/>
-      <c r="E95" s="48"/>
-      <c r="F95" s="48"/>
-      <c r="G95" s="48"/>
-      <c r="H95" s="48"/>
-      <c r="I95" s="48"/>
-      <c r="J95" s="6"/>
+      <c r="D95" s="45"/>
+      <c r="E95" s="73"/>
+      <c r="F95" s="73"/>
+      <c r="G95" s="73"/>
+      <c r="H95" s="73"/>
+      <c r="I95" s="73"/>
+      <c r="J95" s="63"/>
       <c r="L95" s="74"/>
-      <c r="N95" s="44"/>
+      <c r="N95" s="45"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A96" s="34" t="s">
+      <c r="A96" s="6"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="99"/>
+      <c r="E96" s="48"/>
+      <c r="F96" s="48"/>
+      <c r="G96" s="48"/>
+      <c r="H96" s="48"/>
+      <c r="I96" s="48"/>
+      <c r="J96" s="6"/>
+      <c r="L96" s="74"/>
+      <c r="N96" s="44"/>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A97" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B96" s="34"/>
-      <c r="C96" s="34"/>
-      <c r="D96" s="43">
-        <f>SUM(D93:D95)</f>
+      <c r="B97" s="34"/>
+      <c r="C97" s="34"/>
+      <c r="D97" s="43">
+        <f>SUM(D94:D96)</f>
         <v>700000</v>
       </c>
-      <c r="E96" s="43">
-        <f>SUM(E93:E95)</f>
+      <c r="E97" s="43">
+        <f>SUM(E94:E96)</f>
         <v>652400</v>
       </c>
-      <c r="F96" s="43">
-        <f t="shared" ref="F96:I96" si="13">SUM(F93:F95)</f>
+      <c r="F97" s="43">
+        <f t="shared" ref="F97:I97" si="13">SUM(F94:F96)</f>
         <v>7560</v>
       </c>
-      <c r="G96" s="43">
+      <c r="G97" s="43">
         <f t="shared" si="13"/>
         <v>8960</v>
       </c>
-      <c r="H96" s="43">
+      <c r="H97" s="43">
         <f t="shared" si="13"/>
         <v>8470</v>
       </c>
-      <c r="I96" s="43">
+      <c r="I97" s="43">
         <f t="shared" si="13"/>
         <v>10430</v>
       </c>
-      <c r="J96" s="43">
-        <f>SUM(J93:J95)</f>
+      <c r="J97" s="43">
+        <f>SUM(J94:J96)</f>
         <v>12180</v>
       </c>
-      <c r="K96" s="44">
-        <f>E96+J96+F96+G96+H96+I96</f>
+      <c r="K97" s="44">
+        <f>E97+J97+F97+G97+H97+I97</f>
         <v>700000</v>
       </c>
-      <c r="L96" s="74" t="str">
-        <f>IF(D96=K96, "", "Error")</f>
+      <c r="L97" s="74" t="str">
+        <f>IF(D97=K97, "", "Error")</f>
         <v/>
       </c>
-      <c r="N96" s="44"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A97" s="6" t="s">
+      <c r="N97" s="44"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A98" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B97" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="C97" s="6"/>
-      <c r="D97" s="45"/>
-      <c r="E97" s="73">
-        <f>D97*93.2%</f>
-        <v>0</v>
-      </c>
-      <c r="F97" s="63">
-        <f>$D97*1.08%</f>
-        <v>0</v>
-      </c>
-      <c r="G97" s="63">
-        <f>$D97*1.28%</f>
-        <v>0</v>
-      </c>
-      <c r="H97" s="63">
-        <f>$D97*1.21%</f>
-        <v>0</v>
-      </c>
-      <c r="I97" s="63">
-        <f>$D97*1.49%</f>
-        <v>0</v>
-      </c>
-      <c r="J97" s="63">
-        <f>D97*1.74%</f>
-        <v>0</v>
-      </c>
-      <c r="L97" s="74"/>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A98" s="6" t="s">
-        <v>30</v>
-      </c>
       <c r="B98" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="C98" s="52"/>
+        <v>311</v>
+      </c>
+      <c r="C98" s="6"/>
       <c r="D98" s="45"/>
       <c r="E98" s="73">
         <f>D98*93.2%</f>
@@ -4553,205 +4530,227 @@
       </c>
       <c r="L98" s="74"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A99" s="34" t="s">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A99" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="C99" s="52"/>
+      <c r="D99" s="45"/>
+      <c r="E99" s="73">
+        <f>D99*93.2%</f>
+        <v>0</v>
+      </c>
+      <c r="F99" s="63">
+        <f>$D99*1.08%</f>
+        <v>0</v>
+      </c>
+      <c r="G99" s="63">
+        <f>$D99*1.28%</f>
+        <v>0</v>
+      </c>
+      <c r="H99" s="63">
+        <f>$D99*1.21%</f>
+        <v>0</v>
+      </c>
+      <c r="I99" s="63">
+        <f>$D99*1.49%</f>
+        <v>0</v>
+      </c>
+      <c r="J99" s="63">
+        <f>D99*1.74%</f>
+        <v>0</v>
+      </c>
+      <c r="L99" s="74"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A100" s="34" t="s">
         <v>236</v>
       </c>
-      <c r="B99" s="34"/>
-      <c r="C99" s="34"/>
-      <c r="D99" s="81">
-        <f>SUM(D97:D98)</f>
-        <v>0</v>
-      </c>
-      <c r="E99" s="72">
-        <f t="shared" ref="E99:J99" si="14">SUM(E97:E98)</f>
-        <v>0</v>
-      </c>
-      <c r="F99" s="72">
+      <c r="B100" s="34"/>
+      <c r="C100" s="34"/>
+      <c r="D100" s="81">
+        <f>SUM(D98:D99)</f>
+        <v>0</v>
+      </c>
+      <c r="E100" s="72">
+        <f t="shared" ref="E100:J100" si="14">SUM(E98:E99)</f>
+        <v>0</v>
+      </c>
+      <c r="F100" s="72">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G99" s="72">
+      <c r="G100" s="72">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H99" s="72">
+      <c r="H100" s="72">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I99" s="72">
+      <c r="I100" s="72">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J99" s="72">
+      <c r="J100" s="72">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K99" s="44">
-        <f>E99+J99+F99+G99+H99+I99</f>
-        <v>0</v>
-      </c>
-      <c r="L99" s="74" t="str">
-        <f>IF(D99=K99, "", "Error")</f>
+      <c r="K100" s="44">
+        <f>E100+J100+F100+G100+H100+I100</f>
+        <v>0</v>
+      </c>
+      <c r="L100" s="74" t="str">
+        <f>IF(D100=K100, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="115"/>
-      <c r="B100" s="115"/>
-      <c r="C100" s="115"/>
-      <c r="D100" s="116"/>
-      <c r="E100" s="10"/>
-      <c r="F100" s="10"/>
-      <c r="G100" s="10"/>
-      <c r="H100" s="10"/>
-      <c r="I100" s="10"/>
-      <c r="J100" s="115"/>
-      <c r="L100" s="74"/>
-    </row>
-    <row r="101" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="117" t="s">
+    <row r="101" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="115"/>
+      <c r="B101" s="115"/>
+      <c r="C101" s="115"/>
+      <c r="D101" s="116"/>
+      <c r="E101" s="10"/>
+      <c r="F101" s="10"/>
+      <c r="G101" s="10"/>
+      <c r="H101" s="10"/>
+      <c r="I101" s="10"/>
+      <c r="J101" s="115"/>
+      <c r="L101" s="74"/>
+    </row>
+    <row r="102" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="117" t="s">
         <v>47</v>
       </c>
-      <c r="B101" s="118"/>
-      <c r="C101" s="118"/>
-      <c r="D101" s="119">
+      <c r="B102" s="118"/>
+      <c r="C102" s="118"/>
+      <c r="D102" s="119">
         <v>1500000</v>
       </c>
-      <c r="E101" s="143">
-        <f>D101*93.2%</f>
+      <c r="E102" s="143">
+        <f>D102*93.2%</f>
         <v>1398000</v>
       </c>
-      <c r="F101" s="143">
-        <f>$D101*1.08%</f>
+      <c r="F102" s="143">
+        <f>$D102*1.08%</f>
         <v>16200</v>
       </c>
-      <c r="G101" s="143">
-        <f>$D101*1.28%</f>
+      <c r="G102" s="143">
+        <f>$D102*1.28%</f>
         <v>19200</v>
       </c>
-      <c r="H101" s="143">
-        <f>$D101*1.21%</f>
+      <c r="H102" s="143">
+        <f>$D102*1.21%</f>
         <v>18150</v>
       </c>
-      <c r="I101" s="143">
-        <f>$D101*1.49%</f>
+      <c r="I102" s="143">
+        <f>$D102*1.49%</f>
         <v>22350</v>
       </c>
-      <c r="J101" s="144">
-        <f>D101*1.74%</f>
+      <c r="J102" s="144">
+        <f>D102*1.74%</f>
         <v>26100</v>
       </c>
-      <c r="K101" s="44">
-        <f>E101+J101+F101+G101+H101+I101</f>
+      <c r="K102" s="44">
+        <f>E102+J102+F102+G102+H102+I102</f>
         <v>1500000</v>
       </c>
-      <c r="L101" s="74" t="str">
-        <f>IF(D101=K101, "", "Error")</f>
+      <c r="L102" s="74" t="str">
+        <f>IF(D102=K102, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="120"/>
-      <c r="B102" s="121"/>
-      <c r="C102" s="121"/>
-      <c r="D102" s="122"/>
-      <c r="E102" s="123"/>
-      <c r="F102" s="123"/>
-      <c r="G102" s="123"/>
-      <c r="H102" s="123"/>
-      <c r="I102" s="123"/>
-      <c r="J102" s="124"/>
-      <c r="K102" s="44"/>
-      <c r="L102" s="74"/>
-    </row>
-    <row r="103" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="3" t="s">
+    <row r="103" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="120"/>
+      <c r="B103" s="121"/>
+      <c r="C103" s="121"/>
+      <c r="D103" s="122"/>
+      <c r="E103" s="123"/>
+      <c r="F103" s="123"/>
+      <c r="G103" s="123"/>
+      <c r="H103" s="123"/>
+      <c r="I103" s="123"/>
+      <c r="J103" s="124"/>
+      <c r="K103" s="44"/>
+      <c r="L103" s="74"/>
+    </row>
+    <row r="104" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B103" s="12"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="100">
-        <f t="shared" ref="D103:J103" si="15">SUM(D101+D57+D52+D99+D96+D89+D78+D66+D44+D39+D61)</f>
-        <v>9142586.040000001</v>
-      </c>
-      <c r="E103" s="100">
+      <c r="B104" s="12"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="100">
+        <f t="shared" ref="D104:J104" si="15">SUM(D102+D57+D52+D100+D97+D90+D79+D66+D44+D39+D61)</f>
+        <v>10039533.15</v>
+      </c>
+      <c r="E104" s="100">
         <f t="shared" si="15"/>
-        <v>8625269.41952</v>
-      </c>
-      <c r="F103" s="100">
+        <v>9427209.6766800005</v>
+      </c>
+      <c r="F104" s="100">
         <f t="shared" si="15"/>
-        <v>82162.051487999997</v>
-      </c>
-      <c r="G103" s="100">
+        <v>92486.669292000006</v>
+      </c>
+      <c r="G104" s="100">
         <f t="shared" si="15"/>
-        <v>97377.246207999997</v>
-      </c>
-      <c r="H103" s="100">
+        <v>109613.83027199999</v>
+      </c>
+      <c r="H104" s="100">
         <f t="shared" si="15"/>
-        <v>92051.928055999975</v>
-      </c>
-      <c r="I103" s="100">
+        <v>103619.32392899999</v>
+      </c>
+      <c r="I104" s="100">
         <f t="shared" si="15"/>
-        <v>113353.200664</v>
-      </c>
-      <c r="J103" s="100">
+        <v>127597.34930100001</v>
+      </c>
+      <c r="J104" s="100">
         <f t="shared" si="15"/>
-        <v>132372.19406399998</v>
-      </c>
-      <c r="K103" s="44">
-        <f>E103+J103+F103+G103+H103+I103</f>
-        <v>9142586.0400000028</v>
-      </c>
-      <c r="L103" s="74" t="str">
-        <f>IF(D103=K103, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="M103" s="95">
-        <f>D103-K103</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D104" s="98"/>
-      <c r="E104" s="44"/>
-      <c r="F104" s="44"/>
-      <c r="G104" s="44"/>
-      <c r="H104" s="44"/>
-      <c r="I104" s="44"/>
-    </row>
-    <row r="105" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="69" t="s">
-        <v>42</v>
-      </c>
-      <c r="B105" s="68"/>
-      <c r="C105" s="68"/>
+        <v>149006.30052599998</v>
+      </c>
+      <c r="K104" s="44">
+        <f>E104+J104+F104+G104+H104+I104</f>
+        <v>10009533.15</v>
+      </c>
+      <c r="L104" s="74" t="str">
+        <f>IF(D104=K104, "", "Error")</f>
+        <v>Error</v>
+      </c>
+      <c r="M104" s="95">
+        <f>D104-K104</f>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D105" s="98"/>
       <c r="E105" s="44"/>
       <c r="F105" s="44"/>
       <c r="G105" s="44"/>
       <c r="H105" s="44"/>
       <c r="I105" s="44"/>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A106" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C106" s="149">
-        <f>21780*2</f>
-        <v>43560</v>
-      </c>
+    <row r="106" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="69" t="s">
+        <v>42</v>
+      </c>
+      <c r="B106" s="68"/>
+      <c r="C106" s="68"/>
       <c r="E106" s="44"/>
       <c r="F106" s="44"/>
       <c r="G106" s="44"/>
       <c r="H106" s="44"/>
       <c r="I106" s="44"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C107" s="149">
-        <v>21780</v>
+        <v>300</v>
+      </c>
+      <c r="C107" s="148">
+        <f>21780*2</f>
+        <v>43560</v>
       </c>
       <c r="E107" s="44"/>
       <c r="F107" s="44"/>
@@ -4759,12 +4758,12 @@
       <c r="H107" s="44"/>
       <c r="I107" s="44"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C108" s="149">
-        <v>18000</v>
+        <v>301</v>
+      </c>
+      <c r="C108" s="148">
+        <v>21780</v>
       </c>
       <c r="E108" s="44"/>
       <c r="F108" s="44"/>
@@ -4772,12 +4771,12 @@
       <c r="H108" s="44"/>
       <c r="I108" s="44"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C109" s="149">
-        <v>9000</v>
+        <v>302</v>
+      </c>
+      <c r="C109" s="148">
+        <v>18000</v>
       </c>
       <c r="E109" s="44"/>
       <c r="F109" s="44"/>
@@ -4785,12 +4784,12 @@
       <c r="H109" s="44"/>
       <c r="I109" s="44"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C110" s="149">
-        <v>18000</v>
+        <v>303</v>
+      </c>
+      <c r="C110" s="148">
+        <v>9000</v>
       </c>
       <c r="E110" s="44"/>
       <c r="F110" s="44"/>
@@ -4798,11 +4797,11 @@
       <c r="H110" s="44"/>
       <c r="I110" s="44"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="C111" s="149">
+        <v>304</v>
+      </c>
+      <c r="C111" s="148">
         <v>18000</v>
       </c>
       <c r="E111" s="44"/>
@@ -4811,12 +4810,12 @@
       <c r="H111" s="44"/>
       <c r="I111" s="44"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="C112" s="149">
-        <v>9000</v>
+        <v>305</v>
+      </c>
+      <c r="C112" s="148">
+        <v>18000</v>
       </c>
       <c r="E112" s="44"/>
       <c r="F112" s="44"/>
@@ -4826,9 +4825,9 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C113" s="149">
+        <v>307</v>
+      </c>
+      <c r="C113" s="148">
         <v>9000</v>
       </c>
       <c r="E113" s="44"/>
@@ -4839,9 +4838,9 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="C114" s="149">
+        <v>306</v>
+      </c>
+      <c r="C114" s="148">
         <v>9000</v>
       </c>
       <c r="E114" s="44"/>
@@ -4852,9 +4851,9 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C115" s="149">
+        <v>308</v>
+      </c>
+      <c r="C115" s="148">
         <v>9000</v>
       </c>
       <c r="E115" s="44"/>
@@ -4864,17 +4863,21 @@
       <c r="I115" s="44"/>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A116" s="1"/>
-      <c r="C116" s="175"/>
+      <c r="A116" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C116" s="148">
+        <v>9000</v>
+      </c>
       <c r="E116" s="44"/>
       <c r="F116" s="44"/>
       <c r="G116" s="44"/>
       <c r="H116" s="44"/>
       <c r="I116" s="44"/>
     </row>
-    <row r="117" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
-      <c r="C117" s="175"/>
+      <c r="C117" s="174"/>
       <c r="E117" s="44"/>
       <c r="F117" s="44"/>
       <c r="G117" s="44"/>
@@ -4882,21 +4885,23 @@
       <c r="I117" s="44"/>
     </row>
     <row r="118" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="70" t="s">
-        <v>18</v>
-      </c>
-      <c r="B118" s="71"/>
-      <c r="C118" s="67">
-        <f>SUM(C106:C116)</f>
-        <v>164340</v>
-      </c>
+      <c r="A118" s="1"/>
+      <c r="C118" s="174"/>
       <c r="E118" s="44"/>
       <c r="F118" s="44"/>
       <c r="G118" s="44"/>
       <c r="H118" s="44"/>
       <c r="I118" s="44"/>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="70" t="s">
+        <v>18</v>
+      </c>
+      <c r="B119" s="71"/>
+      <c r="C119" s="67">
+        <f>SUM(C107:C117)</f>
+        <v>164340</v>
+      </c>
       <c r="E119" s="44"/>
       <c r="F119" s="44"/>
       <c r="G119" s="44"/>
@@ -4904,170 +4909,159 @@
       <c r="I119" s="44"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E120" s="65"/>
-      <c r="F120" s="65"/>
-      <c r="G120" s="65"/>
-      <c r="H120" s="65"/>
-      <c r="I120" s="65"/>
+      <c r="E120" s="44"/>
+      <c r="F120" s="44"/>
+      <c r="G120" s="44"/>
+      <c r="H120" s="44"/>
+      <c r="I120" s="44"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="186" t="s">
+      <c r="E121" s="65"/>
+      <c r="F121" s="65"/>
+      <c r="G121" s="65"/>
+      <c r="H121" s="65"/>
+      <c r="I121" s="65"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A122" s="185" t="s">
         <v>37</v>
       </c>
-      <c r="B121" s="187"/>
-      <c r="C121" s="187"/>
-      <c r="D121" s="187"/>
-      <c r="E121" s="90" t="s">
+      <c r="B122" s="186"/>
+      <c r="C122" s="186"/>
+      <c r="D122" s="186"/>
+      <c r="E122" s="90" t="s">
         <v>12</v>
       </c>
-      <c r="F121" s="90" t="s">
+      <c r="F122" s="90" t="s">
         <v>174</v>
       </c>
-      <c r="G121" s="90" t="s">
+      <c r="G122" s="90" t="s">
         <v>175</v>
       </c>
-      <c r="H121" s="90" t="s">
+      <c r="H122" s="90" t="s">
         <v>176</v>
       </c>
-      <c r="I121" s="90" t="s">
+      <c r="I122" s="90" t="s">
         <v>177</v>
       </c>
-      <c r="J121" s="91" t="s">
+      <c r="J122" s="91" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="188"/>
-      <c r="B122" s="189"/>
-      <c r="C122" s="92"/>
-      <c r="D122" s="45"/>
-      <c r="E122" s="73">
-        <f>D122</f>
-        <v>0</v>
-      </c>
-      <c r="F122" s="73"/>
-      <c r="G122" s="73"/>
-      <c r="H122" s="73"/>
-      <c r="I122" s="73"/>
-      <c r="J122" s="63"/>
-    </row>
-    <row r="123" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="188"/>
-      <c r="B123" s="189"/>
+    <row r="123" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="187"/>
+      <c r="B123" s="188"/>
       <c r="C123" s="92"/>
       <c r="D123" s="45"/>
-      <c r="E123" s="73"/>
+      <c r="E123" s="73">
+        <f>D123</f>
+        <v>0</v>
+      </c>
       <c r="F123" s="73"/>
       <c r="G123" s="73"/>
       <c r="H123" s="73"/>
       <c r="I123" s="73"/>
       <c r="J123" s="63"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124" s="183" t="s">
+    <row r="124" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="187"/>
+      <c r="B124" s="188"/>
+      <c r="C124" s="92"/>
+      <c r="D124" s="45"/>
+      <c r="E124" s="73"/>
+      <c r="F124" s="73"/>
+      <c r="G124" s="73"/>
+      <c r="H124" s="73"/>
+      <c r="I124" s="73"/>
+      <c r="J124" s="63"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A125" s="182" t="s">
         <v>18</v>
       </c>
-      <c r="B124" s="184"/>
-      <c r="C124" s="185"/>
-      <c r="D124" s="89">
-        <f>SUM(D122:D123)</f>
-        <v>0</v>
-      </c>
-      <c r="E124" s="89">
-        <f>SUM(E122:E123)</f>
-        <v>0</v>
-      </c>
-      <c r="F124" s="89"/>
-      <c r="G124" s="89"/>
-      <c r="H124" s="89"/>
-      <c r="I124" s="89"/>
-      <c r="J124" s="89">
-        <f>SUM(J122:J123)</f>
-        <v>0</v>
-      </c>
-      <c r="L124" s="44">
-        <f>E124+J124</f>
-        <v>0</v>
-      </c>
-      <c r="M124" s="74" t="str">
-        <f>IF(D124=L124, "", "Error")</f>
+      <c r="B125" s="183"/>
+      <c r="C125" s="184"/>
+      <c r="D125" s="89">
+        <f>SUM(D123:D124)</f>
+        <v>0</v>
+      </c>
+      <c r="E125" s="89">
+        <f>SUM(E123:E124)</f>
+        <v>0</v>
+      </c>
+      <c r="F125" s="89"/>
+      <c r="G125" s="89"/>
+      <c r="H125" s="89"/>
+      <c r="I125" s="89"/>
+      <c r="J125" s="89">
+        <f>SUM(J123:J124)</f>
+        <v>0</v>
+      </c>
+      <c r="L125" s="44">
+        <f>E125+J125</f>
+        <v>0</v>
+      </c>
+      <c r="M125" s="74" t="str">
+        <f>IF(D125=L125, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E126" s="44"/>
-      <c r="F126" s="44"/>
-      <c r="G126" s="44"/>
-      <c r="H126" s="44"/>
-      <c r="I126" s="44"/>
-    </row>
     <row r="127" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="39" t="s">
+      <c r="E127" s="44"/>
+      <c r="F127" s="44"/>
+      <c r="G127" s="44"/>
+      <c r="H127" s="44"/>
+      <c r="I127" s="44"/>
+    </row>
+    <row r="128" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="B127" s="40">
-        <f>D103</f>
-        <v>9142586.040000001</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="41" t="s">
+      <c r="B128" s="40">
+        <f>D104</f>
+        <v>10039533.15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="B128" s="42">
-        <f>D103-D101</f>
-        <v>7642586.040000001</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D129" s="182"/>
-      <c r="E129" s="182"/>
-      <c r="F129" s="102"/>
-      <c r="G129" s="102"/>
-      <c r="H129" s="102"/>
-      <c r="I129" s="102"/>
+      <c r="B129" s="42">
+        <f>D104-D102</f>
+        <v>8539533.1500000004</v>
+      </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A130" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B130" s="18"/>
-      <c r="C130" s="19"/>
-      <c r="D130" s="182"/>
-      <c r="E130" s="182"/>
+      <c r="D130" s="181"/>
+      <c r="E130" s="181"/>
       <c r="F130" s="102"/>
       <c r="G130" s="102"/>
       <c r="H130" s="102"/>
       <c r="I130" s="102"/>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A131" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B131" s="9">
-        <v>394371.04000000097</v>
-      </c>
-      <c r="C131" s="21"/>
-      <c r="D131" s="182"/>
-      <c r="E131" s="182"/>
+      <c r="A131" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B131" s="18"/>
+      <c r="C131" s="19"/>
+      <c r="D131" s="181"/>
+      <c r="E131" s="181"/>
       <c r="F131" s="102"/>
       <c r="G131" s="102"/>
       <c r="H131" s="102"/>
       <c r="I131" s="102"/>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A132" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B132" s="31">
-        <f>PRORRATEO!H127</f>
-        <v>5931731.0433599977</v>
-      </c>
-      <c r="C132" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D132" s="182"/>
-      <c r="E132" s="182"/>
+      <c r="A132" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B132" s="9">
+        <v>394371.04000000097</v>
+      </c>
+      <c r="C132" s="21"/>
+      <c r="D132" s="181"/>
+      <c r="E132" s="181"/>
       <c r="F132" s="102"/>
       <c r="G132" s="102"/>
       <c r="H132" s="102"/>
@@ -5075,206 +5069,224 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="B133" s="94">
-        <f>-B128</f>
-        <v>-7642586.040000001</v>
-      </c>
-      <c r="C133" s="19"/>
-      <c r="D133" s="182"/>
-      <c r="E133" s="182"/>
+        <v>23</v>
+      </c>
+      <c r="B133" s="31">
+        <f>PRORRATEO!H127</f>
+        <v>5931731.0433599977</v>
+      </c>
+      <c r="C133" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D133" s="181"/>
+      <c r="E133" s="181"/>
       <c r="F133" s="102"/>
       <c r="G133" s="102"/>
       <c r="H133" s="102"/>
       <c r="I133" s="102"/>
-      <c r="K133" s="45"/>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B134" s="94">
-        <f>-D124</f>
-        <v>0</v>
+        <f>-B129</f>
+        <v>-8539533.1500000004</v>
       </c>
       <c r="C134" s="19"/>
-      <c r="D134" s="182"/>
-      <c r="E134" s="182"/>
+      <c r="D134" s="181"/>
+      <c r="E134" s="181"/>
       <c r="F134" s="102"/>
       <c r="G134" s="102"/>
       <c r="H134" s="102"/>
       <c r="I134" s="102"/>
-      <c r="K134" s="55"/>
+      <c r="K134" s="45"/>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="22" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B135" s="94">
-        <f>-B142</f>
-        <v>0</v>
-      </c>
-      <c r="C135" s="23"/>
+        <f>-D125</f>
+        <v>0</v>
+      </c>
+      <c r="C135" s="19"/>
+      <c r="D135" s="181"/>
+      <c r="E135" s="181"/>
+      <c r="F135" s="102"/>
+      <c r="G135" s="102"/>
+      <c r="H135" s="102"/>
+      <c r="I135" s="102"/>
+      <c r="K135" s="55"/>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B136" s="94">
+        <f>-B143</f>
+        <v>0</v>
+      </c>
+      <c r="C136" s="23"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A137" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="B136" s="94">
-        <f>-C118</f>
+      <c r="B137" s="94">
+        <f>-C119</f>
         <v>-164340</v>
       </c>
-      <c r="C136" s="23"/>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A137" s="22"/>
-      <c r="B137" s="18"/>
       <c r="C137" s="23"/>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A138" s="20" t="s">
+      <c r="A138" s="22"/>
+      <c r="B138" s="18"/>
+      <c r="C138" s="23"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A139" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B138" s="24">
-        <f>SUM(B131:B137)</f>
-        <v>-1480823.9566400023</v>
-      </c>
-      <c r="C138" s="78"/>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A139" s="23"/>
-      <c r="C139" s="19"/>
-      <c r="D139" s="26"/>
+      <c r="B139" s="24">
+        <f>SUM(B132:B138)</f>
+        <v>-2377771.0666400017</v>
+      </c>
+      <c r="C139" s="78"/>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A140" s="23"/>
       <c r="C140" s="19"/>
-      <c r="D140" s="44"/>
-      <c r="E140" s="95"/>
-      <c r="F140" s="95"/>
-      <c r="G140" s="95"/>
-      <c r="H140" s="95"/>
-      <c r="I140" s="95"/>
+      <c r="D140" s="26"/>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A141" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B141" s="9">
-        <v>0</v>
-      </c>
-      <c r="C141" s="25"/>
-      <c r="D141" s="95"/>
+      <c r="C141" s="19"/>
+      <c r="D141" s="44"/>
       <c r="E141" s="95"/>
       <c r="F141" s="95"/>
       <c r="G141" s="95"/>
       <c r="H141" s="95"/>
       <c r="I141" s="95"/>
-      <c r="J141" s="95"/>
-    </row>
-    <row r="142" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="B142" s="32"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A142" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B142" s="9">
+        <v>0</v>
+      </c>
       <c r="C142" s="25"/>
       <c r="D142" s="95"/>
-      <c r="E142" s="103"/>
-      <c r="F142" s="103"/>
-      <c r="G142" s="103"/>
-      <c r="H142" s="103"/>
-      <c r="I142" s="103"/>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A143" s="20"/>
-      <c r="B143" s="94"/>
+      <c r="E142" s="95"/>
+      <c r="F142" s="95"/>
+      <c r="G142" s="95"/>
+      <c r="H142" s="95"/>
+      <c r="I142" s="95"/>
+      <c r="J142" s="95"/>
+    </row>
+    <row r="143" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="B143" s="32"/>
       <c r="C143" s="25"/>
-      <c r="E143" s="44"/>
-      <c r="F143" s="44"/>
-      <c r="G143" s="44"/>
-      <c r="H143" s="44"/>
-      <c r="I143" s="44"/>
+      <c r="D143" s="95"/>
+      <c r="E143" s="103"/>
+      <c r="F143" s="103"/>
+      <c r="G143" s="103"/>
+      <c r="H143" s="103"/>
+      <c r="I143" s="103"/>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A144" s="37" t="s">
+      <c r="A144" s="20"/>
+      <c r="B144" s="94"/>
+      <c r="C144" s="25"/>
+      <c r="E144" s="44"/>
+      <c r="F144" s="44"/>
+      <c r="G144" s="44"/>
+      <c r="H144" s="44"/>
+      <c r="I144" s="44"/>
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A145" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="B144" s="38">
-        <f>SUM(B141:B143)</f>
-        <v>0</v>
-      </c>
-      <c r="C144" s="25"/>
-    </row>
-    <row r="145" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="C145" s="26"/>
-      <c r="D145" s="95"/>
-    </row>
-    <row r="146" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B146" s="23"/>
-      <c r="C146" s="19"/>
-    </row>
-    <row r="148" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="R148" s="10"/>
-    </row>
-    <row r="151" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B151" s="181"/>
-      <c r="C151" s="181"/>
-      <c r="D151" s="181"/>
-      <c r="E151" s="181"/>
-      <c r="F151" s="106"/>
-      <c r="G151" s="106"/>
-      <c r="H151" s="106"/>
-      <c r="I151" s="106"/>
-    </row>
-    <row r="152" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B152" s="181"/>
-      <c r="C152" s="181"/>
-      <c r="D152" s="181"/>
-      <c r="E152" s="181"/>
+      <c r="B145" s="38">
+        <f>SUM(B142:B144)</f>
+        <v>0</v>
+      </c>
+      <c r="C145" s="25"/>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C146" s="26"/>
+      <c r="D146" s="95"/>
+    </row>
+    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B147" s="23"/>
+      <c r="C147" s="19"/>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R149" s="10"/>
+    </row>
+    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B152" s="180"/>
+      <c r="C152" s="180"/>
+      <c r="D152" s="180"/>
+      <c r="E152" s="180"/>
       <c r="F152" s="106"/>
       <c r="G152" s="106"/>
       <c r="H152" s="106"/>
       <c r="I152" s="106"/>
     </row>
-    <row r="153" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B153" s="181"/>
-      <c r="C153" s="181"/>
-      <c r="D153" s="181"/>
-      <c r="E153" s="181"/>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B153" s="180"/>
+      <c r="C153" s="180"/>
+      <c r="D153" s="180"/>
+      <c r="E153" s="180"/>
       <c r="F153" s="106"/>
       <c r="G153" s="106"/>
       <c r="H153" s="106"/>
       <c r="I153" s="106"/>
     </row>
-    <row r="154" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B154" s="181"/>
-      <c r="C154" s="181"/>
-      <c r="D154" s="181"/>
-      <c r="E154" s="181"/>
+    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B154" s="180"/>
+      <c r="C154" s="180"/>
+      <c r="D154" s="180"/>
+      <c r="E154" s="180"/>
       <c r="F154" s="106"/>
       <c r="G154" s="106"/>
       <c r="H154" s="106"/>
       <c r="I154" s="106"/>
     </row>
-    <row r="155" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B155" s="181"/>
-      <c r="C155" s="181"/>
-      <c r="D155" s="181"/>
-      <c r="E155" s="181"/>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B155" s="180"/>
+      <c r="C155" s="180"/>
+      <c r="D155" s="180"/>
+      <c r="E155" s="180"/>
       <c r="F155" s="106"/>
       <c r="G155" s="106"/>
       <c r="H155" s="106"/>
       <c r="I155" s="106"/>
     </row>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B156" s="180"/>
+      <c r="C156" s="180"/>
+      <c r="D156" s="180"/>
+      <c r="E156" s="180"/>
+      <c r="F156" s="106"/>
+      <c r="G156" s="106"/>
+      <c r="H156" s="106"/>
+      <c r="I156" s="106"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A14:J18"/>
-    <mergeCell ref="B151:E155"/>
-    <mergeCell ref="D129:E134"/>
-    <mergeCell ref="A124:C124"/>
-    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="B152:E156"/>
+    <mergeCell ref="D130:E135"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A122:D122"/>
+    <mergeCell ref="A124:B124"/>
     <mergeCell ref="A123:B123"/>
-    <mergeCell ref="A122:B122"/>
     <mergeCell ref="A20:J22"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5322,11 +5334,11 @@
       <c r="K1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="200">
-        <f>RESUMEN!D103-RESUMEN!D101</f>
-        <v>7642586.040000001</v>
-      </c>
-      <c r="M1" s="201"/>
+      <c r="L1" s="195">
+        <f>RESUMEN!D104-RESUMEN!D102</f>
+        <v>8539533.1500000004</v>
+      </c>
+      <c r="M1" s="196"/>
       <c r="N1" s="76"/>
       <c r="O1" s="64"/>
     </row>
@@ -5391,23 +5403,23 @@
       <c r="N4" s="54"/>
       <c r="P4" s="95">
         <f>L1-K127</f>
-        <v>-1240893.8416399993</v>
+        <v>-343946.7316399999</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="191" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="193" t="s">
+      <c r="B5" s="204" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="191" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="195" t="s">
+      <c r="D5" s="206" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="195" t="s">
+      <c r="E5" s="206" t="s">
         <v>279</v>
       </c>
       <c r="F5" s="191" t="s">
@@ -5419,59 +5431,59 @@
       <c r="H5" s="191" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="202" t="s">
+      <c r="I5" s="197" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="204" t="s">
+      <c r="J5" s="199" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="204" t="s">
+      <c r="K5" s="199" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="207" t="s">
+      <c r="L5" s="202" t="s">
         <v>43</v>
       </c>
-      <c r="M5" s="204" t="s">
-        <v>319</v>
-      </c>
-      <c r="N5" s="204" t="s">
-        <v>318</v>
+      <c r="M5" s="199" t="s">
+        <v>314</v>
+      </c>
+      <c r="N5" s="199" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="192"/>
-      <c r="B6" s="194"/>
+      <c r="B6" s="205"/>
       <c r="C6" s="192"/>
-      <c r="D6" s="196"/>
-      <c r="E6" s="196"/>
+      <c r="D6" s="207"/>
+      <c r="E6" s="207"/>
       <c r="F6" s="192"/>
       <c r="G6" s="192"/>
       <c r="H6" s="192"/>
-      <c r="I6" s="203"/>
-      <c r="J6" s="205"/>
-      <c r="K6" s="205"/>
-      <c r="L6" s="208"/>
-      <c r="M6" s="205"/>
-      <c r="N6" s="205"/>
+      <c r="I6" s="198"/>
+      <c r="J6" s="200"/>
+      <c r="K6" s="200"/>
+      <c r="L6" s="203"/>
+      <c r="M6" s="200"/>
+      <c r="N6" s="200"/>
     </row>
     <row r="7" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="192"/>
-      <c r="B7" s="194"/>
+      <c r="B7" s="205"/>
       <c r="C7" s="192"/>
-      <c r="D7" s="196"/>
-      <c r="E7" s="196"/>
+      <c r="D7" s="207"/>
+      <c r="E7" s="207"/>
       <c r="F7" s="192"/>
       <c r="G7" s="192"/>
       <c r="H7" s="192"/>
-      <c r="I7" s="203"/>
-      <c r="J7" s="205"/>
-      <c r="K7" s="206"/>
-      <c r="L7" s="208"/>
-      <c r="M7" s="153" t="str">
+      <c r="I7" s="198"/>
+      <c r="J7" s="200"/>
+      <c r="K7" s="201"/>
+      <c r="L7" s="203"/>
+      <c r="M7" s="152" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 15/09</v>
       </c>
-      <c r="N7" s="152" t="str">
+      <c r="N7" s="151" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 15/09</v>
       </c>
@@ -5491,7 +5503,7 @@
       <c r="F8" s="105">
         <v>1.0800000000000001E-2</v>
       </c>
-      <c r="G8" s="155">
+      <c r="G8" s="154">
         <v>70998.78441600001</v>
       </c>
       <c r="H8" s="99">
@@ -5521,10 +5533,10 @@
         <v>86445.848309040011</v>
       </c>
       <c r="O8" s="133"/>
-      <c r="Q8" s="197" t="s">
+      <c r="Q8" s="190" t="s">
         <v>263</v>
       </c>
-      <c r="R8" s="197"/>
+      <c r="R8" s="190"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -5539,7 +5551,7 @@
       <c r="F9" s="105">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="G9" s="155">
+      <c r="G9" s="154">
         <v>84146.707456000004</v>
       </c>
       <c r="H9" s="99">
@@ -5569,8 +5581,8 @@
         <v>102454.33873664</v>
       </c>
       <c r="O9" s="133"/>
-      <c r="Q9" s="197"/>
-      <c r="R9" s="197"/>
+      <c r="Q9" s="190"/>
+      <c r="R9" s="190"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
@@ -5587,7 +5599,7 @@
       <c r="F10" s="105">
         <v>1.21E-2</v>
       </c>
-      <c r="G10" s="155">
+      <c r="G10" s="154">
         <v>79544.934391999996</v>
       </c>
       <c r="H10" s="99">
@@ -5621,8 +5633,8 @@
         <v>258</v>
       </c>
       <c r="R10">
-        <f>RESUMEN!F103</f>
-        <v>82162.051487999997</v>
+        <f>RESUMEN!F104</f>
+        <v>92486.669292000006</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -5640,7 +5652,7 @@
       <c r="F11" s="105">
         <v>1.49E-2</v>
       </c>
-      <c r="G11" s="155">
+      <c r="G11" s="154">
         <v>97952.026647999999</v>
       </c>
       <c r="H11" s="99">
@@ -5674,8 +5686,8 @@
         <v>259</v>
       </c>
       <c r="R11">
-        <f>RESUMEN!G103</f>
-        <v>97377.246207999997</v>
+        <f>RESUMEN!G104</f>
+        <v>109613.83027199999</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5683,42 +5695,42 @@
         <v>122</v>
       </c>
       <c r="B12" s="6"/>
-      <c r="C12" s="162" t="s">
+      <c r="C12" s="161" t="s">
         <v>120</v>
       </c>
-      <c r="D12" s="169" t="s">
+      <c r="D12" s="168" t="s">
         <v>278</v>
       </c>
-      <c r="E12" s="169"/>
-      <c r="F12" s="163">
+      <c r="E12" s="168"/>
+      <c r="F12" s="162">
         <v>1.7399999999999999E-2</v>
       </c>
-      <c r="G12" s="164">
+      <c r="G12" s="163">
         <v>114386.93044799998</v>
       </c>
-      <c r="H12" s="170">
+      <c r="H12" s="169">
         <f t="shared" si="2"/>
         <v>114386.93044799998</v>
       </c>
-      <c r="I12" s="165">
+      <c r="I12" s="164">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J12" s="166">
-        <v>0</v>
-      </c>
-      <c r="K12" s="166">
+      <c r="J12" s="165">
+        <v>0</v>
+      </c>
+      <c r="K12" s="165">
         <v>131390.440302</v>
       </c>
-      <c r="L12" s="167">
+      <c r="L12" s="166">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M12" s="171">
+      <c r="M12" s="170">
         <f t="shared" si="1"/>
         <v>131390.440302</v>
       </c>
-      <c r="N12" s="168">
+      <c r="N12" s="167">
         <f t="shared" si="4"/>
         <v>139273.86672012002</v>
       </c>
@@ -5727,8 +5739,8 @@
         <v>260</v>
       </c>
       <c r="R12">
-        <f>RESUMEN!H103</f>
-        <v>92051.928055999975</v>
+        <f>RESUMEN!H104</f>
+        <v>103619.32392899999</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -5739,53 +5751,53 @@
       <c r="C13" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="156" t="s">
+      <c r="D13" s="155" t="s">
         <v>181</v>
       </c>
-      <c r="E13" s="156"/>
+      <c r="E13" s="155"/>
       <c r="F13" s="104">
         <v>1.8800000000000001E-2</v>
       </c>
-      <c r="G13" s="157">
+      <c r="G13" s="156">
         <v>134281.01</v>
       </c>
-      <c r="H13" s="176">
+      <c r="H13" s="175">
         <f>G13</f>
         <v>134281.01</v>
       </c>
-      <c r="I13" s="158">
+      <c r="I13" s="157">
         <f>G13-H13</f>
         <v>0</v>
       </c>
-      <c r="J13" s="159">
+      <c r="J13" s="158">
         <f t="shared" ref="J13:J44" si="5">M$4*F13</f>
         <v>0</v>
       </c>
-      <c r="K13" s="159">
+      <c r="K13" s="158">
         <f>M$2*F13</f>
         <v>169200</v>
       </c>
-      <c r="L13" s="160">
+      <c r="L13" s="159">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M13" s="161">
+      <c r="M13" s="160">
         <f>ROUND((K13+J13+I13+L13),0) + O13</f>
         <v>169200.01</v>
       </c>
-      <c r="N13" s="161">
+      <c r="N13" s="160">
         <f>ROUND((M13*6% + M13 ),0) + O13</f>
         <v>179352.01</v>
       </c>
-      <c r="O13" s="154">
+      <c r="O13" s="153">
         <v>0.01</v>
       </c>
       <c r="Q13" t="s">
         <v>261</v>
       </c>
       <c r="R13">
-        <f>RESUMEN!I103</f>
-        <v>113353.200664</v>
+        <f>RESUMEN!I104</f>
+        <v>127597.34930100001</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -5799,11 +5811,11 @@
       <c r="D14" s="125" t="s">
         <v>182</v>
       </c>
-      <c r="E14" s="156"/>
+      <c r="E14" s="155"/>
       <c r="F14" s="104">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="G14" s="155">
+      <c r="G14" s="154">
         <v>59998.02</v>
       </c>
       <c r="H14" s="45">
@@ -5833,7 +5845,7 @@
         <f t="shared" ref="N14:N77" si="7">ROUND((M14*6% + M14 ),0) + O14</f>
         <v>76320.02</v>
       </c>
-      <c r="O14" s="154">
+      <c r="O14" s="153">
         <f>O13+0.01</f>
         <v>0.02</v>
       </c>
@@ -5841,8 +5853,8 @@
         <v>262</v>
       </c>
       <c r="R14">
-        <f>RESUMEN!J103</f>
-        <v>132372.19406399998</v>
+        <f>RESUMEN!J104</f>
+        <v>149006.30052599998</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -5856,11 +5868,11 @@
       <c r="D15" s="125" t="s">
         <v>183</v>
       </c>
-      <c r="E15" s="156"/>
+      <c r="E15" s="155"/>
       <c r="F15" s="104">
         <v>2.01E-2</v>
       </c>
-      <c r="G15" s="155">
+      <c r="G15" s="154">
         <v>143566.03</v>
       </c>
       <c r="H15" s="99">
@@ -5891,7 +5903,7 @@
         <f t="shared" si="7"/>
         <v>191754.03</v>
       </c>
-      <c r="O15" s="154">
+      <c r="O15" s="153">
         <f t="shared" ref="O15:O78" si="9">O14+0.01</f>
         <v>0.03</v>
       </c>
@@ -5907,11 +5919,11 @@
       <c r="D16" s="125" t="s">
         <v>184</v>
       </c>
-      <c r="E16" s="156"/>
+      <c r="E16" s="155"/>
       <c r="F16" s="104">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G16" s="155">
+      <c r="G16" s="154">
         <v>67140.039999999994</v>
       </c>
       <c r="H16" s="45"/>
@@ -5939,7 +5951,7 @@
         <f t="shared" si="7"/>
         <v>160844.04</v>
       </c>
-      <c r="O16" s="154">
+      <c r="O16" s="153">
         <f t="shared" si="9"/>
         <v>0.04</v>
       </c>
@@ -5955,11 +5967,11 @@
       <c r="D17" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E17" s="172"/>
+      <c r="E17" s="171"/>
       <c r="F17" s="104">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G17" s="155">
+      <c r="G17" s="154">
         <v>62141.05</v>
       </c>
       <c r="H17" s="45">
@@ -5989,7 +6001,7 @@
         <f t="shared" si="7"/>
         <v>92538.05</v>
       </c>
-      <c r="O17" s="154">
+      <c r="O17" s="153">
         <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
@@ -6005,13 +6017,13 @@
       <c r="D18" s="62" t="s">
         <v>186</v>
       </c>
-      <c r="E18" s="172" t="s">
+      <c r="E18" s="171" t="s">
         <v>280</v>
       </c>
       <c r="F18" s="104">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G18" s="155">
+      <c r="G18" s="154">
         <v>67855.06</v>
       </c>
       <c r="H18" s="99"/>
@@ -6038,7 +6050,7 @@
         <f t="shared" si="7"/>
         <v>172096.06</v>
       </c>
-      <c r="O18" s="154">
+      <c r="O18" s="153">
         <f t="shared" si="9"/>
         <v>6.0000000000000005E-2</v>
       </c>
@@ -6054,11 +6066,11 @@
       <c r="D19" s="62" t="s">
         <v>186</v>
       </c>
-      <c r="E19" s="172"/>
+      <c r="E19" s="171"/>
       <c r="F19" s="104">
         <v>1.6500000000000001E-2</v>
       </c>
-      <c r="G19" s="155">
+      <c r="G19" s="154">
         <v>117853.07</v>
       </c>
       <c r="H19" s="99"/>
@@ -6086,7 +6098,7 @@
         <f t="shared" si="7"/>
         <v>282334.07</v>
       </c>
-      <c r="O19" s="154">
+      <c r="O19" s="153">
         <f t="shared" si="9"/>
         <v>7.0000000000000007E-2</v>
       </c>
@@ -6102,11 +6114,11 @@
       <c r="D20" s="62" t="s">
         <v>281</v>
       </c>
-      <c r="E20" s="172"/>
+      <c r="E20" s="171"/>
       <c r="F20" s="104">
         <v>7.3000000000000001E-3</v>
       </c>
-      <c r="G20" s="155">
+      <c r="G20" s="154">
         <v>52141.08</v>
       </c>
       <c r="H20" s="45">
@@ -6137,7 +6149,7 @@
         <f t="shared" si="7"/>
         <v>69642.080000000002</v>
       </c>
-      <c r="O20" s="154">
+      <c r="O20" s="153">
         <f t="shared" si="9"/>
         <v>0.08</v>
       </c>
@@ -6153,11 +6165,11 @@
       <c r="D21" s="62" t="s">
         <v>186</v>
       </c>
-      <c r="E21" s="172"/>
+      <c r="E21" s="171"/>
       <c r="F21" s="104">
         <v>1.78E-2</v>
       </c>
-      <c r="G21" s="155">
+      <c r="G21" s="154">
         <v>127138.09</v>
       </c>
       <c r="H21" s="99"/>
@@ -6185,7 +6197,7 @@
         <f t="shared" si="7"/>
         <v>304578.09000000003</v>
       </c>
-      <c r="O21" s="154">
+      <c r="O21" s="153">
         <f t="shared" si="9"/>
         <v>0.09</v>
       </c>
@@ -6201,11 +6213,11 @@
       <c r="D22" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="E22" s="172"/>
+      <c r="E22" s="171"/>
       <c r="F22" s="104">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G22" s="155">
+      <c r="G22" s="154">
         <v>67140.100000000006</v>
       </c>
       <c r="H22" s="99">
@@ -6236,7 +6248,7 @@
         <f t="shared" si="7"/>
         <v>89676.1</v>
       </c>
-      <c r="O22" s="154">
+      <c r="O22" s="153">
         <f t="shared" si="9"/>
         <v>9.9999999999999992E-2</v>
       </c>
@@ -6252,11 +6264,11 @@
       <c r="D23" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="E23" s="172"/>
+      <c r="E23" s="171"/>
       <c r="F23" s="104">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G23" s="155">
+      <c r="G23" s="154">
         <v>62141.11</v>
       </c>
       <c r="H23" s="99">
@@ -6287,7 +6299,7 @@
         <f t="shared" si="7"/>
         <v>82998.11</v>
       </c>
-      <c r="O23" s="154">
+      <c r="O23" s="153">
         <f t="shared" si="9"/>
         <v>0.10999999999999999</v>
       </c>
@@ -6303,11 +6315,11 @@
       <c r="D24" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="E24" s="172"/>
+      <c r="E24" s="171"/>
       <c r="F24" s="104">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G24" s="155">
+      <c r="G24" s="154">
         <v>67855.12</v>
       </c>
       <c r="H24" s="45">
@@ -6338,7 +6350,7 @@
         <f t="shared" si="7"/>
         <v>90630.12</v>
       </c>
-      <c r="O24" s="154">
+      <c r="O24" s="153">
         <f t="shared" si="9"/>
         <v>0.11999999999999998</v>
       </c>
@@ -6354,11 +6366,11 @@
       <c r="D25" s="62" t="s">
         <v>188</v>
       </c>
-      <c r="E25" s="172"/>
+      <c r="E25" s="171"/>
       <c r="F25" s="104">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="G25" s="155">
+      <c r="G25" s="154">
         <v>135139.13</v>
       </c>
       <c r="H25" s="99">
@@ -6389,7 +6401,7 @@
         <f t="shared" si="7"/>
         <v>156456.13</v>
       </c>
-      <c r="O25" s="154">
+      <c r="O25" s="153">
         <f t="shared" si="9"/>
         <v>0.12999999999999998</v>
       </c>
@@ -6405,13 +6417,13 @@
       <c r="D26" s="62" t="s">
         <v>265</v>
       </c>
-      <c r="E26" s="172" t="s">
+      <c r="E26" s="171" t="s">
         <v>282</v>
       </c>
       <c r="F26" s="104">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="G26" s="155">
+      <c r="G26" s="154">
         <v>51427.14</v>
       </c>
       <c r="H26" s="99"/>
@@ -6439,7 +6451,7 @@
         <f t="shared" si="7"/>
         <v>123201.14</v>
       </c>
-      <c r="O26" s="154">
+      <c r="O26" s="153">
         <f t="shared" si="9"/>
         <v>0.13999999999999999</v>
       </c>
@@ -6455,11 +6467,11 @@
       <c r="D27" s="62" t="s">
         <v>189</v>
       </c>
-      <c r="E27" s="172"/>
+      <c r="E27" s="171"/>
       <c r="F27" s="104">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G27" s="155">
+      <c r="G27" s="154">
         <v>150567.15</v>
       </c>
       <c r="H27" s="45">
@@ -6490,7 +6502,7 @@
         <f t="shared" si="7"/>
         <v>165042.15</v>
       </c>
-      <c r="O27" s="154">
+      <c r="O27" s="153">
         <f t="shared" si="9"/>
         <v>0.15</v>
       </c>
@@ -6506,11 +6518,11 @@
       <c r="D28" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="E28" s="172"/>
+      <c r="E28" s="171"/>
       <c r="F28" s="104">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G28" s="155">
+      <c r="G28" s="154">
         <v>67140.160000000003</v>
       </c>
       <c r="H28" s="45">
@@ -6541,7 +6553,7 @@
         <f t="shared" si="7"/>
         <v>89676.160000000003</v>
       </c>
-      <c r="O28" s="154">
+      <c r="O28" s="153">
         <f t="shared" si="9"/>
         <v>0.16</v>
       </c>
@@ -6557,11 +6569,11 @@
       <c r="D29" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="E29" s="172"/>
+      <c r="E29" s="171"/>
       <c r="F29" s="104">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G29" s="155">
+      <c r="G29" s="154">
         <v>62141.17</v>
       </c>
       <c r="H29" s="45">
@@ -6592,7 +6604,7 @@
         <f t="shared" si="7"/>
         <v>82998.17</v>
       </c>
-      <c r="O29" s="154">
+      <c r="O29" s="153">
         <f t="shared" si="9"/>
         <v>0.17</v>
       </c>
@@ -6608,11 +6620,11 @@
       <c r="D30" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="E30" s="172"/>
+      <c r="E30" s="171"/>
       <c r="F30" s="104">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G30" s="155">
+      <c r="G30" s="154">
         <v>67855.179999999993</v>
       </c>
       <c r="H30" s="45">
@@ -6643,7 +6655,7 @@
         <f t="shared" si="7"/>
         <v>90630.18</v>
       </c>
-      <c r="O30" s="154">
+      <c r="O30" s="153">
         <f t="shared" si="9"/>
         <v>0.18000000000000002</v>
       </c>
@@ -6659,11 +6671,11 @@
       <c r="D31" s="62" t="s">
         <v>190</v>
       </c>
-      <c r="E31" s="172"/>
+      <c r="E31" s="171"/>
       <c r="F31" s="104">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="G31" s="155">
+      <c r="G31" s="154">
         <v>117139.19</v>
       </c>
       <c r="H31" s="99">
@@ -6694,7 +6706,7 @@
         <f t="shared" si="7"/>
         <v>156456.19</v>
       </c>
-      <c r="O31" s="154">
+      <c r="O31" s="153">
         <f t="shared" si="9"/>
         <v>0.19000000000000003</v>
       </c>
@@ -6710,11 +6722,11 @@
       <c r="D32" s="62" t="s">
         <v>228</v>
       </c>
-      <c r="E32" s="172"/>
+      <c r="E32" s="171"/>
       <c r="F32" s="104">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="G32" s="155">
+      <c r="G32" s="154">
         <v>51427.199999999997</v>
       </c>
       <c r="H32" s="99">
@@ -6745,7 +6757,7 @@
         <f t="shared" si="7"/>
         <v>68688.2</v>
       </c>
-      <c r="O32" s="154">
+      <c r="O32" s="153">
         <f t="shared" si="9"/>
         <v>0.20000000000000004</v>
       </c>
@@ -6761,11 +6773,11 @@
       <c r="D33" s="62" t="s">
         <v>191</v>
       </c>
-      <c r="E33" s="172"/>
+      <c r="E33" s="171"/>
       <c r="F33" s="104">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G33" s="155">
+      <c r="G33" s="154">
         <v>123567.21</v>
       </c>
       <c r="H33" s="99"/>
@@ -6793,7 +6805,7 @@
         <f t="shared" si="7"/>
         <v>296023.21000000002</v>
       </c>
-      <c r="O33" s="154">
+      <c r="O33" s="153">
         <f t="shared" si="9"/>
         <v>0.21000000000000005</v>
       </c>
@@ -6807,13 +6819,13 @@
         <v>69</v>
       </c>
       <c r="D34" s="62" t="s">
-        <v>320</v>
-      </c>
-      <c r="E34" s="172"/>
+        <v>315</v>
+      </c>
+      <c r="E34" s="171"/>
       <c r="F34" s="104">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G34" s="155">
+      <c r="G34" s="154">
         <v>67140.22</v>
       </c>
       <c r="H34" s="99">
@@ -6844,7 +6856,7 @@
         <f t="shared" si="7"/>
         <v>89676.22</v>
       </c>
-      <c r="O34" s="154">
+      <c r="O34" s="153">
         <f t="shared" si="9"/>
         <v>0.22000000000000006</v>
       </c>
@@ -6860,11 +6872,11 @@
       <c r="D35" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="E35" s="172"/>
+      <c r="E35" s="171"/>
       <c r="F35" s="104">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G35" s="155">
+      <c r="G35" s="154">
         <v>62141.23</v>
       </c>
       <c r="H35" s="99">
@@ -6895,7 +6907,7 @@
         <f t="shared" si="7"/>
         <v>82998.23</v>
       </c>
-      <c r="O35" s="154">
+      <c r="O35" s="153">
         <f t="shared" si="9"/>
         <v>0.23000000000000007</v>
       </c>
@@ -6909,9 +6921,9 @@
         <v>71</v>
       </c>
       <c r="D36" s="62" t="s">
-        <v>320</v>
-      </c>
-      <c r="E36" s="172"/>
+        <v>315</v>
+      </c>
+      <c r="E36" s="171"/>
       <c r="F36" s="104">
         <v>9.4999999999999998E-3</v>
       </c>
@@ -6946,7 +6958,7 @@
         <f t="shared" si="7"/>
         <v>90630.24</v>
       </c>
-      <c r="O36" s="154">
+      <c r="O36" s="153">
         <f t="shared" si="9"/>
         <v>0.24000000000000007</v>
       </c>
@@ -6962,11 +6974,11 @@
       <c r="D37" s="62" t="s">
         <v>192</v>
       </c>
-      <c r="E37" s="172"/>
+      <c r="E37" s="171"/>
       <c r="F37" s="104">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="G37" s="155">
+      <c r="G37" s="154">
         <v>117139.25</v>
       </c>
       <c r="H37" s="99">
@@ -6997,7 +7009,7 @@
         <f t="shared" si="7"/>
         <v>156456.25</v>
       </c>
-      <c r="O37" s="154">
+      <c r="O37" s="153">
         <f t="shared" si="9"/>
         <v>0.25000000000000006</v>
       </c>
@@ -7013,13 +7025,13 @@
       <c r="D38" s="62" t="s">
         <v>193</v>
       </c>
-      <c r="E38" s="172" t="s">
+      <c r="E38" s="171" t="s">
         <v>283</v>
       </c>
       <c r="F38" s="104">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="G38" s="155">
+      <c r="G38" s="154">
         <v>78427.259999999995</v>
       </c>
       <c r="H38" s="99">
@@ -7049,7 +7061,7 @@
         <f t="shared" si="7"/>
         <v>68685.259999999995</v>
       </c>
-      <c r="O38" s="154">
+      <c r="O38" s="153">
         <f t="shared" si="9"/>
         <v>0.26000000000000006</v>
       </c>
@@ -7065,11 +7077,11 @@
       <c r="D39" s="62" t="s">
         <v>194</v>
       </c>
-      <c r="E39" s="172"/>
+      <c r="E39" s="171"/>
       <c r="F39" s="104">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G39" s="155">
+      <c r="G39" s="154">
         <v>123567.27</v>
       </c>
       <c r="H39" s="99">
@@ -7099,7 +7111,7 @@
         <f t="shared" si="7"/>
         <v>184122.27</v>
       </c>
-      <c r="O39" s="154">
+      <c r="O39" s="153">
         <f t="shared" si="9"/>
         <v>0.27000000000000007</v>
       </c>
@@ -7121,11 +7133,11 @@
       <c r="D40" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="E40" s="172"/>
+      <c r="E40" s="171"/>
       <c r="F40" s="104">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G40" s="155">
+      <c r="G40" s="154">
         <v>67140.28</v>
       </c>
       <c r="H40" s="99">
@@ -7156,7 +7168,7 @@
         <f t="shared" si="7"/>
         <v>89676.28</v>
       </c>
-      <c r="O40" s="154">
+      <c r="O40" s="153">
         <f t="shared" si="9"/>
         <v>0.28000000000000008</v>
       </c>
@@ -7175,11 +7187,11 @@
       <c r="D41" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E41" s="172"/>
+      <c r="E41" s="171"/>
       <c r="F41" s="104">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G41" s="155">
+      <c r="G41" s="154">
         <v>62141.29</v>
       </c>
       <c r="H41" s="99">
@@ -7210,7 +7222,7 @@
         <f t="shared" si="7"/>
         <v>82998.289999999994</v>
       </c>
-      <c r="O41" s="154">
+      <c r="O41" s="153">
         <f t="shared" si="9"/>
         <v>0.29000000000000009</v>
       </c>
@@ -7226,11 +7238,11 @@
       <c r="D42" s="62" t="s">
         <v>195</v>
       </c>
-      <c r="E42" s="172"/>
+      <c r="E42" s="171"/>
       <c r="F42" s="104">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G42" s="155">
+      <c r="G42" s="154">
         <v>67855.3</v>
       </c>
       <c r="H42" s="99">
@@ -7261,7 +7273,7 @@
         <f t="shared" si="7"/>
         <v>90630.3</v>
       </c>
-      <c r="O42" s="154">
+      <c r="O42" s="153">
         <f t="shared" si="9"/>
         <v>0.3000000000000001</v>
       </c>
@@ -7277,11 +7289,11 @@
       <c r="D43" s="62" t="s">
         <v>196</v>
       </c>
-      <c r="E43" s="172"/>
+      <c r="E43" s="171"/>
       <c r="F43" s="104">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="G43" s="155">
+      <c r="G43" s="154">
         <v>117139.31</v>
       </c>
       <c r="H43" s="99">
@@ -7311,7 +7323,7 @@
         <f t="shared" si="7"/>
         <v>165996.31</v>
       </c>
-      <c r="O43" s="154">
+      <c r="O43" s="153">
         <f t="shared" si="9"/>
         <v>0.31000000000000011</v>
       </c>
@@ -7327,11 +7339,11 @@
       <c r="D44" s="62" t="s">
         <v>197</v>
       </c>
-      <c r="E44" s="172"/>
+      <c r="E44" s="171"/>
       <c r="F44" s="104">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="G44" s="155">
+      <c r="G44" s="154">
         <v>51427.32</v>
       </c>
       <c r="H44" s="99">
@@ -7362,7 +7374,7 @@
         <f t="shared" si="7"/>
         <v>68688.320000000007</v>
       </c>
-      <c r="O44" s="154">
+      <c r="O44" s="153">
         <f t="shared" si="9"/>
         <v>0.32000000000000012</v>
       </c>
@@ -7379,11 +7391,11 @@
       <c r="D45" s="62" t="s">
         <v>198</v>
       </c>
-      <c r="E45" s="172"/>
+      <c r="E45" s="171"/>
       <c r="F45" s="104">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G45" s="155">
+      <c r="G45" s="154">
         <v>123567.33</v>
       </c>
       <c r="H45" s="99">
@@ -7413,7 +7425,7 @@
         <f t="shared" si="7"/>
         <v>184122.33</v>
       </c>
-      <c r="O45" s="154">
+      <c r="O45" s="153">
         <f t="shared" si="9"/>
         <v>0.33000000000000013</v>
       </c>
@@ -7430,11 +7442,11 @@
       <c r="D46" s="62" t="s">
         <v>199</v>
       </c>
-      <c r="E46" s="172"/>
+      <c r="E46" s="171"/>
       <c r="F46" s="104">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G46" s="155">
+      <c r="G46" s="154">
         <v>67140.34</v>
       </c>
       <c r="H46" s="99">
@@ -7465,7 +7477,7 @@
         <f t="shared" si="7"/>
         <v>89676.34</v>
       </c>
-      <c r="O46" s="154">
+      <c r="O46" s="153">
         <f t="shared" si="9"/>
         <v>0.34000000000000014</v>
       </c>
@@ -7481,11 +7493,11 @@
       <c r="D47" s="62" t="s">
         <v>229</v>
       </c>
-      <c r="E47" s="172"/>
+      <c r="E47" s="171"/>
       <c r="F47" s="104">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G47" s="155">
+      <c r="G47" s="154">
         <v>62141.35</v>
       </c>
       <c r="H47" s="99">
@@ -7516,7 +7528,7 @@
         <f t="shared" si="7"/>
         <v>82998.350000000006</v>
       </c>
-      <c r="O47" s="154">
+      <c r="O47" s="153">
         <f t="shared" si="9"/>
         <v>0.35000000000000014</v>
       </c>
@@ -7532,11 +7544,11 @@
       <c r="D48" s="62" t="s">
         <v>200</v>
       </c>
-      <c r="E48" s="172"/>
+      <c r="E48" s="171"/>
       <c r="F48" s="104">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G48" s="155">
+      <c r="G48" s="154">
         <v>67855.360000000001</v>
       </c>
       <c r="H48" s="99"/>
@@ -7564,7 +7576,7 @@
         <f t="shared" si="7"/>
         <v>162557.35999999999</v>
       </c>
-      <c r="O48" s="154">
+      <c r="O48" s="153">
         <f t="shared" si="9"/>
         <v>0.36000000000000015</v>
       </c>
@@ -7580,11 +7592,11 @@
       <c r="D49" s="62" t="s">
         <v>196</v>
       </c>
-      <c r="E49" s="172"/>
+      <c r="E49" s="171"/>
       <c r="F49" s="104">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="G49" s="155">
+      <c r="G49" s="154">
         <v>117139.37</v>
       </c>
       <c r="H49" s="99">
@@ -7615,7 +7627,7 @@
         <f t="shared" si="7"/>
         <v>156456.37</v>
       </c>
-      <c r="O49" s="154">
+      <c r="O49" s="153">
         <f t="shared" si="9"/>
         <v>0.37000000000000016</v>
       </c>
@@ -7632,13 +7644,13 @@
       <c r="D50" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="E50" s="172" t="s">
+      <c r="E50" s="171" t="s">
         <v>284</v>
       </c>
       <c r="F50" s="104">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="G50" s="155">
+      <c r="G50" s="154">
         <v>51427.38</v>
       </c>
       <c r="H50" s="99">
@@ -7668,7 +7680,7 @@
         <f t="shared" si="7"/>
         <v>65417.38</v>
       </c>
-      <c r="O50" s="154">
+      <c r="O50" s="153">
         <f t="shared" si="9"/>
         <v>0.38000000000000017</v>
       </c>
@@ -7684,11 +7696,11 @@
       <c r="D51" s="62" t="s">
         <v>202</v>
       </c>
-      <c r="E51" s="172"/>
+      <c r="E51" s="171"/>
       <c r="F51" s="104">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G51" s="155">
+      <c r="G51" s="154">
         <v>123567.39</v>
       </c>
       <c r="H51" s="99">
@@ -7719,7 +7731,7 @@
         <f t="shared" si="7"/>
         <v>165042.39000000001</v>
       </c>
-      <c r="O51" s="154">
+      <c r="O51" s="153">
         <f t="shared" si="9"/>
         <v>0.39000000000000018</v>
       </c>
@@ -7735,11 +7747,11 @@
       <c r="D52" s="62" t="s">
         <v>203</v>
       </c>
-      <c r="E52" s="172"/>
+      <c r="E52" s="171"/>
       <c r="F52" s="104">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G52" s="155">
+      <c r="G52" s="154">
         <v>67140.399999999994</v>
       </c>
       <c r="H52" s="99"/>
@@ -7767,7 +7779,7 @@
         <f t="shared" si="7"/>
         <v>160845.4</v>
       </c>
-      <c r="O52" s="154">
+      <c r="O52" s="153">
         <f t="shared" si="9"/>
         <v>0.40000000000000019</v>
       </c>
@@ -7783,11 +7795,11 @@
       <c r="D53" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="E53" s="172"/>
+      <c r="E53" s="171"/>
       <c r="F53" s="104">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G53" s="155">
+      <c r="G53" s="154">
         <v>62141.41</v>
       </c>
       <c r="H53" s="99">
@@ -7818,7 +7830,7 @@
         <f t="shared" si="7"/>
         <v>82998.41</v>
       </c>
-      <c r="O53" s="154">
+      <c r="O53" s="153">
         <f t="shared" si="9"/>
         <v>0.4100000000000002</v>
       </c>
@@ -7834,14 +7846,14 @@
       <c r="C54" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D54" s="178" t="s">
+      <c r="D54" s="177" t="s">
         <v>204</v>
       </c>
-      <c r="E54" s="172"/>
+      <c r="E54" s="171"/>
       <c r="F54" s="104">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G54" s="155">
+      <c r="G54" s="154">
         <v>67855.42</v>
       </c>
       <c r="H54" s="45"/>
@@ -7869,12 +7881,12 @@
         <f t="shared" si="7"/>
         <v>162557.42000000001</v>
       </c>
-      <c r="O54" s="154">
+      <c r="O54" s="153">
         <f t="shared" si="9"/>
         <v>0.42000000000000021</v>
       </c>
       <c r="P54" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.3">
@@ -7888,11 +7900,11 @@
       <c r="D55" s="62" t="s">
         <v>205</v>
       </c>
-      <c r="E55" s="172"/>
+      <c r="E55" s="171"/>
       <c r="F55" s="104">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="G55" s="155">
+      <c r="G55" s="154">
         <v>117139.43</v>
       </c>
       <c r="H55" s="99">
@@ -7922,7 +7934,7 @@
         <f t="shared" si="7"/>
         <v>175536.43</v>
       </c>
-      <c r="O55" s="154">
+      <c r="O55" s="153">
         <f t="shared" si="9"/>
         <v>0.43000000000000022</v>
       </c>
@@ -7938,11 +7950,11 @@
       <c r="D56" s="62" t="s">
         <v>205</v>
       </c>
-      <c r="E56" s="172"/>
+      <c r="E56" s="171"/>
       <c r="F56" s="104">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="G56" s="155">
+      <c r="G56" s="154">
         <v>51427.44</v>
       </c>
       <c r="H56" s="99">
@@ -7973,7 +7985,7 @@
         <f t="shared" si="7"/>
         <v>68688.44</v>
       </c>
-      <c r="O56" s="154">
+      <c r="O56" s="153">
         <f t="shared" si="9"/>
         <v>0.44000000000000022</v>
       </c>
@@ -7989,11 +8001,11 @@
       <c r="D57" s="62" t="s">
         <v>206</v>
       </c>
-      <c r="E57" s="172"/>
+      <c r="E57" s="171"/>
       <c r="F57" s="104">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G57" s="155">
+      <c r="G57" s="154">
         <v>123567.45</v>
       </c>
       <c r="H57" s="99">
@@ -8024,7 +8036,7 @@
         <f t="shared" si="7"/>
         <v>165042.45000000001</v>
       </c>
-      <c r="O57" s="154">
+      <c r="O57" s="153">
         <f t="shared" si="9"/>
         <v>0.45000000000000023</v>
       </c>
@@ -8040,13 +8052,13 @@
       <c r="D58" s="62" t="s">
         <v>207</v>
       </c>
-      <c r="E58" s="172" t="s">
+      <c r="E58" s="171" t="s">
         <v>285</v>
       </c>
       <c r="F58" s="104">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G58" s="155">
+      <c r="G58" s="154">
         <v>67140.460000000006</v>
       </c>
       <c r="H58" s="99"/>
@@ -8074,7 +8086,7 @@
         <f t="shared" si="7"/>
         <v>160845.46</v>
       </c>
-      <c r="O58" s="154">
+      <c r="O58" s="153">
         <f t="shared" si="9"/>
         <v>0.46000000000000024</v>
       </c>
@@ -8090,11 +8102,11 @@
       <c r="D59" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E59" s="172"/>
+      <c r="E59" s="171"/>
       <c r="F59" s="104">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G59" s="155">
+      <c r="G59" s="154">
         <v>62141.47</v>
       </c>
       <c r="H59" s="99">
@@ -8124,7 +8136,7 @@
         <f t="shared" si="7"/>
         <v>79046.47</v>
       </c>
-      <c r="O59" s="154">
+      <c r="O59" s="153">
         <f t="shared" si="9"/>
         <v>0.47000000000000025</v>
       </c>
@@ -8140,11 +8152,11 @@
       <c r="D60" s="62" t="s">
         <v>208</v>
       </c>
-      <c r="E60" s="172"/>
+      <c r="E60" s="171"/>
       <c r="F60" s="104">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G60" s="155">
+      <c r="G60" s="154">
         <v>67855.48</v>
       </c>
       <c r="H60" s="99">
@@ -8174,7 +8186,7 @@
         <f t="shared" si="7"/>
         <v>86314.48</v>
       </c>
-      <c r="O60" s="154">
+      <c r="O60" s="153">
         <f t="shared" si="9"/>
         <v>0.48000000000000026</v>
       </c>
@@ -8190,11 +8202,11 @@
       <c r="D61" s="62" t="s">
         <v>209</v>
       </c>
-      <c r="E61" s="172"/>
+      <c r="E61" s="171"/>
       <c r="F61" s="104">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="G61" s="155">
+      <c r="G61" s="154">
         <v>117139.49</v>
       </c>
       <c r="H61" s="99">
@@ -8225,7 +8237,7 @@
         <f t="shared" si="7"/>
         <v>156457.49</v>
       </c>
-      <c r="O61" s="154">
+      <c r="O61" s="153">
         <f t="shared" si="9"/>
         <v>0.49000000000000027</v>
       </c>
@@ -8241,11 +8253,11 @@
       <c r="D62" s="62" t="s">
         <v>210</v>
       </c>
-      <c r="E62" s="172"/>
+      <c r="E62" s="171"/>
       <c r="F62" s="104">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="G62" s="155">
+      <c r="G62" s="154">
         <v>51427.5</v>
       </c>
       <c r="H62" s="99"/>
@@ -8273,7 +8285,7 @@
         <f t="shared" si="7"/>
         <v>123202.5</v>
       </c>
-      <c r="O62" s="154">
+      <c r="O62" s="153">
         <f t="shared" si="9"/>
         <v>0.50000000000000022</v>
       </c>
@@ -8289,11 +8301,11 @@
       <c r="D63" s="62" t="s">
         <v>211</v>
       </c>
-      <c r="E63" s="172"/>
+      <c r="E63" s="171"/>
       <c r="F63" s="104">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G63" s="155">
+      <c r="G63" s="154">
         <v>123567.51</v>
       </c>
       <c r="H63" s="99">
@@ -8324,7 +8336,7 @@
         <f t="shared" si="7"/>
         <v>165043.51</v>
       </c>
-      <c r="O63" s="154">
+      <c r="O63" s="153">
         <f t="shared" si="9"/>
         <v>0.51000000000000023</v>
       </c>
@@ -8340,11 +8352,11 @@
       <c r="D64" s="62" t="s">
         <v>212</v>
       </c>
-      <c r="E64" s="172"/>
+      <c r="E64" s="171"/>
       <c r="F64" s="104">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G64" s="155">
+      <c r="G64" s="154">
         <v>67140.52</v>
       </c>
       <c r="H64" s="99"/>
@@ -8372,7 +8384,7 @@
         <f t="shared" si="7"/>
         <v>160846.51999999999</v>
       </c>
-      <c r="O64" s="154">
+      <c r="O64" s="153">
         <f t="shared" si="9"/>
         <v>0.52000000000000024</v>
       </c>
@@ -8388,11 +8400,11 @@
       <c r="D65" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="E65" s="172"/>
+      <c r="E65" s="171"/>
       <c r="F65" s="104">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G65" s="155">
+      <c r="G65" s="154">
         <v>62141.53</v>
       </c>
       <c r="H65" s="99">
@@ -8423,7 +8435,7 @@
         <f t="shared" si="7"/>
         <v>82999.53</v>
       </c>
-      <c r="O65" s="154">
+      <c r="O65" s="153">
         <f t="shared" si="9"/>
         <v>0.53000000000000025</v>
       </c>
@@ -8442,11 +8454,11 @@
       <c r="D66" s="62" t="s">
         <v>213</v>
       </c>
-      <c r="E66" s="172"/>
+      <c r="E66" s="171"/>
       <c r="F66" s="104">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G66" s="155">
+      <c r="G66" s="154">
         <v>67855.539999999994</v>
       </c>
       <c r="H66" s="99">
@@ -8477,7 +8489,7 @@
         <f t="shared" si="7"/>
         <v>90631.54</v>
       </c>
-      <c r="O66" s="154">
+      <c r="O66" s="153">
         <f t="shared" si="9"/>
         <v>0.54000000000000026</v>
       </c>
@@ -8493,11 +8505,11 @@
       <c r="D67" s="62" t="s">
         <v>214</v>
       </c>
-      <c r="E67" s="172"/>
+      <c r="E67" s="171"/>
       <c r="F67" s="104">
         <v>2.35E-2</v>
       </c>
-      <c r="G67" s="155">
+      <c r="G67" s="154">
         <v>167851.55</v>
       </c>
       <c r="H67" s="99">
@@ -8527,7 +8539,7 @@
         <f t="shared" si="7"/>
         <v>213514.55</v>
       </c>
-      <c r="O67" s="154">
+      <c r="O67" s="153">
         <f t="shared" si="9"/>
         <v>0.55000000000000027</v>
       </c>
@@ -8543,11 +8555,11 @@
       <c r="D68" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="E68" s="172"/>
+      <c r="E68" s="171"/>
       <c r="F68" s="104">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G68" s="155">
+      <c r="G68" s="154">
         <v>123567.56</v>
       </c>
       <c r="H68" s="99">
@@ -8578,7 +8590,7 @@
         <f t="shared" si="7"/>
         <v>165043.56</v>
       </c>
-      <c r="O68" s="154">
+      <c r="O68" s="153">
         <f t="shared" si="9"/>
         <v>0.56000000000000028</v>
       </c>
@@ -8594,11 +8606,11 @@
       <c r="D69" s="62" t="s">
         <v>216</v>
       </c>
-      <c r="E69" s="172"/>
+      <c r="E69" s="171"/>
       <c r="F69" s="104">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G69" s="155">
+      <c r="G69" s="154">
         <v>67140.570000000007</v>
       </c>
       <c r="H69" s="99"/>
@@ -8626,7 +8638,7 @@
         <f t="shared" si="7"/>
         <v>160846.57</v>
       </c>
-      <c r="O69" s="154">
+      <c r="O69" s="153">
         <f t="shared" si="9"/>
         <v>0.57000000000000028</v>
       </c>
@@ -8642,11 +8654,11 @@
       <c r="D70" s="62" t="s">
         <v>217</v>
       </c>
-      <c r="E70" s="172"/>
+      <c r="E70" s="171"/>
       <c r="F70" s="104">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G70" s="155">
+      <c r="G70" s="154">
         <v>62141.58</v>
       </c>
       <c r="H70" s="99"/>
@@ -8674,7 +8686,7 @@
         <f t="shared" si="7"/>
         <v>148869.57999999999</v>
       </c>
-      <c r="O70" s="154">
+      <c r="O70" s="153">
         <f t="shared" si="9"/>
         <v>0.58000000000000029</v>
       </c>
@@ -8690,11 +8702,11 @@
       <c r="D71" s="62" t="s">
         <v>218</v>
       </c>
-      <c r="E71" s="172"/>
+      <c r="E71" s="171"/>
       <c r="F71" s="104">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G71" s="155">
+      <c r="G71" s="154">
         <v>67855.59</v>
       </c>
       <c r="H71" s="99">
@@ -8724,7 +8736,7 @@
         <f t="shared" si="7"/>
         <v>86314.59</v>
       </c>
-      <c r="O71" s="154">
+      <c r="O71" s="153">
         <f t="shared" si="9"/>
         <v>0.5900000000000003</v>
       </c>
@@ -8740,11 +8752,11 @@
       <c r="D72" s="62" t="s">
         <v>219</v>
       </c>
-      <c r="E72" s="172"/>
+      <c r="E72" s="171"/>
       <c r="F72" s="104">
         <v>2.35E-2</v>
       </c>
-      <c r="G72" s="155">
+      <c r="G72" s="154">
         <v>167851.6</v>
       </c>
       <c r="H72" s="99">
@@ -8775,7 +8787,7 @@
         <f t="shared" si="7"/>
         <v>224191.6</v>
       </c>
-      <c r="O72" s="154">
+      <c r="O72" s="153">
         <f t="shared" si="9"/>
         <v>0.60000000000000031</v>
       </c>
@@ -8791,11 +8803,11 @@
       <c r="D73" s="62" t="s">
         <v>220</v>
       </c>
-      <c r="E73" s="172"/>
+      <c r="E73" s="171"/>
       <c r="F73" s="104">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G73" s="155">
+      <c r="G73" s="154">
         <v>123567.61</v>
       </c>
       <c r="H73" s="99">
@@ -8826,7 +8838,7 @@
         <f t="shared" si="7"/>
         <v>165043.60999999999</v>
       </c>
-      <c r="O73" s="154">
+      <c r="O73" s="153">
         <f t="shared" si="9"/>
         <v>0.61000000000000032</v>
       </c>
@@ -8842,11 +8854,11 @@
       <c r="D74" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="E74" s="172"/>
+      <c r="E74" s="171"/>
       <c r="F74" s="104">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G74" s="155">
+      <c r="G74" s="154">
         <v>67140.62</v>
       </c>
       <c r="H74" s="99">
@@ -8877,7 +8889,7 @@
         <f t="shared" si="7"/>
         <v>89677.62</v>
       </c>
-      <c r="O74" s="154">
+      <c r="O74" s="153">
         <f t="shared" si="9"/>
         <v>0.62000000000000033</v>
       </c>
@@ -8893,13 +8905,13 @@
       <c r="D75" s="62" t="s">
         <v>222</v>
       </c>
-      <c r="E75" s="172" t="s">
+      <c r="E75" s="171" t="s">
         <v>286</v>
       </c>
       <c r="F75" s="104">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G75" s="155">
+      <c r="G75" s="154">
         <v>62141.63</v>
       </c>
       <c r="H75" s="99">
@@ -8930,7 +8942,7 @@
         <f t="shared" si="7"/>
         <v>82999.63</v>
       </c>
-      <c r="O75" s="154">
+      <c r="O75" s="153">
         <f t="shared" si="9"/>
         <v>0.63000000000000034</v>
       </c>
@@ -8946,11 +8958,11 @@
       <c r="D76" s="62" t="s">
         <v>223</v>
       </c>
-      <c r="E76" s="172"/>
+      <c r="E76" s="171"/>
       <c r="F76" s="104">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G76" s="155">
+      <c r="G76" s="154">
         <v>76855.64</v>
       </c>
       <c r="H76" s="99">
@@ -8980,12 +8992,12 @@
         <f t="shared" si="7"/>
         <v>85742.64</v>
       </c>
-      <c r="O76" s="154">
+      <c r="O76" s="153">
         <f t="shared" si="9"/>
         <v>0.64000000000000035</v>
       </c>
       <c r="P76" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.3">
@@ -8999,11 +9011,11 @@
       <c r="D77" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="E77" s="172"/>
+      <c r="E77" s="171"/>
       <c r="F77" s="104">
         <v>2.35E-2</v>
       </c>
-      <c r="G77" s="155">
+      <c r="G77" s="154">
         <v>167851.65</v>
       </c>
       <c r="H77" s="99">
@@ -9033,7 +9045,7 @@
         <f t="shared" si="7"/>
         <v>315758.65000000002</v>
       </c>
-      <c r="O77" s="154">
+      <c r="O77" s="153">
         <f t="shared" si="9"/>
         <v>0.65000000000000036</v>
       </c>
@@ -9049,11 +9061,11 @@
       <c r="D78" s="62" t="s">
         <v>224</v>
       </c>
-      <c r="E78" s="172"/>
+      <c r="E78" s="171"/>
       <c r="F78" s="104">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G78" s="155">
+      <c r="G78" s="154">
         <v>123567.66</v>
       </c>
       <c r="H78" s="99">
@@ -9084,7 +9096,7 @@
         <f t="shared" ref="N78:N125" si="20">ROUND((M78*6% + M78 ),0) + O78</f>
         <v>165043.66</v>
       </c>
-      <c r="O78" s="154">
+      <c r="O78" s="153">
         <f t="shared" si="9"/>
         <v>0.66000000000000036</v>
       </c>
@@ -9100,11 +9112,11 @@
       <c r="D79" s="62" t="s">
         <v>225</v>
       </c>
-      <c r="E79" s="172"/>
+      <c r="E79" s="171"/>
       <c r="F79" s="104">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G79" s="155">
+      <c r="G79" s="154">
         <v>67140.67</v>
       </c>
       <c r="H79" s="99">
@@ -9134,7 +9146,7 @@
         <f t="shared" si="20"/>
         <v>99217.67</v>
       </c>
-      <c r="O79" s="154">
+      <c r="O79" s="153">
         <f t="shared" ref="O79:O125" si="21">O78+0.01</f>
         <v>0.67000000000000037</v>
       </c>
@@ -9150,11 +9162,11 @@
       <c r="D80" s="62" t="s">
         <v>226</v>
       </c>
-      <c r="E80" s="172"/>
+      <c r="E80" s="171"/>
       <c r="F80" s="104">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G80" s="155">
+      <c r="G80" s="154">
         <v>62141.68</v>
       </c>
       <c r="H80" s="99">
@@ -9184,7 +9196,7 @@
         <f t="shared" si="20"/>
         <v>92539.68</v>
       </c>
-      <c r="O80" s="154">
+      <c r="O80" s="153">
         <f t="shared" si="21"/>
         <v>0.68000000000000038</v>
       </c>
@@ -9200,11 +9212,11 @@
       <c r="D81" s="125" t="s">
         <v>227</v>
       </c>
-      <c r="E81" s="156"/>
+      <c r="E81" s="155"/>
       <c r="F81" s="104">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G81" s="155">
+      <c r="G81" s="154">
         <v>67855.69</v>
       </c>
       <c r="H81" s="99">
@@ -9234,7 +9246,7 @@
         <f t="shared" si="20"/>
         <v>136804.69</v>
       </c>
-      <c r="O81" s="154">
+      <c r="O81" s="153">
         <f t="shared" si="21"/>
         <v>0.69000000000000039</v>
       </c>
@@ -9252,7 +9264,7 @@
       <c r="F82" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G82" s="155">
+      <c r="G82" s="154">
         <v>16428.7</v>
       </c>
       <c r="H82" s="99">
@@ -9283,7 +9295,7 @@
         <f t="shared" si="20"/>
         <v>21943.7</v>
       </c>
-      <c r="O82" s="154">
+      <c r="O82" s="153">
         <f t="shared" si="21"/>
         <v>0.7000000000000004</v>
       </c>
@@ -9301,7 +9313,7 @@
       <c r="F83" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G83" s="155">
+      <c r="G83" s="154">
         <v>16428.71</v>
       </c>
       <c r="H83" s="99">
@@ -9332,7 +9344,7 @@
         <f t="shared" si="20"/>
         <v>21943.71</v>
       </c>
-      <c r="O83" s="154">
+      <c r="O83" s="153">
         <f t="shared" si="21"/>
         <v>0.71000000000000041</v>
       </c>
@@ -9350,7 +9362,7 @@
       <c r="F84" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G84" s="155">
+      <c r="G84" s="154">
         <v>16428.72</v>
       </c>
       <c r="H84" s="99">
@@ -9381,7 +9393,7 @@
         <f t="shared" si="20"/>
         <v>21943.72</v>
       </c>
-      <c r="O84" s="154">
+      <c r="O84" s="153">
         <f t="shared" si="21"/>
         <v>0.72000000000000042</v>
       </c>
@@ -9399,7 +9411,7 @@
       <c r="F85" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G85" s="155">
+      <c r="G85" s="154">
         <v>16428.73</v>
       </c>
       <c r="H85" s="99">
@@ -9430,7 +9442,7 @@
         <f t="shared" si="20"/>
         <v>21943.73</v>
       </c>
-      <c r="O85" s="154">
+      <c r="O85" s="153">
         <f t="shared" si="21"/>
         <v>0.73000000000000043</v>
       </c>
@@ -9448,7 +9460,7 @@
       <c r="F86" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G86" s="155">
+      <c r="G86" s="154">
         <v>16428.740000000002</v>
       </c>
       <c r="H86" s="99">
@@ -9479,12 +9491,12 @@
         <f t="shared" si="20"/>
         <v>21943.74</v>
       </c>
-      <c r="O86" s="154">
+      <c r="O86" s="153">
         <f t="shared" si="21"/>
         <v>0.74000000000000044</v>
       </c>
       <c r="P86" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
@@ -9500,7 +9512,7 @@
       <c r="F87" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G87" s="155">
+      <c r="G87" s="154">
         <v>16428.75</v>
       </c>
       <c r="H87" s="99"/>
@@ -9528,7 +9540,7 @@
         <f t="shared" si="20"/>
         <v>39358.75</v>
       </c>
-      <c r="O87" s="154">
+      <c r="O87" s="153">
         <f t="shared" si="21"/>
         <v>0.75000000000000044</v>
       </c>
@@ -9546,7 +9558,7 @@
       <c r="F88" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G88" s="155">
+      <c r="G88" s="154">
         <v>16428.759999999998</v>
       </c>
       <c r="H88" s="99">
@@ -9577,7 +9589,7 @@
         <f t="shared" si="20"/>
         <v>21943.759999999998</v>
       </c>
-      <c r="O88" s="154">
+      <c r="O88" s="153">
         <f t="shared" si="21"/>
         <v>0.76000000000000045</v>
       </c>
@@ -9595,7 +9607,7 @@
       <c r="F89" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G89" s="155">
+      <c r="G89" s="154">
         <v>16428.77</v>
       </c>
       <c r="H89" s="99">
@@ -9626,7 +9638,7 @@
         <f t="shared" si="20"/>
         <v>21943.77</v>
       </c>
-      <c r="O89" s="154">
+      <c r="O89" s="153">
         <f t="shared" si="21"/>
         <v>0.77000000000000046</v>
       </c>
@@ -9644,7 +9656,7 @@
       <c r="F90" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G90" s="155">
+      <c r="G90" s="154">
         <v>16428.78</v>
       </c>
       <c r="H90" s="99"/>
@@ -9672,7 +9684,7 @@
         <f t="shared" si="20"/>
         <v>39358.78</v>
       </c>
-      <c r="O90" s="154">
+      <c r="O90" s="153">
         <f t="shared" si="21"/>
         <v>0.78000000000000047</v>
       </c>
@@ -9690,7 +9702,7 @@
       <c r="F91" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G91" s="155">
+      <c r="G91" s="154">
         <v>16428.79</v>
       </c>
       <c r="H91" s="99"/>
@@ -9718,7 +9730,7 @@
         <f t="shared" si="20"/>
         <v>39358.79</v>
       </c>
-      <c r="O91" s="154">
+      <c r="O91" s="153">
         <f t="shared" si="21"/>
         <v>0.79000000000000048</v>
       </c>
@@ -9736,7 +9748,7 @@
       <c r="F92" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G92" s="155">
+      <c r="G92" s="154">
         <v>16428.8</v>
       </c>
       <c r="H92" s="99">
@@ -9767,7 +9779,7 @@
         <f t="shared" si="20"/>
         <v>21943.8</v>
       </c>
-      <c r="O92" s="154">
+      <c r="O92" s="153">
         <f t="shared" si="21"/>
         <v>0.80000000000000049</v>
       </c>
@@ -9785,7 +9797,7 @@
       <c r="F93" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G93" s="155">
+      <c r="G93" s="154">
         <v>16428.810000000001</v>
       </c>
       <c r="H93" s="99">
@@ -9816,7 +9828,7 @@
         <f t="shared" si="20"/>
         <v>21943.81</v>
       </c>
-      <c r="O93" s="154">
+      <c r="O93" s="153">
         <f t="shared" si="21"/>
         <v>0.8100000000000005</v>
       </c>
@@ -9834,7 +9846,7 @@
       <c r="F94" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G94" s="155">
+      <c r="G94" s="154">
         <v>16428.82</v>
       </c>
       <c r="H94" s="99">
@@ -9865,7 +9877,7 @@
         <f t="shared" si="20"/>
         <v>21943.82</v>
       </c>
-      <c r="O94" s="154">
+      <c r="O94" s="153">
         <f t="shared" si="21"/>
         <v>0.82000000000000051</v>
       </c>
@@ -9883,7 +9895,7 @@
       <c r="F95" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G95" s="155">
+      <c r="G95" s="154">
         <v>16428.830000000002</v>
       </c>
       <c r="H95" s="99">
@@ -9914,7 +9926,7 @@
         <f t="shared" si="20"/>
         <v>21943.83</v>
       </c>
-      <c r="O95" s="154">
+      <c r="O95" s="153">
         <f t="shared" si="21"/>
         <v>0.83000000000000052</v>
       </c>
@@ -9932,7 +9944,7 @@
       <c r="F96" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G96" s="155">
+      <c r="G96" s="154">
         <v>16428.84</v>
       </c>
       <c r="H96" s="99">
@@ -9963,7 +9975,7 @@
         <f t="shared" si="20"/>
         <v>21943.84</v>
       </c>
-      <c r="O96" s="154">
+      <c r="O96" s="153">
         <f t="shared" si="21"/>
         <v>0.84000000000000052</v>
       </c>
@@ -9981,7 +9993,7 @@
       <c r="F97" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G97" s="155">
+      <c r="G97" s="154">
         <v>16428.849999999999</v>
       </c>
       <c r="H97" s="99">
@@ -10012,7 +10024,7 @@
         <f t="shared" si="20"/>
         <v>21943.85</v>
       </c>
-      <c r="O97" s="154">
+      <c r="O97" s="153">
         <f t="shared" si="21"/>
         <v>0.85000000000000053</v>
       </c>
@@ -10030,7 +10042,7 @@
       <c r="F98" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G98" s="155">
+      <c r="G98" s="154">
         <v>16428.86</v>
       </c>
       <c r="H98" s="99">
@@ -10061,7 +10073,7 @@
         <f t="shared" si="20"/>
         <v>21943.86</v>
       </c>
-      <c r="O98" s="154">
+      <c r="O98" s="153">
         <f t="shared" si="21"/>
         <v>0.86000000000000054</v>
       </c>
@@ -10079,7 +10091,7 @@
       <c r="F99" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G99" s="155">
+      <c r="G99" s="154">
         <v>16428.87</v>
       </c>
       <c r="H99" s="99"/>
@@ -10107,7 +10119,7 @@
         <f t="shared" si="20"/>
         <v>39358.870000000003</v>
       </c>
-      <c r="O99" s="154">
+      <c r="O99" s="153">
         <f t="shared" si="21"/>
         <v>0.87000000000000055</v>
       </c>
@@ -10125,7 +10137,7 @@
       <c r="F100" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G100" s="155">
+      <c r="G100" s="154">
         <v>16428.88</v>
       </c>
       <c r="H100" s="99"/>
@@ -10153,7 +10165,7 @@
         <f t="shared" si="20"/>
         <v>39358.879999999997</v>
       </c>
-      <c r="O100" s="154">
+      <c r="O100" s="153">
         <f t="shared" si="21"/>
         <v>0.88000000000000056</v>
       </c>
@@ -10171,7 +10183,7 @@
       <c r="F101" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G101" s="155">
+      <c r="G101" s="154">
         <v>16428.89</v>
       </c>
       <c r="H101" s="99">
@@ -10201,7 +10213,7 @@
         <f t="shared" si="20"/>
         <v>20897.89</v>
       </c>
-      <c r="O101" s="154">
+      <c r="O101" s="153">
         <f t="shared" si="21"/>
         <v>0.89000000000000057</v>
       </c>
@@ -10219,7 +10231,7 @@
       <c r="F102" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G102" s="155">
+      <c r="G102" s="154">
         <v>16428.900000000001</v>
       </c>
       <c r="H102" s="99">
@@ -10249,7 +10261,7 @@
         <f t="shared" si="20"/>
         <v>20897.900000000001</v>
       </c>
-      <c r="O102" s="154">
+      <c r="O102" s="153">
         <f t="shared" si="21"/>
         <v>0.90000000000000058</v>
       </c>
@@ -10267,7 +10279,7 @@
       <c r="F103" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G103" s="155">
+      <c r="G103" s="154">
         <v>16428.91</v>
       </c>
       <c r="H103" s="99">
@@ -10298,7 +10310,7 @@
         <f t="shared" si="20"/>
         <v>21943.91</v>
       </c>
-      <c r="O103" s="154">
+      <c r="O103" s="153">
         <f t="shared" si="21"/>
         <v>0.91000000000000059</v>
       </c>
@@ -10316,7 +10328,7 @@
       <c r="F104" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G104" s="155">
+      <c r="G104" s="154">
         <v>16428.919999999998</v>
       </c>
       <c r="H104" s="99">
@@ -10347,7 +10359,7 @@
         <f t="shared" si="20"/>
         <v>21943.919999999998</v>
       </c>
-      <c r="O104" s="154">
+      <c r="O104" s="153">
         <f t="shared" si="21"/>
         <v>0.9200000000000006</v>
       </c>
@@ -10365,7 +10377,7 @@
       <c r="F105" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G105" s="155">
+      <c r="G105" s="154">
         <v>16428.93</v>
       </c>
       <c r="H105" s="99">
@@ -10396,7 +10408,7 @@
         <f t="shared" si="20"/>
         <v>21943.93</v>
       </c>
-      <c r="O105" s="154">
+      <c r="O105" s="153">
         <f t="shared" si="21"/>
         <v>0.9300000000000006</v>
       </c>
@@ -10414,7 +10426,7 @@
       <c r="F106" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G106" s="155">
+      <c r="G106" s="154">
         <v>16428.939999999999</v>
       </c>
       <c r="H106" s="99"/>
@@ -10442,7 +10454,7 @@
         <f t="shared" si="20"/>
         <v>39358.94</v>
       </c>
-      <c r="O106" s="154">
+      <c r="O106" s="153">
         <f t="shared" si="21"/>
         <v>0.94000000000000061</v>
       </c>
@@ -10460,7 +10472,7 @@
       <c r="F107" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G107" s="155">
+      <c r="G107" s="154">
         <v>16428.95</v>
       </c>
       <c r="H107" s="99">
@@ -10491,7 +10503,7 @@
         <f t="shared" si="20"/>
         <v>21943.95</v>
       </c>
-      <c r="O107" s="154">
+      <c r="O107" s="153">
         <f t="shared" si="21"/>
         <v>0.95000000000000062</v>
       </c>
@@ -10509,7 +10521,7 @@
       <c r="F108" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G108" s="155">
+      <c r="G108" s="154">
         <v>16428.96</v>
       </c>
       <c r="H108" s="99">
@@ -10540,7 +10552,7 @@
         <f t="shared" si="20"/>
         <v>21943.96</v>
       </c>
-      <c r="O108" s="154">
+      <c r="O108" s="153">
         <f t="shared" si="21"/>
         <v>0.96000000000000063</v>
       </c>
@@ -10558,7 +10570,7 @@
       <c r="F109" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G109" s="155">
+      <c r="G109" s="154">
         <v>16428.97</v>
       </c>
       <c r="H109" s="99">
@@ -10589,7 +10601,7 @@
         <f t="shared" si="20"/>
         <v>21943.97</v>
       </c>
-      <c r="O109" s="154">
+      <c r="O109" s="153">
         <f t="shared" si="21"/>
         <v>0.97000000000000064</v>
       </c>
@@ -10607,7 +10619,7 @@
       <c r="F110" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G110" s="155">
+      <c r="G110" s="154">
         <v>16428.98</v>
       </c>
       <c r="H110" s="99">
@@ -10638,7 +10650,7 @@
         <f t="shared" si="20"/>
         <v>21943.98</v>
       </c>
-      <c r="O110" s="154">
+      <c r="O110" s="153">
         <f t="shared" si="21"/>
         <v>0.98000000000000065</v>
       </c>
@@ -10656,7 +10668,7 @@
       <c r="F111" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G111" s="155">
+      <c r="G111" s="154">
         <v>16428.990000000002</v>
       </c>
       <c r="H111" s="99">
@@ -10687,7 +10699,7 @@
         <f t="shared" si="20"/>
         <v>21943.99</v>
       </c>
-      <c r="O111" s="154">
+      <c r="O111" s="153">
         <f t="shared" si="21"/>
         <v>0.99000000000000066</v>
       </c>
@@ -10705,7 +10717,7 @@
       <c r="F112" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G112" s="155">
+      <c r="G112" s="154">
         <v>16429</v>
       </c>
       <c r="H112" s="99">
@@ -10736,13 +10748,13 @@
         <f t="shared" si="20"/>
         <v>21944</v>
       </c>
-      <c r="O112" s="154">
+      <c r="O112" s="153">
         <f t="shared" si="21"/>
         <v>1.0000000000000007</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A113" s="148"/>
+      <c r="A113" s="147"/>
       <c r="B113" s="36"/>
       <c r="C113" s="36" t="s">
         <v>159</v>
@@ -10754,7 +10766,7 @@
       <c r="F113" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G113" s="155">
+      <c r="G113" s="154">
         <v>16429.009999999998</v>
       </c>
       <c r="H113" s="99">
@@ -10785,13 +10797,13 @@
         <f t="shared" si="20"/>
         <v>21944.01</v>
       </c>
-      <c r="O113" s="154">
+      <c r="O113" s="153">
         <f t="shared" si="21"/>
         <v>1.0100000000000007</v>
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A114" s="148"/>
+      <c r="A114" s="147"/>
       <c r="B114" s="36"/>
       <c r="C114" s="36" t="s">
         <v>160</v>
@@ -10803,7 +10815,7 @@
       <c r="F114" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G114" s="155">
+      <c r="G114" s="154">
         <v>16429.02</v>
       </c>
       <c r="H114" s="99">
@@ -10834,13 +10846,13 @@
         <f t="shared" si="20"/>
         <v>21944.02</v>
       </c>
-      <c r="O114" s="154">
+      <c r="O114" s="153">
         <f t="shared" si="21"/>
         <v>1.0200000000000007</v>
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A115" s="148"/>
+      <c r="A115" s="147"/>
       <c r="B115" s="36"/>
       <c r="C115" s="36" t="s">
         <v>161</v>
@@ -10852,7 +10864,7 @@
       <c r="F115" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G115" s="155">
+      <c r="G115" s="154">
         <v>16429.03</v>
       </c>
       <c r="H115" s="99">
@@ -10883,13 +10895,13 @@
         <f t="shared" si="20"/>
         <v>21944.03</v>
       </c>
-      <c r="O115" s="154">
+      <c r="O115" s="153">
         <f t="shared" si="21"/>
         <v>1.0300000000000007</v>
       </c>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A116" s="148"/>
+      <c r="A116" s="147"/>
       <c r="B116" s="36"/>
       <c r="C116" s="36" t="s">
         <v>162</v>
@@ -10901,7 +10913,7 @@
       <c r="F116" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G116" s="155">
+      <c r="G116" s="154">
         <v>16429.04</v>
       </c>
       <c r="H116" s="99">
@@ -10932,13 +10944,13 @@
         <f t="shared" si="20"/>
         <v>21944.04</v>
       </c>
-      <c r="O116" s="154">
+      <c r="O116" s="153">
         <f t="shared" si="21"/>
         <v>1.0400000000000007</v>
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A117" s="148"/>
+      <c r="A117" s="147"/>
       <c r="B117" s="36"/>
       <c r="C117" s="36" t="s">
         <v>163</v>
@@ -10950,7 +10962,7 @@
       <c r="F117" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G117" s="155">
+      <c r="G117" s="154">
         <v>16429.05</v>
       </c>
       <c r="H117" s="99"/>
@@ -10978,13 +10990,13 @@
         <f t="shared" si="20"/>
         <v>39359.050000000003</v>
       </c>
-      <c r="O117" s="154">
+      <c r="O117" s="153">
         <f t="shared" si="21"/>
         <v>1.0500000000000007</v>
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A118" s="148"/>
+      <c r="A118" s="147"/>
       <c r="B118" s="36"/>
       <c r="C118" s="36" t="s">
         <v>164</v>
@@ -10996,7 +11008,7 @@
       <c r="F118" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G118" s="155">
+      <c r="G118" s="154">
         <v>16429.060000000001</v>
       </c>
       <c r="H118" s="99">
@@ -11027,13 +11039,13 @@
         <f t="shared" si="20"/>
         <v>21944.06</v>
       </c>
-      <c r="O118" s="154">
+      <c r="O118" s="153">
         <f t="shared" si="21"/>
         <v>1.0600000000000007</v>
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A119" s="148"/>
+      <c r="A119" s="147"/>
       <c r="B119" s="36"/>
       <c r="C119" s="36" t="s">
         <v>165</v>
@@ -11045,7 +11057,7 @@
       <c r="F119" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G119" s="155">
+      <c r="G119" s="154">
         <v>16429.07</v>
       </c>
       <c r="H119" s="99">
@@ -11076,13 +11088,13 @@
         <f t="shared" si="20"/>
         <v>21944.07</v>
       </c>
-      <c r="O119" s="154">
+      <c r="O119" s="153">
         <f t="shared" si="21"/>
         <v>1.0700000000000007</v>
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A120" s="148"/>
+      <c r="A120" s="147"/>
       <c r="B120" s="36"/>
       <c r="C120" s="36" t="s">
         <v>166</v>
@@ -11094,7 +11106,7 @@
       <c r="F120" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G120" s="155">
+      <c r="G120" s="154">
         <v>16429.080000000002</v>
       </c>
       <c r="H120" s="99">
@@ -11125,13 +11137,13 @@
         <f t="shared" si="20"/>
         <v>21944.080000000002</v>
       </c>
-      <c r="O120" s="154">
+      <c r="O120" s="153">
         <f t="shared" si="21"/>
         <v>1.0800000000000007</v>
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A121" s="148"/>
+      <c r="A121" s="147"/>
       <c r="B121" s="36"/>
       <c r="C121" s="36" t="s">
         <v>167</v>
@@ -11143,7 +11155,7 @@
       <c r="F121" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G121" s="155">
+      <c r="G121" s="154">
         <v>16429.09</v>
       </c>
       <c r="H121" s="99">
@@ -11174,13 +11186,13 @@
         <f t="shared" si="20"/>
         <v>21944.09</v>
       </c>
-      <c r="O121" s="154">
+      <c r="O121" s="153">
         <f t="shared" si="21"/>
         <v>1.0900000000000007</v>
       </c>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A122" s="148"/>
+      <c r="A122" s="147"/>
       <c r="B122" s="36"/>
       <c r="C122" s="36" t="s">
         <v>168</v>
@@ -11192,7 +11204,7 @@
       <c r="F122" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G122" s="155">
+      <c r="G122" s="154">
         <v>16429.099999999999</v>
       </c>
       <c r="H122" s="99">
@@ -11223,13 +11235,13 @@
         <f t="shared" si="20"/>
         <v>21944.1</v>
       </c>
-      <c r="O122" s="154">
+      <c r="O122" s="153">
         <f t="shared" si="21"/>
         <v>1.1000000000000008</v>
       </c>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A123" s="148"/>
+      <c r="A123" s="147"/>
       <c r="B123" s="36"/>
       <c r="C123" s="36" t="s">
         <v>169</v>
@@ -11241,7 +11253,7 @@
       <c r="F123" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G123" s="155">
+      <c r="G123" s="154">
         <v>16429.11</v>
       </c>
       <c r="H123" s="99">
@@ -11272,13 +11284,13 @@
         <f t="shared" si="20"/>
         <v>21944.11</v>
       </c>
-      <c r="O123" s="154">
+      <c r="O123" s="153">
         <f t="shared" si="21"/>
         <v>1.1100000000000008</v>
       </c>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A124" s="148" t="s">
+      <c r="A124" s="147" t="s">
         <v>27</v>
       </c>
       <c r="B124" s="36"/>
@@ -11292,7 +11304,7 @@
       <c r="F124" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G124" s="155">
+      <c r="G124" s="154">
         <v>16429.12</v>
       </c>
       <c r="H124" s="99">
@@ -11323,13 +11335,13 @@
         <f t="shared" si="20"/>
         <v>21944.12</v>
       </c>
-      <c r="O124" s="154">
+      <c r="O124" s="153">
         <f t="shared" si="21"/>
         <v>1.1200000000000008</v>
       </c>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A125" s="148" t="s">
+      <c r="A125" s="147" t="s">
         <v>27</v>
       </c>
       <c r="B125" s="36"/>
@@ -11343,7 +11355,7 @@
       <c r="F125" s="105">
         <v>2.3E-3</v>
       </c>
-      <c r="G125" s="155">
+      <c r="G125" s="154">
         <v>16429.13</v>
       </c>
       <c r="H125" s="99">
@@ -11374,7 +11386,7 @@
         <f t="shared" si="20"/>
         <v>21944.13</v>
       </c>
-      <c r="O125" s="154">
+      <c r="O125" s="153">
         <f t="shared" si="21"/>
         <v>1.1300000000000008</v>
       </c>
@@ -11441,36 +11453,36 @@
     <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K128" s="66">
         <f>K127-L1</f>
-        <v>1240893.8416399993</v>
+        <v>343946.7316399999</v>
       </c>
     </row>
     <row r="129" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C129" s="199"/>
-      <c r="D129" s="199"/>
-      <c r="E129" s="199"/>
-      <c r="F129" s="199"/>
-      <c r="G129" s="199"/>
-      <c r="H129" s="199"/>
-      <c r="I129" s="199"/>
-      <c r="J129" s="199"/>
-      <c r="K129" s="199"/>
-      <c r="L129" s="199"/>
-      <c r="M129" s="199"/>
-      <c r="N129" s="199"/>
+      <c r="C129" s="194"/>
+      <c r="D129" s="194"/>
+      <c r="E129" s="194"/>
+      <c r="F129" s="194"/>
+      <c r="G129" s="194"/>
+      <c r="H129" s="194"/>
+      <c r="I129" s="194"/>
+      <c r="J129" s="194"/>
+      <c r="K129" s="194"/>
+      <c r="L129" s="194"/>
+      <c r="M129" s="194"/>
+      <c r="N129" s="194"/>
     </row>
     <row r="130" spans="3:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C130" s="199"/>
-      <c r="D130" s="199"/>
-      <c r="E130" s="199"/>
-      <c r="F130" s="199"/>
-      <c r="G130" s="199"/>
-      <c r="H130" s="199"/>
-      <c r="I130" s="199"/>
-      <c r="J130" s="199"/>
-      <c r="K130" s="199"/>
-      <c r="L130" s="199"/>
-      <c r="M130" s="199"/>
-      <c r="N130" s="199"/>
+      <c r="C130" s="194"/>
+      <c r="D130" s="194"/>
+      <c r="E130" s="194"/>
+      <c r="F130" s="194"/>
+      <c r="G130" s="194"/>
+      <c r="H130" s="194"/>
+      <c r="I130" s="194"/>
+      <c r="J130" s="194"/>
+      <c r="K130" s="194"/>
+      <c r="L130" s="194"/>
+      <c r="M130" s="194"/>
+      <c r="N130" s="194"/>
     </row>
     <row r="131" spans="3:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C131" s="87"/>
@@ -11487,118 +11499,118 @@
       <c r="N131" s="87"/>
     </row>
     <row r="132" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C132" s="199" t="s">
+      <c r="C132" s="194" t="s">
         <v>269</v>
       </c>
-      <c r="D132" s="199"/>
-      <c r="E132" s="199"/>
-      <c r="F132" s="199"/>
-      <c r="G132" s="199"/>
-      <c r="H132" s="199"/>
-      <c r="I132" s="199"/>
-      <c r="J132" s="199"/>
-      <c r="K132" s="199"/>
-      <c r="L132" s="199"/>
-      <c r="M132" s="199"/>
-      <c r="N132" s="199"/>
+      <c r="D132" s="194"/>
+      <c r="E132" s="194"/>
+      <c r="F132" s="194"/>
+      <c r="G132" s="194"/>
+      <c r="H132" s="194"/>
+      <c r="I132" s="194"/>
+      <c r="J132" s="194"/>
+      <c r="K132" s="194"/>
+      <c r="L132" s="194"/>
+      <c r="M132" s="194"/>
+      <c r="N132" s="194"/>
     </row>
     <row r="133" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C133" s="199"/>
-      <c r="D133" s="199"/>
-      <c r="E133" s="199"/>
-      <c r="F133" s="199"/>
-      <c r="G133" s="199"/>
-      <c r="H133" s="199"/>
-      <c r="I133" s="199"/>
-      <c r="J133" s="199"/>
-      <c r="K133" s="199"/>
-      <c r="L133" s="199"/>
-      <c r="M133" s="199"/>
-      <c r="N133" s="199"/>
+      <c r="C133" s="194"/>
+      <c r="D133" s="194"/>
+      <c r="E133" s="194"/>
+      <c r="F133" s="194"/>
+      <c r="G133" s="194"/>
+      <c r="H133" s="194"/>
+      <c r="I133" s="194"/>
+      <c r="J133" s="194"/>
+      <c r="K133" s="194"/>
+      <c r="L133" s="194"/>
+      <c r="M133" s="194"/>
+      <c r="N133" s="194"/>
     </row>
     <row r="134" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C134" s="199"/>
-      <c r="D134" s="199"/>
-      <c r="E134" s="199"/>
-      <c r="F134" s="199"/>
-      <c r="G134" s="199"/>
-      <c r="H134" s="199"/>
-      <c r="I134" s="199"/>
-      <c r="J134" s="199"/>
-      <c r="K134" s="199"/>
-      <c r="L134" s="199"/>
-      <c r="M134" s="199"/>
-      <c r="N134" s="199"/>
+      <c r="C134" s="194"/>
+      <c r="D134" s="194"/>
+      <c r="E134" s="194"/>
+      <c r="F134" s="194"/>
+      <c r="G134" s="194"/>
+      <c r="H134" s="194"/>
+      <c r="I134" s="194"/>
+      <c r="J134" s="194"/>
+      <c r="K134" s="194"/>
+      <c r="L134" s="194"/>
+      <c r="M134" s="194"/>
+      <c r="N134" s="194"/>
     </row>
     <row r="135" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C135" s="199"/>
-      <c r="D135" s="199"/>
-      <c r="E135" s="199"/>
-      <c r="F135" s="199"/>
-      <c r="G135" s="199"/>
-      <c r="H135" s="199"/>
-      <c r="I135" s="199"/>
-      <c r="J135" s="199"/>
-      <c r="K135" s="199"/>
-      <c r="L135" s="199"/>
-      <c r="M135" s="199"/>
-      <c r="N135" s="199"/>
+      <c r="C135" s="194"/>
+      <c r="D135" s="194"/>
+      <c r="E135" s="194"/>
+      <c r="F135" s="194"/>
+      <c r="G135" s="194"/>
+      <c r="H135" s="194"/>
+      <c r="I135" s="194"/>
+      <c r="J135" s="194"/>
+      <c r="K135" s="194"/>
+      <c r="L135" s="194"/>
+      <c r="M135" s="194"/>
+      <c r="N135" s="194"/>
     </row>
     <row r="136" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C136" s="199"/>
-      <c r="D136" s="199"/>
-      <c r="E136" s="199"/>
-      <c r="F136" s="199"/>
-      <c r="G136" s="199"/>
-      <c r="H136" s="199"/>
-      <c r="I136" s="199"/>
-      <c r="J136" s="199"/>
-      <c r="K136" s="199"/>
-      <c r="L136" s="199"/>
-      <c r="M136" s="199"/>
-      <c r="N136" s="199"/>
+      <c r="C136" s="194"/>
+      <c r="D136" s="194"/>
+      <c r="E136" s="194"/>
+      <c r="F136" s="194"/>
+      <c r="G136" s="194"/>
+      <c r="H136" s="194"/>
+      <c r="I136" s="194"/>
+      <c r="J136" s="194"/>
+      <c r="K136" s="194"/>
+      <c r="L136" s="194"/>
+      <c r="M136" s="194"/>
+      <c r="N136" s="194"/>
     </row>
     <row r="137" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C137" s="199"/>
-      <c r="D137" s="199"/>
-      <c r="E137" s="199"/>
-      <c r="F137" s="199"/>
-      <c r="G137" s="199"/>
-      <c r="H137" s="199"/>
-      <c r="I137" s="199"/>
-      <c r="J137" s="199"/>
-      <c r="K137" s="199"/>
-      <c r="L137" s="199"/>
-      <c r="M137" s="199"/>
-      <c r="N137" s="199"/>
+      <c r="C137" s="194"/>
+      <c r="D137" s="194"/>
+      <c r="E137" s="194"/>
+      <c r="F137" s="194"/>
+      <c r="G137" s="194"/>
+      <c r="H137" s="194"/>
+      <c r="I137" s="194"/>
+      <c r="J137" s="194"/>
+      <c r="K137" s="194"/>
+      <c r="L137" s="194"/>
+      <c r="M137" s="194"/>
+      <c r="N137" s="194"/>
     </row>
     <row r="138" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C138" s="199"/>
-      <c r="D138" s="199"/>
-      <c r="E138" s="199"/>
-      <c r="F138" s="199"/>
-      <c r="G138" s="199"/>
-      <c r="H138" s="199"/>
-      <c r="I138" s="199"/>
-      <c r="J138" s="199"/>
-      <c r="K138" s="199"/>
-      <c r="L138" s="199"/>
-      <c r="M138" s="199"/>
-      <c r="N138" s="199"/>
+      <c r="C138" s="194"/>
+      <c r="D138" s="194"/>
+      <c r="E138" s="194"/>
+      <c r="F138" s="194"/>
+      <c r="G138" s="194"/>
+      <c r="H138" s="194"/>
+      <c r="I138" s="194"/>
+      <c r="J138" s="194"/>
+      <c r="K138" s="194"/>
+      <c r="L138" s="194"/>
+      <c r="M138" s="194"/>
+      <c r="N138" s="194"/>
     </row>
     <row r="139" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C139" s="199"/>
-      <c r="D139" s="199"/>
-      <c r="E139" s="199"/>
-      <c r="F139" s="199"/>
-      <c r="G139" s="199"/>
-      <c r="H139" s="199"/>
-      <c r="I139" s="199"/>
-      <c r="J139" s="199"/>
-      <c r="K139" s="199"/>
-      <c r="L139" s="199"/>
-      <c r="M139" s="199"/>
-      <c r="N139" s="199"/>
+      <c r="C139" s="194"/>
+      <c r="D139" s="194"/>
+      <c r="E139" s="194"/>
+      <c r="F139" s="194"/>
+      <c r="G139" s="194"/>
+      <c r="H139" s="194"/>
+      <c r="I139" s="194"/>
+      <c r="J139" s="194"/>
+      <c r="K139" s="194"/>
+      <c r="L139" s="194"/>
+      <c r="M139" s="194"/>
+      <c r="N139" s="194"/>
     </row>
     <row r="140" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C140" s="87"/>
@@ -11629,111 +11641,117 @@
       <c r="N141" s="87"/>
     </row>
     <row r="142" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C142" s="198" t="s">
+      <c r="C142" s="193" t="s">
         <v>268</v>
       </c>
-      <c r="D142" s="198"/>
-      <c r="E142" s="198"/>
-      <c r="F142" s="198"/>
-      <c r="G142" s="198"/>
-      <c r="H142" s="198"/>
-      <c r="I142" s="198"/>
-      <c r="J142" s="198"/>
-      <c r="K142" s="198"/>
-      <c r="L142" s="198"/>
-      <c r="M142" s="198"/>
-      <c r="N142" s="198"/>
+      <c r="D142" s="193"/>
+      <c r="E142" s="193"/>
+      <c r="F142" s="193"/>
+      <c r="G142" s="193"/>
+      <c r="H142" s="193"/>
+      <c r="I142" s="193"/>
+      <c r="J142" s="193"/>
+      <c r="K142" s="193"/>
+      <c r="L142" s="193"/>
+      <c r="M142" s="193"/>
+      <c r="N142" s="193"/>
     </row>
     <row r="143" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C143" s="198"/>
-      <c r="D143" s="198"/>
-      <c r="E143" s="198"/>
-      <c r="F143" s="198"/>
-      <c r="G143" s="198"/>
-      <c r="H143" s="198"/>
-      <c r="I143" s="198"/>
-      <c r="J143" s="198"/>
-      <c r="K143" s="198"/>
-      <c r="L143" s="198"/>
-      <c r="M143" s="198"/>
-      <c r="N143" s="198"/>
+      <c r="C143" s="193"/>
+      <c r="D143" s="193"/>
+      <c r="E143" s="193"/>
+      <c r="F143" s="193"/>
+      <c r="G143" s="193"/>
+      <c r="H143" s="193"/>
+      <c r="I143" s="193"/>
+      <c r="J143" s="193"/>
+      <c r="K143" s="193"/>
+      <c r="L143" s="193"/>
+      <c r="M143" s="193"/>
+      <c r="N143" s="193"/>
     </row>
     <row r="144" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C144" s="198"/>
-      <c r="D144" s="198"/>
-      <c r="E144" s="198"/>
-      <c r="F144" s="198"/>
-      <c r="G144" s="198"/>
-      <c r="H144" s="198"/>
-      <c r="I144" s="198"/>
-      <c r="J144" s="198"/>
-      <c r="K144" s="198"/>
-      <c r="L144" s="198"/>
-      <c r="M144" s="198"/>
-      <c r="N144" s="198"/>
+      <c r="C144" s="193"/>
+      <c r="D144" s="193"/>
+      <c r="E144" s="193"/>
+      <c r="F144" s="193"/>
+      <c r="G144" s="193"/>
+      <c r="H144" s="193"/>
+      <c r="I144" s="193"/>
+      <c r="J144" s="193"/>
+      <c r="K144" s="193"/>
+      <c r="L144" s="193"/>
+      <c r="M144" s="193"/>
+      <c r="N144" s="193"/>
       <c r="P144" s="95">
         <f>L1-K127</f>
-        <v>-1240893.8416399993</v>
+        <v>-343946.7316399999</v>
       </c>
     </row>
     <row r="145" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C145" s="198"/>
-      <c r="D145" s="198"/>
-      <c r="E145" s="198"/>
-      <c r="F145" s="198"/>
-      <c r="G145" s="198"/>
-      <c r="H145" s="198"/>
-      <c r="I145" s="198"/>
-      <c r="J145" s="198"/>
-      <c r="K145" s="198"/>
-      <c r="L145" s="198"/>
-      <c r="M145" s="198"/>
-      <c r="N145" s="198"/>
+      <c r="C145" s="193"/>
+      <c r="D145" s="193"/>
+      <c r="E145" s="193"/>
+      <c r="F145" s="193"/>
+      <c r="G145" s="193"/>
+      <c r="H145" s="193"/>
+      <c r="I145" s="193"/>
+      <c r="J145" s="193"/>
+      <c r="K145" s="193"/>
+      <c r="L145" s="193"/>
+      <c r="M145" s="193"/>
+      <c r="N145" s="193"/>
     </row>
     <row r="146" spans="3:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C146" s="198"/>
-      <c r="D146" s="198"/>
-      <c r="E146" s="198"/>
-      <c r="F146" s="198"/>
-      <c r="G146" s="198"/>
-      <c r="H146" s="198"/>
-      <c r="I146" s="198"/>
-      <c r="J146" s="198"/>
-      <c r="K146" s="198"/>
-      <c r="L146" s="198"/>
-      <c r="M146" s="198"/>
-      <c r="N146" s="198"/>
+      <c r="C146" s="193"/>
+      <c r="D146" s="193"/>
+      <c r="E146" s="193"/>
+      <c r="F146" s="193"/>
+      <c r="G146" s="193"/>
+      <c r="H146" s="193"/>
+      <c r="I146" s="193"/>
+      <c r="J146" s="193"/>
+      <c r="K146" s="193"/>
+      <c r="L146" s="193"/>
+      <c r="M146" s="193"/>
+      <c r="N146" s="193"/>
     </row>
     <row r="147" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C147" s="198"/>
-      <c r="D147" s="198"/>
-      <c r="E147" s="198"/>
-      <c r="F147" s="198"/>
-      <c r="G147" s="198"/>
-      <c r="H147" s="198"/>
-      <c r="I147" s="198"/>
-      <c r="J147" s="198"/>
-      <c r="K147" s="198"/>
-      <c r="L147" s="198"/>
-      <c r="M147" s="198"/>
-      <c r="N147" s="198"/>
+      <c r="C147" s="193"/>
+      <c r="D147" s="193"/>
+      <c r="E147" s="193"/>
+      <c r="F147" s="193"/>
+      <c r="G147" s="193"/>
+      <c r="H147" s="193"/>
+      <c r="I147" s="193"/>
+      <c r="J147" s="193"/>
+      <c r="K147" s="193"/>
+      <c r="L147" s="193"/>
+      <c r="M147" s="193"/>
+      <c r="N147" s="193"/>
     </row>
     <row r="148" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C148" s="198"/>
-      <c r="D148" s="198"/>
-      <c r="E148" s="198"/>
-      <c r="F148" s="198"/>
-      <c r="G148" s="198"/>
-      <c r="H148" s="198"/>
-      <c r="I148" s="198"/>
-      <c r="J148" s="198"/>
-      <c r="K148" s="198"/>
-      <c r="L148" s="198"/>
-      <c r="M148" s="198"/>
-      <c r="N148" s="198"/>
+      <c r="C148" s="193"/>
+      <c r="D148" s="193"/>
+      <c r="E148" s="193"/>
+      <c r="F148" s="193"/>
+      <c r="G148" s="193"/>
+      <c r="H148" s="193"/>
+      <c r="I148" s="193"/>
+      <c r="J148" s="193"/>
+      <c r="K148" s="193"/>
+      <c r="L148" s="193"/>
+      <c r="M148" s="193"/>
+      <c r="N148" s="193"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="E5:E7"/>
     <mergeCell ref="Q8:R9"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="C142:N148"/>
@@ -11747,12 +11765,6 @@
     <mergeCell ref="C132:N139"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="E5:E7"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11767,8 +11779,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B4" s="179" t="s">
-        <v>335</v>
+      <c r="B4" s="178" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -11785,85 +11797,85 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="208" t="s">
+        <v>316</v>
+      </c>
+      <c r="D4" s="208"/>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C5" s="176">
+        <v>52141.08</v>
+      </c>
+      <c r="D5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C6" s="176">
+        <v>67140.100000000006</v>
+      </c>
+      <c r="D6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C7" s="176">
+        <v>52121.11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C8" s="176">
+        <v>67885.119999999995</v>
+      </c>
+      <c r="D8" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C9" s="176">
+        <v>67140.160000000003</v>
+      </c>
+      <c r="D9" t="s">
         <v>321</v>
       </c>
-      <c r="D4" s="209"/>
-    </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C5" s="177">
-        <v>52141.08</v>
-      </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C10" s="176">
+        <v>62141.17</v>
+      </c>
+      <c r="D10" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C6" s="177">
-        <v>67140.100000000006</v>
-      </c>
-      <c r="D6" t="s">
+    <row r="11" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C11" s="176">
+        <v>67855.179999999993</v>
+      </c>
+      <c r="D11" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C7" s="177">
-        <v>52121.11</v>
-      </c>
-      <c r="D7" t="s">
+    <row r="12" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C12" s="176">
+        <v>62141.23</v>
+      </c>
+      <c r="D12" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C8" s="177">
-        <v>67885.119999999995</v>
-      </c>
-      <c r="D8" t="s">
+    <row r="13" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C13" s="176">
+        <v>67855.240000000005</v>
+      </c>
+      <c r="D13" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C9" s="177">
-        <v>67140.160000000003</v>
-      </c>
-      <c r="D9" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C10" s="177">
-        <v>62141.17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C11" s="177">
-        <v>67855.179999999993</v>
-      </c>
-      <c r="D11" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C12" s="177">
-        <v>62141.23</v>
-      </c>
-      <c r="D12" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C13" s="177">
-        <v>67855.240000000005</v>
-      </c>
-      <c r="D13" t="s">
-        <v>330</v>
-      </c>
-    </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C14" s="177">
+      <c r="C14" s="176">
         <f>SUM(C5:C13)</f>
         <v>566420.39</v>
       </c>

--- a/EL MIRADOR/Agosto/Agosto - EL MIRADOR .xlsx
+++ b/EL MIRADOR/Agosto/Agosto - EL MIRADOR .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\EL MIRADOR\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1C16BA-C72F-454E-BC7A-796A6F85D8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345ED8AF-F522-470C-B222-8C9EC439FBF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="339">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1042,6 +1042,9 @@
   </si>
   <si>
     <t>Horas extras</t>
+  </si>
+  <si>
+    <t>No tiene que tener deuda</t>
   </si>
 </sst>
 </file>
@@ -1650,7 +1653,7 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="228">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1923,26 +1926,14 @@
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1977,9 +1968,22 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -5251,11 +5255,11 @@
       <c r="K1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="217">
+      <c r="L1" s="213">
         <f>RESUMEN!D104-RESUMEN!D102</f>
         <v>6937168.6099999994</v>
       </c>
-      <c r="M1" s="218"/>
+      <c r="M1" s="214"/>
       <c r="N1" s="76"/>
       <c r="O1" s="64"/>
     </row>
@@ -5324,78 +5328,78 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="208" t="s">
+      <c r="A5" s="209" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="210" t="s">
+      <c r="B5" s="222" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="208" t="s">
+      <c r="C5" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="212" t="s">
+      <c r="D5" s="224" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="212" t="s">
+      <c r="E5" s="224" t="s">
         <v>278</v>
       </c>
-      <c r="F5" s="208" t="s">
+      <c r="F5" s="209" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="208" t="s">
+      <c r="G5" s="209" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="208" t="s">
+      <c r="H5" s="209" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="219" t="s">
+      <c r="I5" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="221" t="s">
+      <c r="J5" s="217" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="221" t="s">
+      <c r="K5" s="217" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="224" t="s">
+      <c r="L5" s="220" t="s">
         <v>43</v>
       </c>
-      <c r="M5" s="221" t="s">
+      <c r="M5" s="217" t="s">
         <v>291</v>
       </c>
-      <c r="N5" s="221" t="s">
+      <c r="N5" s="217" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="209"/>
-      <c r="B6" s="211"/>
-      <c r="C6" s="209"/>
-      <c r="D6" s="213"/>
-      <c r="E6" s="213"/>
-      <c r="F6" s="209"/>
-      <c r="G6" s="209"/>
-      <c r="H6" s="209"/>
-      <c r="I6" s="220"/>
-      <c r="J6" s="222"/>
-      <c r="K6" s="222"/>
-      <c r="L6" s="225"/>
-      <c r="M6" s="222"/>
-      <c r="N6" s="222"/>
+      <c r="A6" s="210"/>
+      <c r="B6" s="223"/>
+      <c r="C6" s="210"/>
+      <c r="D6" s="225"/>
+      <c r="E6" s="225"/>
+      <c r="F6" s="210"/>
+      <c r="G6" s="210"/>
+      <c r="H6" s="210"/>
+      <c r="I6" s="216"/>
+      <c r="J6" s="218"/>
+      <c r="K6" s="218"/>
+      <c r="L6" s="221"/>
+      <c r="M6" s="218"/>
+      <c r="N6" s="218"/>
     </row>
     <row r="7" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="209"/>
-      <c r="B7" s="211"/>
-      <c r="C7" s="209"/>
-      <c r="D7" s="213"/>
-      <c r="E7" s="213"/>
-      <c r="F7" s="209"/>
-      <c r="G7" s="209"/>
-      <c r="H7" s="209"/>
-      <c r="I7" s="220"/>
-      <c r="J7" s="222"/>
-      <c r="K7" s="223"/>
-      <c r="L7" s="225"/>
+      <c r="A7" s="210"/>
+      <c r="B7" s="223"/>
+      <c r="C7" s="210"/>
+      <c r="D7" s="225"/>
+      <c r="E7" s="225"/>
+      <c r="F7" s="210"/>
+      <c r="G7" s="210"/>
+      <c r="H7" s="210"/>
+      <c r="I7" s="216"/>
+      <c r="J7" s="218"/>
+      <c r="K7" s="219"/>
+      <c r="L7" s="221"/>
       <c r="M7" s="152" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 15/09</v>
@@ -5452,10 +5456,10 @@
         <v>127313.57001968</v>
       </c>
       <c r="O8" s="133"/>
-      <c r="Q8" s="214" t="s">
+      <c r="Q8" s="208" t="s">
         <v>262</v>
       </c>
-      <c r="R8" s="214"/>
+      <c r="R8" s="208"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
@@ -5500,8 +5504,8 @@
         <v>107925.25557887998</v>
       </c>
       <c r="O9" s="133"/>
-      <c r="Q9" s="214"/>
-      <c r="R9" s="214"/>
+      <c r="Q9" s="208"/>
+      <c r="R9" s="208"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
@@ -9917,7 +9921,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="125"/>
       <c r="B97" s="36"/>
       <c r="C97" s="36" t="s">
@@ -9966,7 +9970,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="125"/>
       <c r="B98" s="36"/>
       <c r="C98" s="36" t="s">
@@ -10015,7 +10019,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="125"/>
       <c r="B99" s="36"/>
       <c r="C99" s="36" t="s">
@@ -10064,7 +10068,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="125"/>
       <c r="B100" s="36"/>
       <c r="C100" s="36" t="s">
@@ -10113,7 +10117,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="101" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="125"/>
       <c r="B101" s="36"/>
       <c r="C101" s="36" t="s">
@@ -10162,7 +10166,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="125"/>
       <c r="B102" s="36"/>
       <c r="C102" s="36" t="s">
@@ -10211,7 +10215,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="125"/>
       <c r="B103" s="36"/>
       <c r="C103" s="36" t="s">
@@ -10260,7 +10264,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="125"/>
       <c r="B104" s="36"/>
       <c r="C104" s="36" t="s">
@@ -10309,7 +10313,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="125"/>
       <c r="B105" s="36"/>
       <c r="C105" s="36" t="s">
@@ -10358,7 +10362,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="125"/>
       <c r="B106" s="36"/>
       <c r="C106" s="36" t="s">
@@ -10374,7 +10378,7 @@
       <c r="G106" s="154">
         <v>37129.94</v>
       </c>
-      <c r="H106" s="99">
+      <c r="H106" s="227">
         <v>20700.939999999999</v>
       </c>
       <c r="I106" s="60">
@@ -10405,8 +10409,11 @@
         <f t="shared" si="21"/>
         <v>0.94000000000000061</v>
       </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P106" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="125"/>
       <c r="B107" s="36"/>
       <c r="C107" s="36" t="s">
@@ -10455,7 +10462,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="125"/>
       <c r="B108" s="36"/>
       <c r="C108" s="180" t="s">
@@ -10501,7 +10508,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="125"/>
       <c r="B109" s="36"/>
       <c r="C109" s="36" t="s">
@@ -10550,7 +10557,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="125"/>
       <c r="B110" s="36"/>
       <c r="C110" s="36" t="s">
@@ -10599,7 +10606,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="125"/>
       <c r="B111" s="36"/>
       <c r="C111" s="36" t="s">
@@ -10648,7 +10655,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="125"/>
       <c r="B112" s="36"/>
       <c r="C112" s="36" t="s">
@@ -11404,32 +11411,32 @@
       </c>
     </row>
     <row r="129" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C129" s="216"/>
-      <c r="D129" s="216"/>
-      <c r="E129" s="216"/>
-      <c r="F129" s="216"/>
-      <c r="G129" s="216"/>
-      <c r="H129" s="216"/>
-      <c r="I129" s="216"/>
-      <c r="J129" s="216"/>
-      <c r="K129" s="216"/>
-      <c r="L129" s="216"/>
-      <c r="M129" s="216"/>
-      <c r="N129" s="216"/>
+      <c r="C129" s="212"/>
+      <c r="D129" s="212"/>
+      <c r="E129" s="212"/>
+      <c r="F129" s="212"/>
+      <c r="G129" s="212"/>
+      <c r="H129" s="212"/>
+      <c r="I129" s="212"/>
+      <c r="J129" s="212"/>
+      <c r="K129" s="212"/>
+      <c r="L129" s="212"/>
+      <c r="M129" s="212"/>
+      <c r="N129" s="212"/>
     </row>
     <row r="130" spans="3:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C130" s="216"/>
-      <c r="D130" s="216"/>
-      <c r="E130" s="216"/>
-      <c r="F130" s="216"/>
-      <c r="G130" s="216"/>
-      <c r="H130" s="216"/>
-      <c r="I130" s="216"/>
-      <c r="J130" s="216"/>
-      <c r="K130" s="216"/>
-      <c r="L130" s="216"/>
-      <c r="M130" s="216"/>
-      <c r="N130" s="216"/>
+      <c r="C130" s="212"/>
+      <c r="D130" s="212"/>
+      <c r="E130" s="212"/>
+      <c r="F130" s="212"/>
+      <c r="G130" s="212"/>
+      <c r="H130" s="212"/>
+      <c r="I130" s="212"/>
+      <c r="J130" s="212"/>
+      <c r="K130" s="212"/>
+      <c r="L130" s="212"/>
+      <c r="M130" s="212"/>
+      <c r="N130" s="212"/>
     </row>
     <row r="131" spans="3:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C131" s="87"/>
@@ -11446,118 +11453,118 @@
       <c r="N131" s="87"/>
     </row>
     <row r="132" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C132" s="216" t="s">
+      <c r="C132" s="212" t="s">
         <v>268</v>
       </c>
-      <c r="D132" s="216"/>
-      <c r="E132" s="216"/>
-      <c r="F132" s="216"/>
-      <c r="G132" s="216"/>
-      <c r="H132" s="216"/>
-      <c r="I132" s="216"/>
-      <c r="J132" s="216"/>
-      <c r="K132" s="216"/>
-      <c r="L132" s="216"/>
-      <c r="M132" s="216"/>
-      <c r="N132" s="216"/>
+      <c r="D132" s="212"/>
+      <c r="E132" s="212"/>
+      <c r="F132" s="212"/>
+      <c r="G132" s="212"/>
+      <c r="H132" s="212"/>
+      <c r="I132" s="212"/>
+      <c r="J132" s="212"/>
+      <c r="K132" s="212"/>
+      <c r="L132" s="212"/>
+      <c r="M132" s="212"/>
+      <c r="N132" s="212"/>
     </row>
     <row r="133" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C133" s="216"/>
-      <c r="D133" s="216"/>
-      <c r="E133" s="216"/>
-      <c r="F133" s="216"/>
-      <c r="G133" s="216"/>
-      <c r="H133" s="216"/>
-      <c r="I133" s="216"/>
-      <c r="J133" s="216"/>
-      <c r="K133" s="216"/>
-      <c r="L133" s="216"/>
-      <c r="M133" s="216"/>
-      <c r="N133" s="216"/>
+      <c r="C133" s="212"/>
+      <c r="D133" s="212"/>
+      <c r="E133" s="212"/>
+      <c r="F133" s="212"/>
+      <c r="G133" s="212"/>
+      <c r="H133" s="212"/>
+      <c r="I133" s="212"/>
+      <c r="J133" s="212"/>
+      <c r="K133" s="212"/>
+      <c r="L133" s="212"/>
+      <c r="M133" s="212"/>
+      <c r="N133" s="212"/>
     </row>
     <row r="134" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C134" s="216"/>
-      <c r="D134" s="216"/>
-      <c r="E134" s="216"/>
-      <c r="F134" s="216"/>
-      <c r="G134" s="216"/>
-      <c r="H134" s="216"/>
-      <c r="I134" s="216"/>
-      <c r="J134" s="216"/>
-      <c r="K134" s="216"/>
-      <c r="L134" s="216"/>
-      <c r="M134" s="216"/>
-      <c r="N134" s="216"/>
+      <c r="C134" s="212"/>
+      <c r="D134" s="212"/>
+      <c r="E134" s="212"/>
+      <c r="F134" s="212"/>
+      <c r="G134" s="212"/>
+      <c r="H134" s="212"/>
+      <c r="I134" s="212"/>
+      <c r="J134" s="212"/>
+      <c r="K134" s="212"/>
+      <c r="L134" s="212"/>
+      <c r="M134" s="212"/>
+      <c r="N134" s="212"/>
     </row>
     <row r="135" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C135" s="216"/>
-      <c r="D135" s="216"/>
-      <c r="E135" s="216"/>
-      <c r="F135" s="216"/>
-      <c r="G135" s="216"/>
-      <c r="H135" s="216"/>
-      <c r="I135" s="216"/>
-      <c r="J135" s="216"/>
-      <c r="K135" s="216"/>
-      <c r="L135" s="216"/>
-      <c r="M135" s="216"/>
-      <c r="N135" s="216"/>
+      <c r="C135" s="212"/>
+      <c r="D135" s="212"/>
+      <c r="E135" s="212"/>
+      <c r="F135" s="212"/>
+      <c r="G135" s="212"/>
+      <c r="H135" s="212"/>
+      <c r="I135" s="212"/>
+      <c r="J135" s="212"/>
+      <c r="K135" s="212"/>
+      <c r="L135" s="212"/>
+      <c r="M135" s="212"/>
+      <c r="N135" s="212"/>
     </row>
     <row r="136" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C136" s="216"/>
-      <c r="D136" s="216"/>
-      <c r="E136" s="216"/>
-      <c r="F136" s="216"/>
-      <c r="G136" s="216"/>
-      <c r="H136" s="216"/>
-      <c r="I136" s="216"/>
-      <c r="J136" s="216"/>
-      <c r="K136" s="216"/>
-      <c r="L136" s="216"/>
-      <c r="M136" s="216"/>
-      <c r="N136" s="216"/>
+      <c r="C136" s="212"/>
+      <c r="D136" s="212"/>
+      <c r="E136" s="212"/>
+      <c r="F136" s="212"/>
+      <c r="G136" s="212"/>
+      <c r="H136" s="212"/>
+      <c r="I136" s="212"/>
+      <c r="J136" s="212"/>
+      <c r="K136" s="212"/>
+      <c r="L136" s="212"/>
+      <c r="M136" s="212"/>
+      <c r="N136" s="212"/>
     </row>
     <row r="137" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C137" s="216"/>
-      <c r="D137" s="216"/>
-      <c r="E137" s="216"/>
-      <c r="F137" s="216"/>
-      <c r="G137" s="216"/>
-      <c r="H137" s="216"/>
-      <c r="I137" s="216"/>
-      <c r="J137" s="216"/>
-      <c r="K137" s="216"/>
-      <c r="L137" s="216"/>
-      <c r="M137" s="216"/>
-      <c r="N137" s="216"/>
+      <c r="C137" s="212"/>
+      <c r="D137" s="212"/>
+      <c r="E137" s="212"/>
+      <c r="F137" s="212"/>
+      <c r="G137" s="212"/>
+      <c r="H137" s="212"/>
+      <c r="I137" s="212"/>
+      <c r="J137" s="212"/>
+      <c r="K137" s="212"/>
+      <c r="L137" s="212"/>
+      <c r="M137" s="212"/>
+      <c r="N137" s="212"/>
     </row>
     <row r="138" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C138" s="216"/>
-      <c r="D138" s="216"/>
-      <c r="E138" s="216"/>
-      <c r="F138" s="216"/>
-      <c r="G138" s="216"/>
-      <c r="H138" s="216"/>
-      <c r="I138" s="216"/>
-      <c r="J138" s="216"/>
-      <c r="K138" s="216"/>
-      <c r="L138" s="216"/>
-      <c r="M138" s="216"/>
-      <c r="N138" s="216"/>
+      <c r="C138" s="212"/>
+      <c r="D138" s="212"/>
+      <c r="E138" s="212"/>
+      <c r="F138" s="212"/>
+      <c r="G138" s="212"/>
+      <c r="H138" s="212"/>
+      <c r="I138" s="212"/>
+      <c r="J138" s="212"/>
+      <c r="K138" s="212"/>
+      <c r="L138" s="212"/>
+      <c r="M138" s="212"/>
+      <c r="N138" s="212"/>
     </row>
     <row r="139" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C139" s="216"/>
-      <c r="D139" s="216"/>
-      <c r="E139" s="216"/>
-      <c r="F139" s="216"/>
-      <c r="G139" s="216"/>
-      <c r="H139" s="216"/>
-      <c r="I139" s="216"/>
-      <c r="J139" s="216"/>
-      <c r="K139" s="216"/>
-      <c r="L139" s="216"/>
-      <c r="M139" s="216"/>
-      <c r="N139" s="216"/>
+      <c r="C139" s="212"/>
+      <c r="D139" s="212"/>
+      <c r="E139" s="212"/>
+      <c r="F139" s="212"/>
+      <c r="G139" s="212"/>
+      <c r="H139" s="212"/>
+      <c r="I139" s="212"/>
+      <c r="J139" s="212"/>
+      <c r="K139" s="212"/>
+      <c r="L139" s="212"/>
+      <c r="M139" s="212"/>
+      <c r="N139" s="212"/>
     </row>
     <row r="140" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C140" s="87"/>
@@ -11588,111 +11595,117 @@
       <c r="N141" s="87"/>
     </row>
     <row r="142" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C142" s="215" t="s">
+      <c r="C142" s="211" t="s">
         <v>267</v>
       </c>
-      <c r="D142" s="215"/>
-      <c r="E142" s="215"/>
-      <c r="F142" s="215"/>
-      <c r="G142" s="215"/>
-      <c r="H142" s="215"/>
-      <c r="I142" s="215"/>
-      <c r="J142" s="215"/>
-      <c r="K142" s="215"/>
-      <c r="L142" s="215"/>
-      <c r="M142" s="215"/>
-      <c r="N142" s="215"/>
+      <c r="D142" s="211"/>
+      <c r="E142" s="211"/>
+      <c r="F142" s="211"/>
+      <c r="G142" s="211"/>
+      <c r="H142" s="211"/>
+      <c r="I142" s="211"/>
+      <c r="J142" s="211"/>
+      <c r="K142" s="211"/>
+      <c r="L142" s="211"/>
+      <c r="M142" s="211"/>
+      <c r="N142" s="211"/>
     </row>
     <row r="143" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C143" s="215"/>
-      <c r="D143" s="215"/>
-      <c r="E143" s="215"/>
-      <c r="F143" s="215"/>
-      <c r="G143" s="215"/>
-      <c r="H143" s="215"/>
-      <c r="I143" s="215"/>
-      <c r="J143" s="215"/>
-      <c r="K143" s="215"/>
-      <c r="L143" s="215"/>
-      <c r="M143" s="215"/>
-      <c r="N143" s="215"/>
+      <c r="C143" s="211"/>
+      <c r="D143" s="211"/>
+      <c r="E143" s="211"/>
+      <c r="F143" s="211"/>
+      <c r="G143" s="211"/>
+      <c r="H143" s="211"/>
+      <c r="I143" s="211"/>
+      <c r="J143" s="211"/>
+      <c r="K143" s="211"/>
+      <c r="L143" s="211"/>
+      <c r="M143" s="211"/>
+      <c r="N143" s="211"/>
     </row>
     <row r="144" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C144" s="215"/>
-      <c r="D144" s="215"/>
-      <c r="E144" s="215"/>
-      <c r="F144" s="215"/>
-      <c r="G144" s="215"/>
-      <c r="H144" s="215"/>
-      <c r="I144" s="215"/>
-      <c r="J144" s="215"/>
-      <c r="K144" s="215"/>
-      <c r="L144" s="215"/>
-      <c r="M144" s="215"/>
-      <c r="N144" s="215"/>
+      <c r="C144" s="211"/>
+      <c r="D144" s="211"/>
+      <c r="E144" s="211"/>
+      <c r="F144" s="211"/>
+      <c r="G144" s="211"/>
+      <c r="H144" s="211"/>
+      <c r="I144" s="211"/>
+      <c r="J144" s="211"/>
+      <c r="K144" s="211"/>
+      <c r="L144" s="211"/>
+      <c r="M144" s="211"/>
+      <c r="N144" s="211"/>
       <c r="P144" s="95">
         <f>L1-K127</f>
         <v>-1973730.177240001</v>
       </c>
     </row>
     <row r="145" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C145" s="215"/>
-      <c r="D145" s="215"/>
-      <c r="E145" s="215"/>
-      <c r="F145" s="215"/>
-      <c r="G145" s="215"/>
-      <c r="H145" s="215"/>
-      <c r="I145" s="215"/>
-      <c r="J145" s="215"/>
-      <c r="K145" s="215"/>
-      <c r="L145" s="215"/>
-      <c r="M145" s="215"/>
-      <c r="N145" s="215"/>
+      <c r="C145" s="211"/>
+      <c r="D145" s="211"/>
+      <c r="E145" s="211"/>
+      <c r="F145" s="211"/>
+      <c r="G145" s="211"/>
+      <c r="H145" s="211"/>
+      <c r="I145" s="211"/>
+      <c r="J145" s="211"/>
+      <c r="K145" s="211"/>
+      <c r="L145" s="211"/>
+      <c r="M145" s="211"/>
+      <c r="N145" s="211"/>
     </row>
     <row r="146" spans="3:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C146" s="215"/>
-      <c r="D146" s="215"/>
-      <c r="E146" s="215"/>
-      <c r="F146" s="215"/>
-      <c r="G146" s="215"/>
-      <c r="H146" s="215"/>
-      <c r="I146" s="215"/>
-      <c r="J146" s="215"/>
-      <c r="K146" s="215"/>
-      <c r="L146" s="215"/>
-      <c r="M146" s="215"/>
-      <c r="N146" s="215"/>
+      <c r="C146" s="211"/>
+      <c r="D146" s="211"/>
+      <c r="E146" s="211"/>
+      <c r="F146" s="211"/>
+      <c r="G146" s="211"/>
+      <c r="H146" s="211"/>
+      <c r="I146" s="211"/>
+      <c r="J146" s="211"/>
+      <c r="K146" s="211"/>
+      <c r="L146" s="211"/>
+      <c r="M146" s="211"/>
+      <c r="N146" s="211"/>
     </row>
     <row r="147" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C147" s="215"/>
-      <c r="D147" s="215"/>
-      <c r="E147" s="215"/>
-      <c r="F147" s="215"/>
-      <c r="G147" s="215"/>
-      <c r="H147" s="215"/>
-      <c r="I147" s="215"/>
-      <c r="J147" s="215"/>
-      <c r="K147" s="215"/>
-      <c r="L147" s="215"/>
-      <c r="M147" s="215"/>
-      <c r="N147" s="215"/>
+      <c r="C147" s="211"/>
+      <c r="D147" s="211"/>
+      <c r="E147" s="211"/>
+      <c r="F147" s="211"/>
+      <c r="G147" s="211"/>
+      <c r="H147" s="211"/>
+      <c r="I147" s="211"/>
+      <c r="J147" s="211"/>
+      <c r="K147" s="211"/>
+      <c r="L147" s="211"/>
+      <c r="M147" s="211"/>
+      <c r="N147" s="211"/>
     </row>
     <row r="148" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C148" s="215"/>
-      <c r="D148" s="215"/>
-      <c r="E148" s="215"/>
-      <c r="F148" s="215"/>
-      <c r="G148" s="215"/>
-      <c r="H148" s="215"/>
-      <c r="I148" s="215"/>
-      <c r="J148" s="215"/>
-      <c r="K148" s="215"/>
-      <c r="L148" s="215"/>
-      <c r="M148" s="215"/>
-      <c r="N148" s="215"/>
+      <c r="C148" s="211"/>
+      <c r="D148" s="211"/>
+      <c r="E148" s="211"/>
+      <c r="F148" s="211"/>
+      <c r="G148" s="211"/>
+      <c r="H148" s="211"/>
+      <c r="I148" s="211"/>
+      <c r="J148" s="211"/>
+      <c r="K148" s="211"/>
+      <c r="L148" s="211"/>
+      <c r="M148" s="211"/>
+      <c r="N148" s="211"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="E5:E7"/>
     <mergeCell ref="Q8:R9"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="C142:N148"/>
@@ -11706,12 +11719,6 @@
     <mergeCell ref="C132:N139"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="E5:E7"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/EL MIRADOR/Agosto/Agosto - EL MIRADOR .xlsx
+++ b/EL MIRADOR/Agosto/Agosto - EL MIRADOR .xlsx
@@ -1,33 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\EL MIRADOR\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\EL MIRADOR\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345ED8AF-F522-470C-B222-8C9EC439FBF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9889540F-8C50-49A6-BAB7-AF9CBD8EFB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
     <sheet name="ANOTACIONES" sheetId="3" r:id="rId3"/>
-    <sheet name="Hoja1" sheetId="4" r:id="rId4"/>
+    <sheet name="SUELDOS" sheetId="5" r:id="rId4"/>
+    <sheet name="Hoja1" sheetId="4" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$149</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$147</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">SUELDOS!$A$3:$J$27</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="342">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1045,6 +1050,15 @@
   </si>
   <si>
     <t>No tiene que tener deuda</t>
+  </si>
+  <si>
+    <t>Firma</t>
+  </si>
+  <si>
+    <t>__________________________________</t>
+  </si>
+  <si>
+    <t>Aclaracion</t>
   </si>
 </sst>
 </file>
@@ -1052,14 +1066,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -1649,11 +1663,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="228">
+  <cellXfs count="239">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1662,7 +1676,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1670,95 +1684,95 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1767,19 +1781,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="17" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1788,8 +1802,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1803,12 +1817,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="8" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="8" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1819,7 +1833,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1831,12 +1845,12 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1846,22 +1860,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="11" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1870,29 +1884,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="11" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="15" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1941,10 +1962,10 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1980,10 +2001,24 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2118,6 +2153,39 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="RESUMEN"/>
+      <sheetName val="PRORRATEO"/>
+      <sheetName val="ANOTACIONES"/>
+      <sheetName val="SUELDOS"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="22">
+          <cell r="A22" t="str">
+            <v xml:space="preserve">Sueldo encargada Sonia Arzamendia Galeano </v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>Sueldo encargada Miriam</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2408,23 +2476,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R157"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="129"/>
       <c r="B1" s="139"/>
       <c r="C1" s="149" t="s">
@@ -2438,7 +2506,7 @@
       <c r="I1" s="127"/>
       <c r="J1" s="128"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="130"/>
       <c r="B2" s="140"/>
       <c r="C2" s="140" t="s">
@@ -2452,7 +2520,7 @@
       <c r="I2" s="141"/>
       <c r="J2" s="126"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="130"/>
       <c r="B3" s="140"/>
       <c r="C3" s="140" t="s">
@@ -2468,7 +2536,7 @@
       <c r="I3" s="141"/>
       <c r="J3" s="126"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="130"/>
       <c r="B4" s="140"/>
       <c r="C4" s="140" t="s">
@@ -2482,7 +2550,7 @@
       <c r="I4" s="141"/>
       <c r="J4" s="126"/>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="135"/>
       <c r="B5" s="140"/>
       <c r="C5" s="140" t="s">
@@ -2498,7 +2566,7 @@
       <c r="I5" s="140"/>
       <c r="J5" s="136"/>
     </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="135"/>
       <c r="B6" s="140"/>
       <c r="C6" s="140" t="s">
@@ -2512,7 +2580,7 @@
       <c r="I6" s="140"/>
       <c r="J6" s="136"/>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="137"/>
       <c r="B7" s="138"/>
       <c r="C7" s="138"/>
@@ -2524,118 +2592,118 @@
       <c r="I7" s="138"/>
       <c r="J7" s="142"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="197" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="204" t="s">
         <v>268</v>
       </c>
-      <c r="B14" s="197"/>
-      <c r="C14" s="197"/>
-      <c r="D14" s="197"/>
-      <c r="E14" s="197"/>
-      <c r="F14" s="197"/>
-      <c r="G14" s="197"/>
-      <c r="H14" s="197"/>
-      <c r="I14" s="197"/>
-      <c r="J14" s="197"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="197"/>
-      <c r="B15" s="197"/>
-      <c r="C15" s="197"/>
-      <c r="D15" s="197"/>
-      <c r="E15" s="197"/>
-      <c r="F15" s="197"/>
-      <c r="G15" s="197"/>
-      <c r="H15" s="197"/>
-      <c r="I15" s="197"/>
-      <c r="J15" s="197"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="197"/>
-      <c r="B16" s="197"/>
-      <c r="C16" s="197"/>
-      <c r="D16" s="197"/>
-      <c r="E16" s="197"/>
-      <c r="F16" s="197"/>
-      <c r="G16" s="197"/>
-      <c r="H16" s="197"/>
-      <c r="I16" s="197"/>
-      <c r="J16" s="197"/>
-    </row>
-    <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="197"/>
-      <c r="B17" s="197"/>
-      <c r="C17" s="197"/>
-      <c r="D17" s="197"/>
-      <c r="E17" s="197"/>
-      <c r="F17" s="197"/>
-      <c r="G17" s="197"/>
-      <c r="H17" s="197"/>
-      <c r="I17" s="197"/>
-      <c r="J17" s="197"/>
-    </row>
-    <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="197"/>
-      <c r="B18" s="197"/>
-      <c r="C18" s="197"/>
-      <c r="D18" s="197"/>
-      <c r="E18" s="197"/>
-      <c r="F18" s="197"/>
-      <c r="G18" s="197"/>
-      <c r="H18" s="197"/>
-      <c r="I18" s="197"/>
-      <c r="J18" s="197"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="204"/>
+      <c r="C14" s="204"/>
+      <c r="D14" s="204"/>
+      <c r="E14" s="204"/>
+      <c r="F14" s="204"/>
+      <c r="G14" s="204"/>
+      <c r="H14" s="204"/>
+      <c r="I14" s="204"/>
+      <c r="J14" s="204"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="204"/>
+      <c r="B15" s="204"/>
+      <c r="C15" s="204"/>
+      <c r="D15" s="204"/>
+      <c r="E15" s="204"/>
+      <c r="F15" s="204"/>
+      <c r="G15" s="204"/>
+      <c r="H15" s="204"/>
+      <c r="I15" s="204"/>
+      <c r="J15" s="204"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="204"/>
+      <c r="B16" s="204"/>
+      <c r="C16" s="204"/>
+      <c r="D16" s="204"/>
+      <c r="E16" s="204"/>
+      <c r="F16" s="204"/>
+      <c r="G16" s="204"/>
+      <c r="H16" s="204"/>
+      <c r="I16" s="204"/>
+      <c r="J16" s="204"/>
+    </row>
+    <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="204"/>
+      <c r="B17" s="204"/>
+      <c r="C17" s="204"/>
+      <c r="D17" s="204"/>
+      <c r="E17" s="204"/>
+      <c r="F17" s="204"/>
+      <c r="G17" s="204"/>
+      <c r="H17" s="204"/>
+      <c r="I17" s="204"/>
+      <c r="J17" s="204"/>
+    </row>
+    <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="204"/>
+      <c r="B18" s="204"/>
+      <c r="C18" s="204"/>
+      <c r="D18" s="204"/>
+      <c r="E18" s="204"/>
+      <c r="F18" s="204"/>
+      <c r="G18" s="204"/>
+      <c r="H18" s="204"/>
+      <c r="I18" s="204"/>
+      <c r="J18" s="204"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="H19" s="111"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="207" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="214" t="s">
         <v>306</v>
       </c>
-      <c r="B20" s="207"/>
-      <c r="C20" s="207"/>
-      <c r="D20" s="207"/>
-      <c r="E20" s="207"/>
-      <c r="F20" s="207"/>
-      <c r="G20" s="207"/>
-      <c r="H20" s="207"/>
-      <c r="I20" s="207"/>
-      <c r="J20" s="207"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="207"/>
-      <c r="B21" s="207"/>
-      <c r="C21" s="207"/>
-      <c r="D21" s="207"/>
-      <c r="E21" s="207"/>
-      <c r="F21" s="207"/>
-      <c r="G21" s="207"/>
-      <c r="H21" s="207"/>
-      <c r="I21" s="207"/>
-      <c r="J21" s="207"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="207"/>
-      <c r="B22" s="207"/>
-      <c r="C22" s="207"/>
-      <c r="D22" s="207"/>
-      <c r="E22" s="207"/>
-      <c r="F22" s="207"/>
-      <c r="G22" s="207"/>
-      <c r="H22" s="207"/>
-      <c r="I22" s="207"/>
-      <c r="J22" s="207"/>
-    </row>
-    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="214"/>
+      <c r="C20" s="214"/>
+      <c r="D20" s="214"/>
+      <c r="E20" s="214"/>
+      <c r="F20" s="214"/>
+      <c r="G20" s="214"/>
+      <c r="H20" s="214"/>
+      <c r="I20" s="214"/>
+      <c r="J20" s="214"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="214"/>
+      <c r="B21" s="214"/>
+      <c r="C21" s="214"/>
+      <c r="D21" s="214"/>
+      <c r="E21" s="214"/>
+      <c r="F21" s="214"/>
+      <c r="G21" s="214"/>
+      <c r="H21" s="214"/>
+      <c r="I21" s="214"/>
+      <c r="J21" s="214"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="214"/>
+      <c r="B22" s="214"/>
+      <c r="C22" s="214"/>
+      <c r="D22" s="214"/>
+      <c r="E22" s="214"/>
+      <c r="F22" s="214"/>
+      <c r="G22" s="214"/>
+      <c r="H22" s="214"/>
+      <c r="I22" s="214"/>
+      <c r="J22" s="214"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="111"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
         <v>20</v>
       </c>
@@ -2661,7 +2729,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="51" t="s">
         <v>240</v>
       </c>
@@ -2675,7 +2743,7 @@
       <c r="I25" s="112"/>
       <c r="J25" s="112"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>46</v>
       </c>
@@ -2691,7 +2759,7 @@
       <c r="I26" s="63"/>
       <c r="J26" s="63"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>243</v>
       </c>
@@ -2707,7 +2775,7 @@
       <c r="I27" s="63"/>
       <c r="J27" s="63"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>241</v>
       </c>
@@ -2723,7 +2791,7 @@
       <c r="I28" s="63"/>
       <c r="J28" s="63"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>242</v>
       </c>
@@ -2739,7 +2807,7 @@
       <c r="I29" s="63"/>
       <c r="J29" s="63"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>244</v>
       </c>
@@ -2755,7 +2823,7 @@
       <c r="I30" s="63"/>
       <c r="J30" s="63"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="110" t="s">
         <v>172</v>
       </c>
@@ -2772,7 +2840,7 @@
       <c r="I31" s="109"/>
       <c r="J31" s="109"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="51" t="s">
         <v>239</v>
       </c>
@@ -2786,7 +2854,7 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>46</v>
       </c>
@@ -2802,7 +2870,7 @@
       <c r="I33" s="63"/>
       <c r="J33" s="63"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>337</v>
       </c>
@@ -2819,7 +2887,7 @@
       <c r="I34" s="63"/>
       <c r="J34" s="63"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>243</v>
       </c>
@@ -2835,7 +2903,7 @@
       <c r="I35" s="63"/>
       <c r="J35" s="63"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>241</v>
       </c>
@@ -2851,7 +2919,7 @@
       <c r="I36" s="63"/>
       <c r="J36" s="63"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>242</v>
       </c>
@@ -2867,7 +2935,7 @@
       <c r="I37" s="63"/>
       <c r="J37" s="63"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>244</v>
       </c>
@@ -2883,7 +2951,7 @@
       <c r="I38" s="63"/>
       <c r="J38" s="63"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="110" t="s">
         <v>172</v>
       </c>
@@ -2900,7 +2968,7 @@
       <c r="I39" s="109"/>
       <c r="J39" s="109"/>
     </row>
-    <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="34" t="s">
         <v>1</v>
       </c>
@@ -2943,7 +3011,7 @@
         <v>1336846.7999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="33" t="s">
         <v>35</v>
       </c>
@@ -2966,7 +3034,7 @@
       </c>
       <c r="L41" s="74"/>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -2987,7 +3055,7 @@
       </c>
       <c r="L42" s="74"/>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -3000,7 +3068,7 @@
       <c r="J43" s="6"/>
       <c r="L43" s="74"/>
     </row>
-    <row r="44" spans="1:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="33"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -3013,7 +3081,7 @@
       <c r="J44" s="6"/>
       <c r="L44" s="74"/>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="34" t="s">
         <v>41</v>
       </c>
@@ -3044,7 +3112,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="33" t="s">
         <v>255</v>
       </c>
@@ -3065,7 +3133,7 @@
       </c>
       <c r="L46" s="74"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>256</v>
       </c>
@@ -3087,7 +3155,7 @@
       <c r="J47" s="63"/>
       <c r="L47" s="74"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>256</v>
       </c>
@@ -3109,7 +3177,7 @@
       <c r="J48" s="63"/>
       <c r="L48" s="74"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>256</v>
       </c>
@@ -3131,7 +3199,7 @@
       <c r="J49" s="63"/>
       <c r="L49" s="74"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -3147,7 +3215,7 @@
       <c r="J50" s="63"/>
       <c r="L50" s="74"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -3163,7 +3231,7 @@
       <c r="J51" s="63"/>
       <c r="L51" s="74"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="33"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -3182,7 +3250,7 @@
       </c>
       <c r="L52" s="74"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="34" t="s">
         <v>36</v>
       </c>
@@ -3210,7 +3278,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="33" t="s">
         <v>249</v>
       </c>
@@ -3225,7 +3293,7 @@
       <c r="J54" s="50"/>
       <c r="L54" s="74"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="36" t="s">
         <v>252</v>
       </c>
@@ -3244,7 +3312,7 @@
       <c r="J55" s="50"/>
       <c r="L55" s="74"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="36" t="s">
         <v>254</v>
       </c>
@@ -3263,7 +3331,7 @@
       <c r="J56" s="50"/>
       <c r="L56" s="74"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="36" t="s">
         <v>253</v>
       </c>
@@ -3283,7 +3351,7 @@
       <c r="J57" s="50"/>
       <c r="L57" s="74"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="34" t="s">
         <v>251</v>
       </c>
@@ -3326,7 +3394,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="33" t="s">
         <v>2</v>
       </c>
@@ -3341,7 +3409,7 @@
       <c r="J59" s="6"/>
       <c r="L59" s="74"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>245</v>
       </c>
@@ -3360,7 +3428,7 @@
       <c r="J60" s="6"/>
       <c r="L60" s="74"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>303</v>
       </c>
@@ -3379,7 +3447,7 @@
       <c r="J61" s="6"/>
       <c r="L61" s="74"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="34" t="s">
         <v>250</v>
       </c>
@@ -3422,7 +3490,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="33" t="s">
         <v>232</v>
       </c>
@@ -3437,7 +3505,7 @@
       <c r="J63" s="37"/>
       <c r="L63" s="74"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>236</v>
       </c>
@@ -3478,7 +3546,7 @@
       </c>
       <c r="L64" s="74"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>237</v>
       </c>
@@ -3519,7 +3587,7 @@
       </c>
       <c r="L65" s="74"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>238</v>
       </c>
@@ -3560,7 +3628,7 @@
       </c>
       <c r="L66" s="74"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="34" t="s">
         <v>3</v>
       </c>
@@ -3603,7 +3671,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="33" t="s">
         <v>4</v>
       </c>
@@ -3618,7 +3686,7 @@
       <c r="J68" s="6"/>
       <c r="L68" s="74"/>
     </row>
-    <row r="69" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="79" t="s">
         <v>246</v>
       </c>
@@ -3668,7 +3736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>247</v>
       </c>
@@ -3720,7 +3788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>248</v>
       </c>
@@ -3757,7 +3825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>308</v>
       </c>
@@ -3788,7 +3856,7 @@
       <c r="M72" s="95"/>
       <c r="N72" s="95"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="36" t="s">
         <v>310</v>
       </c>
@@ -3825,7 +3893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="36" t="s">
         <v>310</v>
       </c>
@@ -3856,7 +3924,7 @@
       <c r="M74" s="95"/>
       <c r="N74" s="95"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="36" t="s">
         <v>287</v>
       </c>
@@ -3908,7 +3976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="36" t="s">
         <v>288</v>
       </c>
@@ -3960,7 +4028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="79" t="s">
         <v>286</v>
       </c>
@@ -3995,7 +4063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="172"/>
       <c r="B78" s="172"/>
       <c r="C78" s="173"/>
@@ -4026,7 +4094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="79"/>
       <c r="B79" s="80"/>
       <c r="C79" s="80"/>
@@ -4044,7 +4112,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="34" t="s">
         <v>5</v>
       </c>
@@ -4091,7 +4159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -4104,7 +4172,7 @@
       <c r="J81" s="6"/>
       <c r="L81" s="74"/>
     </row>
-    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -4117,7 +4185,7 @@
       <c r="J82" s="6"/>
       <c r="L82" s="74"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="33" t="s">
         <v>233</v>
       </c>
@@ -4132,7 +4200,7 @@
       <c r="J83" s="6"/>
       <c r="L83" s="74"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>309</v>
       </c>
@@ -4168,7 +4236,7 @@
       <c r="K84" s="82"/>
       <c r="L84" s="74"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="36"/>
       <c r="C85" s="6"/>
@@ -4182,7 +4250,7 @@
       <c r="K85" s="82"/>
       <c r="L85" s="74"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="36"/>
       <c r="C86" s="6"/>
@@ -4196,7 +4264,7 @@
       <c r="K86" s="82"/>
       <c r="L86" s="74"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="36"/>
       <c r="C87" s="6"/>
@@ -4210,7 +4278,7 @@
       <c r="K87" s="82"/>
       <c r="L87" s="74"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="36"/>
       <c r="C88" s="6"/>
@@ -4224,7 +4292,7 @@
       <c r="K88" s="82"/>
       <c r="L88" s="74"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -4238,7 +4306,7 @@
       <c r="L89" s="74"/>
       <c r="M89" s="44"/>
     </row>
-    <row r="90" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="34" t="s">
         <v>234</v>
       </c>
@@ -4282,7 +4350,7 @@
       </c>
       <c r="N90" s="44"/>
     </row>
-    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -4295,7 +4363,7 @@
       <c r="J91" s="6"/>
       <c r="L91" s="74"/>
     </row>
-    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -4308,7 +4376,7 @@
       <c r="J92" s="6"/>
       <c r="L92" s="74"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="33" t="s">
         <v>6</v>
       </c>
@@ -4323,7 +4391,7 @@
       <c r="J93" s="6"/>
       <c r="L93" s="74"/>
     </row>
-    <row r="94" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
         <v>7</v>
       </c>
@@ -4360,7 +4428,7 @@
       </c>
       <c r="L94" s="74"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="33"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -4374,7 +4442,7 @@
       <c r="L95" s="74"/>
       <c r="N95" s="45"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -4388,7 +4456,7 @@
       <c r="L96" s="74"/>
       <c r="N96" s="44"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="34" t="s">
         <v>8</v>
       </c>
@@ -4432,7 +4500,7 @@
       </c>
       <c r="N97" s="44"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
         <v>29</v>
       </c>
@@ -4467,7 +4535,7 @@
       </c>
       <c r="L98" s="74"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
         <v>30</v>
       </c>
@@ -4502,7 +4570,7 @@
       </c>
       <c r="L99" s="74"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="34" t="s">
         <v>235</v>
       </c>
@@ -4545,7 +4613,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="115"/>
       <c r="B101" s="115"/>
       <c r="C101" s="115"/>
@@ -4558,7 +4626,7 @@
       <c r="J101" s="115"/>
       <c r="L101" s="74"/>
     </row>
-    <row r="102" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="117" t="s">
         <v>47</v>
       </c>
@@ -4600,7 +4668,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="120"/>
       <c r="B103" s="121"/>
       <c r="C103" s="121"/>
@@ -4614,7 +4682,7 @@
       <c r="K103" s="44"/>
       <c r="L103" s="74"/>
     </row>
-    <row r="104" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
         <v>31</v>
       </c>
@@ -4661,7 +4729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D105" s="98"/>
       <c r="E105" s="44"/>
       <c r="F105" s="44"/>
@@ -4669,7 +4737,7 @@
       <c r="H105" s="44"/>
       <c r="I105" s="44"/>
     </row>
-    <row r="106" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="69" t="s">
         <v>42</v>
       </c>
@@ -4681,7 +4749,7 @@
       <c r="H106" s="44"/>
       <c r="I106" s="44"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>333</v>
       </c>
@@ -4694,7 +4762,7 @@
       <c r="H107" s="44"/>
       <c r="I107" s="44"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>334</v>
       </c>
@@ -4707,7 +4775,7 @@
       <c r="H108" s="44"/>
       <c r="I108" s="44"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="C109" s="148"/>
       <c r="E109" s="44"/>
@@ -4716,7 +4784,7 @@
       <c r="H109" s="44"/>
       <c r="I109" s="44"/>
     </row>
-    <row r="110" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1"/>
       <c r="C110" s="148"/>
       <c r="E110" s="44"/>
@@ -4725,7 +4793,7 @@
       <c r="H110" s="44"/>
       <c r="I110" s="44"/>
     </row>
-    <row r="111" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="70" t="s">
         <v>18</v>
       </c>
@@ -4740,27 +4808,27 @@
       <c r="H111" s="44"/>
       <c r="I111" s="44"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E112" s="44"/>
       <c r="F112" s="44"/>
       <c r="G112" s="44"/>
       <c r="H112" s="44"/>
       <c r="I112" s="44"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E113" s="65"/>
       <c r="F113" s="65"/>
       <c r="G113" s="65"/>
       <c r="H113" s="65"/>
       <c r="I113" s="65"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A114" s="203" t="s">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A114" s="210" t="s">
         <v>37</v>
       </c>
-      <c r="B114" s="204"/>
-      <c r="C114" s="204"/>
-      <c r="D114" s="204"/>
+      <c r="B114" s="211"/>
+      <c r="C114" s="211"/>
+      <c r="D114" s="211"/>
       <c r="E114" s="90" t="s">
         <v>12</v>
       </c>
@@ -4780,9 +4848,9 @@
         <v>178</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="205"/>
-      <c r="B115" s="206"/>
+    <row r="115" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="212"/>
+      <c r="B115" s="213"/>
       <c r="C115" s="92"/>
       <c r="D115" s="45"/>
       <c r="E115" s="73">
@@ -4795,9 +4863,9 @@
       <c r="I115" s="73"/>
       <c r="J115" s="63"/>
     </row>
-    <row r="116" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="205"/>
-      <c r="B116" s="206"/>
+    <row r="116" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="212"/>
+      <c r="B116" s="213"/>
       <c r="C116" s="92"/>
       <c r="D116" s="45"/>
       <c r="E116" s="73"/>
@@ -4807,12 +4875,12 @@
       <c r="I116" s="73"/>
       <c r="J116" s="63"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="200" t="s">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A117" s="207" t="s">
         <v>18</v>
       </c>
-      <c r="B117" s="201"/>
-      <c r="C117" s="202"/>
+      <c r="B117" s="208"/>
+      <c r="C117" s="209"/>
       <c r="D117" s="89">
         <f>SUM(D115:D116)</f>
         <v>0</v>
@@ -4838,14 +4906,14 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E119" s="44"/>
       <c r="F119" s="44"/>
       <c r="G119" s="44"/>
       <c r="H119" s="44"/>
       <c r="I119" s="44"/>
     </row>
-    <row r="120" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="39" t="s">
         <v>32</v>
       </c>
@@ -4854,7 +4922,7 @@
         <v>8437168.6099999994</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="41" t="s">
         <v>34</v>
       </c>
@@ -4863,28 +4931,28 @@
         <v>6937168.6099999994</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D122" s="199"/>
-      <c r="E122" s="199"/>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D122" s="206"/>
+      <c r="E122" s="206"/>
       <c r="F122" s="102"/>
       <c r="G122" s="102"/>
       <c r="H122" s="102"/>
       <c r="I122" s="102"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="17" t="s">
         <v>21</v>
       </c>
       <c r="B123" s="18"/>
       <c r="C123" s="19"/>
-      <c r="D123" s="199"/>
-      <c r="E123" s="199"/>
+      <c r="D123" s="206"/>
+      <c r="E123" s="206"/>
       <c r="F123" s="102"/>
       <c r="G123" s="102"/>
       <c r="H123" s="102"/>
       <c r="I123" s="102"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="20" t="s">
         <v>22</v>
       </c>
@@ -4892,14 +4960,14 @@
         <v>-1480823.9566400023</v>
       </c>
       <c r="C124" s="21"/>
-      <c r="D124" s="199"/>
-      <c r="E124" s="199"/>
+      <c r="D124" s="206"/>
+      <c r="E124" s="206"/>
       <c r="F124" s="102"/>
       <c r="G124" s="102"/>
       <c r="H124" s="102"/>
       <c r="I124" s="102"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="22" t="s">
         <v>23</v>
       </c>
@@ -4910,14 +4978,14 @@
       <c r="C125" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D125" s="199"/>
-      <c r="E125" s="199"/>
+      <c r="D125" s="206"/>
+      <c r="E125" s="206"/>
       <c r="F125" s="102"/>
       <c r="G125" s="102"/>
       <c r="H125" s="102"/>
       <c r="I125" s="102"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="22" t="s">
         <v>39</v>
       </c>
@@ -4926,15 +4994,15 @@
         <v>-6937168.6099999994</v>
       </c>
       <c r="C126" s="19"/>
-      <c r="D126" s="199"/>
-      <c r="E126" s="199"/>
+      <c r="D126" s="206"/>
+      <c r="E126" s="206"/>
       <c r="F126" s="102"/>
       <c r="G126" s="102"/>
       <c r="H126" s="102"/>
       <c r="I126" s="102"/>
       <c r="K126" s="45"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="22" t="s">
         <v>38</v>
       </c>
@@ -4943,15 +5011,15 @@
         <v>0</v>
       </c>
       <c r="C127" s="19"/>
-      <c r="D127" s="199"/>
-      <c r="E127" s="199"/>
+      <c r="D127" s="206"/>
+      <c r="E127" s="206"/>
       <c r="F127" s="102"/>
       <c r="G127" s="102"/>
       <c r="H127" s="102"/>
       <c r="I127" s="102"/>
       <c r="K127" s="55"/>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="22" t="s">
         <v>331</v>
       </c>
@@ -4968,7 +5036,7 @@
       <c r="I128" s="102"/>
       <c r="K128" s="55"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="22" t="s">
         <v>332</v>
       </c>
@@ -4984,7 +5052,7 @@
       <c r="I129" s="102"/>
       <c r="K129" s="55"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="22" t="s">
         <v>33</v>
       </c>
@@ -4994,7 +5062,7 @@
       </c>
       <c r="C130" s="23"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="22" t="s">
         <v>328</v>
       </c>
@@ -5003,7 +5071,7 @@
       </c>
       <c r="C131" s="23"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="22" t="s">
         <v>42</v>
       </c>
@@ -5013,12 +5081,12 @@
       </c>
       <c r="C132" s="23"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="22"/>
       <c r="B133" s="18"/>
       <c r="C133" s="23"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="20" t="s">
         <v>25</v>
       </c>
@@ -5028,12 +5096,12 @@
       </c>
       <c r="C134" s="78"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="23"/>
       <c r="C135" s="19"/>
       <c r="D135" s="26"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="17" t="s">
         <v>329</v>
       </c>
@@ -5043,7 +5111,7 @@
       <c r="C136" s="19"/>
       <c r="D136" s="26"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="20" t="s">
         <v>330</v>
       </c>
@@ -5053,13 +5121,13 @@
       <c r="C137" s="19"/>
       <c r="D137" s="26"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="20"/>
       <c r="B138" s="94"/>
       <c r="C138" s="19"/>
       <c r="D138" s="26"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="37" t="s">
         <v>18</v>
       </c>
@@ -5070,17 +5138,17 @@
       <c r="C139" s="19"/>
       <c r="D139" s="26"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="23"/>
       <c r="C140" s="19"/>
       <c r="D140" s="26"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="23"/>
       <c r="C141" s="19"/>
       <c r="D141" s="26"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C142" s="19"/>
       <c r="D142" s="44"/>
       <c r="E142" s="95"/>
@@ -5089,7 +5157,7 @@
       <c r="H142" s="95"/>
       <c r="I142" s="95"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="17" t="s">
         <v>26</v>
       </c>
@@ -5105,7 +5173,7 @@
       <c r="I143" s="95"/>
       <c r="J143" s="95"/>
     </row>
-    <row r="144" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="20" t="s">
         <v>263</v>
       </c>
@@ -5118,7 +5186,7 @@
       <c r="H144" s="103"/>
       <c r="I144" s="103"/>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145" s="20"/>
       <c r="B145" s="94"/>
       <c r="C145" s="25"/>
@@ -5128,7 +5196,7 @@
       <c r="H145" s="44"/>
       <c r="I145" s="44"/>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146" s="37" t="s">
         <v>18</v>
       </c>
@@ -5138,62 +5206,62 @@
       </c>
       <c r="C146" s="25"/>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C147" s="26"/>
       <c r="D147" s="95"/>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B148" s="23"/>
       <c r="C148" s="19"/>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="R150" s="10"/>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B153" s="198"/>
-      <c r="C153" s="198"/>
-      <c r="D153" s="198"/>
-      <c r="E153" s="198"/>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B153" s="205"/>
+      <c r="C153" s="205"/>
+      <c r="D153" s="205"/>
+      <c r="E153" s="205"/>
       <c r="F153" s="106"/>
       <c r="G153" s="106"/>
       <c r="H153" s="106"/>
       <c r="I153" s="106"/>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B154" s="198"/>
-      <c r="C154" s="198"/>
-      <c r="D154" s="198"/>
-      <c r="E154" s="198"/>
+    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B154" s="205"/>
+      <c r="C154" s="205"/>
+      <c r="D154" s="205"/>
+      <c r="E154" s="205"/>
       <c r="F154" s="106"/>
       <c r="G154" s="106"/>
       <c r="H154" s="106"/>
       <c r="I154" s="106"/>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B155" s="198"/>
-      <c r="C155" s="198"/>
-      <c r="D155" s="198"/>
-      <c r="E155" s="198"/>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B155" s="205"/>
+      <c r="C155" s="205"/>
+      <c r="D155" s="205"/>
+      <c r="E155" s="205"/>
       <c r="F155" s="106"/>
       <c r="G155" s="106"/>
       <c r="H155" s="106"/>
       <c r="I155" s="106"/>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B156" s="198"/>
-      <c r="C156" s="198"/>
-      <c r="D156" s="198"/>
-      <c r="E156" s="198"/>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B156" s="205"/>
+      <c r="C156" s="205"/>
+      <c r="D156" s="205"/>
+      <c r="E156" s="205"/>
       <c r="F156" s="106"/>
       <c r="G156" s="106"/>
       <c r="H156" s="106"/>
       <c r="I156" s="106"/>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B157" s="198"/>
-      <c r="C157" s="198"/>
-      <c r="D157" s="198"/>
-      <c r="E157" s="198"/>
+    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B157" s="205"/>
+      <c r="C157" s="205"/>
+      <c r="D157" s="205"/>
+      <c r="E157" s="205"/>
       <c r="F157" s="106"/>
       <c r="G157" s="106"/>
       <c r="H157" s="106"/>
@@ -5219,27 +5287,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R148"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="43.5703125" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
+    <col min="4" max="4" width="43.5546875" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5255,15 +5323,15 @@
       <c r="K1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="213">
+      <c r="L1" s="220">
         <f>RESUMEN!D104-RESUMEN!D102</f>
         <v>6937168.6099999994</v>
       </c>
-      <c r="M1" s="214"/>
+      <c r="M1" s="221"/>
       <c r="N1" s="76"/>
       <c r="O1" s="64"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -5284,7 +5352,7 @@
       <c r="N2" s="77"/>
       <c r="O2" s="64"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="str">
         <f>RESUMEN!C5</f>
         <v>PERÍODO: AGOSTO</v>
@@ -5304,7 +5372,7 @@
       <c r="N3" s="75"/>
       <c r="O3" s="16"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -5327,79 +5395,79 @@
         <v>-1973730.177240001</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="209" t="s">
+    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="216" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="222" t="s">
+      <c r="B5" s="229" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="209" t="s">
+      <c r="C5" s="216" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="224" t="s">
+      <c r="D5" s="231" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="224" t="s">
+      <c r="E5" s="231" t="s">
         <v>278</v>
       </c>
-      <c r="F5" s="209" t="s">
+      <c r="F5" s="216" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="209" t="s">
+      <c r="G5" s="216" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="209" t="s">
+      <c r="H5" s="216" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="215" t="s">
+      <c r="I5" s="222" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="217" t="s">
+      <c r="J5" s="224" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="217" t="s">
+      <c r="K5" s="224" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="220" t="s">
+      <c r="L5" s="227" t="s">
         <v>43</v>
       </c>
-      <c r="M5" s="217" t="s">
+      <c r="M5" s="224" t="s">
         <v>291</v>
       </c>
-      <c r="N5" s="217" t="s">
+      <c r="N5" s="224" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="210"/>
-      <c r="B6" s="223"/>
-      <c r="C6" s="210"/>
-      <c r="D6" s="225"/>
-      <c r="E6" s="225"/>
-      <c r="F6" s="210"/>
-      <c r="G6" s="210"/>
-      <c r="H6" s="210"/>
-      <c r="I6" s="216"/>
-      <c r="J6" s="218"/>
-      <c r="K6" s="218"/>
-      <c r="L6" s="221"/>
-      <c r="M6" s="218"/>
-      <c r="N6" s="218"/>
-    </row>
-    <row r="7" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="210"/>
-      <c r="B7" s="223"/>
-      <c r="C7" s="210"/>
-      <c r="D7" s="225"/>
-      <c r="E7" s="225"/>
-      <c r="F7" s="210"/>
-      <c r="G7" s="210"/>
-      <c r="H7" s="210"/>
-      <c r="I7" s="216"/>
-      <c r="J7" s="218"/>
-      <c r="K7" s="219"/>
-      <c r="L7" s="221"/>
+    <row r="6" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="217"/>
+      <c r="B6" s="230"/>
+      <c r="C6" s="217"/>
+      <c r="D6" s="232"/>
+      <c r="E6" s="232"/>
+      <c r="F6" s="217"/>
+      <c r="G6" s="217"/>
+      <c r="H6" s="217"/>
+      <c r="I6" s="223"/>
+      <c r="J6" s="225"/>
+      <c r="K6" s="225"/>
+      <c r="L6" s="228"/>
+      <c r="M6" s="225"/>
+      <c r="N6" s="225"/>
+    </row>
+    <row r="7" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="217"/>
+      <c r="B7" s="230"/>
+      <c r="C7" s="217"/>
+      <c r="D7" s="232"/>
+      <c r="E7" s="232"/>
+      <c r="F7" s="217"/>
+      <c r="G7" s="217"/>
+      <c r="H7" s="217"/>
+      <c r="I7" s="223"/>
+      <c r="J7" s="225"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="228"/>
       <c r="M7" s="152" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 15/09</v>
@@ -5409,7 +5477,7 @@
         <v>VTO 15/09</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>122</v>
       </c>
@@ -5456,12 +5524,12 @@
         <v>127313.57001968</v>
       </c>
       <c r="O8" s="133"/>
-      <c r="Q8" s="208" t="s">
+      <c r="Q8" s="215" t="s">
         <v>262</v>
       </c>
-      <c r="R8" s="208"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R8" s="215"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
@@ -5504,10 +5572,10 @@
         <v>107925.25557887998</v>
       </c>
       <c r="O9" s="133"/>
-      <c r="Q9" s="208"/>
-      <c r="R9" s="208"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q9" s="215"/>
+      <c r="R9" s="215"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>122</v>
       </c>
@@ -5560,7 +5628,7 @@
         <v>85907.454444000003</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>122</v>
       </c>
@@ -5612,7 +5680,7 @@
         <v>101816.24230399998</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>122</v>
       </c>
@@ -5665,7 +5733,7 @@
         <v>96248.166552999988</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="62" t="s">
         <v>124</v>
       </c>
@@ -5722,7 +5790,7 @@
         <v>118520.469557</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="62" t="s">
         <v>125</v>
       </c>
@@ -5780,7 +5848,7 @@
         <v>138406.45438199997</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="62" t="s">
         <v>124</v>
       </c>
@@ -5831,7 +5899,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="62" t="s">
         <v>126</v>
       </c>
@@ -5883,7 +5951,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="62" t="s">
         <v>126</v>
       </c>
@@ -5931,7 +5999,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="62" t="s">
         <v>126</v>
       </c>
@@ -5984,7 +6052,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="62" t="s">
         <v>124</v>
       </c>
@@ -6035,7 +6103,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="62" t="s">
         <v>125</v>
       </c>
@@ -6086,7 +6154,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="62" t="s">
         <v>124</v>
       </c>
@@ -6136,7 +6204,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="62" t="s">
         <v>126</v>
       </c>
@@ -6184,7 +6252,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="62" t="s">
         <v>126</v>
       </c>
@@ -6232,7 +6300,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="62" t="s">
         <v>126</v>
       </c>
@@ -6280,7 +6348,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="62" t="s">
         <v>124</v>
       </c>
@@ -6331,7 +6399,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="62" t="s">
         <v>125</v>
       </c>
@@ -6384,7 +6452,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="62" t="s">
         <v>124</v>
       </c>
@@ -6435,7 +6503,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="181" t="s">
         <v>126</v>
       </c>
@@ -6483,7 +6551,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="62" t="s">
         <v>126</v>
       </c>
@@ -6536,7 +6604,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="62" t="s">
         <v>126</v>
       </c>
@@ -6584,7 +6652,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="62" t="s">
         <v>124</v>
       </c>
@@ -6636,7 +6704,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="62" t="s">
         <v>125</v>
       </c>
@@ -6687,7 +6755,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="192" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" s="192" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="181" t="s">
         <v>124</v>
       </c>
@@ -6735,7 +6803,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="192" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" s="192" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="181" t="s">
         <v>126</v>
       </c>
@@ -6783,7 +6851,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="192" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" s="192" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="181" t="s">
         <v>126</v>
       </c>
@@ -6831,7 +6899,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="192" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" s="192" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="181" t="s">
         <v>126</v>
       </c>
@@ -6879,7 +6947,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="62" t="s">
         <v>124</v>
       </c>
@@ -6930,7 +6998,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="62" t="s">
         <v>125</v>
       </c>
@@ -6983,7 +7051,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="62" t="s">
         <v>124</v>
       </c>
@@ -7040,7 +7108,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="62" t="s">
         <v>126</v>
       </c>
@@ -7094,7 +7162,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="62" t="s">
         <v>126</v>
       </c>
@@ -7145,7 +7213,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="62" t="s">
         <v>126</v>
       </c>
@@ -7196,7 +7264,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="62" t="s">
         <v>124</v>
       </c>
@@ -7247,7 +7315,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="62" t="s">
         <v>125</v>
       </c>
@@ -7299,7 +7367,7 @@
       </c>
       <c r="P44" s="44"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="62" t="s">
         <v>124</v>
       </c>
@@ -7351,7 +7419,7 @@
       </c>
       <c r="P45" s="44"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="62" t="s">
         <v>126</v>
       </c>
@@ -7401,7 +7469,7 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="62" t="s">
         <v>126</v>
       </c>
@@ -7452,7 +7520,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="62" t="s">
         <v>126</v>
       </c>
@@ -7503,7 +7571,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="62" t="s">
         <v>124</v>
       </c>
@@ -7555,7 +7623,7 @@
       </c>
       <c r="Q49" s="64"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="62" t="s">
         <v>125</v>
       </c>
@@ -7608,7 +7676,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="62" t="s">
         <v>124</v>
       </c>
@@ -7659,7 +7727,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="62" t="s">
         <v>126</v>
       </c>
@@ -7710,7 +7778,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="62" t="s">
         <v>126</v>
       </c>
@@ -7764,7 +7832,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="62" t="s">
         <v>126</v>
       </c>
@@ -7818,7 +7886,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="62" t="s">
         <v>124</v>
       </c>
@@ -7869,7 +7937,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="62" t="s">
         <v>125</v>
       </c>
@@ -7920,7 +7988,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="62" t="s">
         <v>124</v>
       </c>
@@ -7971,7 +8039,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="62" t="s">
         <v>126</v>
       </c>
@@ -8021,7 +8089,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="62" t="s">
         <v>126</v>
       </c>
@@ -8072,7 +8140,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="62" t="s">
         <v>126</v>
       </c>
@@ -8123,7 +8191,7 @@
         <v>0.48000000000000026</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="62" t="s">
         <v>124</v>
       </c>
@@ -8174,7 +8242,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="181" t="s">
         <v>125</v>
       </c>
@@ -8222,7 +8290,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="62" t="s">
         <v>124</v>
       </c>
@@ -8273,7 +8341,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="62" t="s">
         <v>126</v>
       </c>
@@ -8324,7 +8392,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="62" t="s">
         <v>126</v>
       </c>
@@ -8378,7 +8446,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="62" t="s">
         <v>126</v>
       </c>
@@ -8429,7 +8497,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="62" t="s">
         <v>127</v>
       </c>
@@ -8480,7 +8548,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="62" t="s">
         <v>124</v>
       </c>
@@ -8531,7 +8599,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="62" t="s">
         <v>126</v>
       </c>
@@ -8579,7 +8647,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="62" t="s">
         <v>126</v>
       </c>
@@ -8629,7 +8697,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="62" t="s">
         <v>126</v>
       </c>
@@ -8680,7 +8748,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="62" t="s">
         <v>127</v>
       </c>
@@ -8731,7 +8799,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="62" t="s">
         <v>124</v>
       </c>
@@ -8782,7 +8850,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="62" t="s">
         <v>126</v>
       </c>
@@ -8830,7 +8898,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="62" t="s">
         <v>126</v>
       </c>
@@ -8883,7 +8951,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="62" t="s">
         <v>126</v>
       </c>
@@ -8937,7 +9005,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="62" t="s">
         <v>127</v>
       </c>
@@ -8988,7 +9056,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="62" t="s">
         <v>124</v>
       </c>
@@ -9039,7 +9107,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="62" t="s">
         <v>126</v>
       </c>
@@ -9090,7 +9158,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="62" t="s">
         <v>126</v>
       </c>
@@ -9141,7 +9209,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="125" t="s">
         <v>126</v>
       </c>
@@ -9189,7 +9257,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="125"/>
       <c r="B82" s="36"/>
       <c r="C82" s="36" t="s">
@@ -9238,7 +9306,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="125"/>
       <c r="B83" s="36"/>
       <c r="C83" s="36" t="s">
@@ -9287,7 +9355,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="125"/>
       <c r="B84" s="36"/>
       <c r="C84" s="36" t="s">
@@ -9336,7 +9404,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="125"/>
       <c r="B85" s="36"/>
       <c r="C85" s="36" t="s">
@@ -9385,7 +9453,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="125"/>
       <c r="B86" s="36"/>
       <c r="C86" s="36" t="s">
@@ -9437,7 +9505,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="125"/>
       <c r="B87" s="36"/>
       <c r="C87" s="180" t="s">
@@ -9483,7 +9551,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="125"/>
       <c r="B88" s="36"/>
       <c r="C88" s="36" t="s">
@@ -9532,7 +9600,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="125"/>
       <c r="B89" s="36"/>
       <c r="C89" s="36" t="s">
@@ -9581,7 +9649,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="125"/>
       <c r="B90" s="36"/>
       <c r="C90" s="36" t="s">
@@ -9630,7 +9698,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="125"/>
       <c r="B91" s="36"/>
       <c r="C91" s="180" t="s">
@@ -9676,7 +9744,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="125"/>
       <c r="B92" s="36"/>
       <c r="C92" s="36" t="s">
@@ -9725,7 +9793,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="125"/>
       <c r="B93" s="36"/>
       <c r="C93" s="36" t="s">
@@ -9774,7 +9842,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" s="125"/>
       <c r="B94" s="36"/>
       <c r="C94" s="36" t="s">
@@ -9823,7 +9891,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="125"/>
       <c r="B95" s="36"/>
       <c r="C95" s="36" t="s">
@@ -9872,7 +9940,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="96" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="125"/>
       <c r="B96" s="36"/>
       <c r="C96" s="36" t="s">
@@ -9921,7 +9989,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="97" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="125"/>
       <c r="B97" s="36"/>
       <c r="C97" s="36" t="s">
@@ -9970,7 +10038,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="98" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="125"/>
       <c r="B98" s="36"/>
       <c r="C98" s="36" t="s">
@@ -10019,7 +10087,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="125"/>
       <c r="B99" s="36"/>
       <c r="C99" s="36" t="s">
@@ -10068,7 +10136,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="100" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="125"/>
       <c r="B100" s="36"/>
       <c r="C100" s="36" t="s">
@@ -10117,7 +10185,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="101" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="125"/>
       <c r="B101" s="36"/>
       <c r="C101" s="36" t="s">
@@ -10166,7 +10234,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="125"/>
       <c r="B102" s="36"/>
       <c r="C102" s="36" t="s">
@@ -10215,7 +10283,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="125"/>
       <c r="B103" s="36"/>
       <c r="C103" s="36" t="s">
@@ -10264,7 +10332,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="125"/>
       <c r="B104" s="36"/>
       <c r="C104" s="36" t="s">
@@ -10313,7 +10381,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="125"/>
       <c r="B105" s="36"/>
       <c r="C105" s="36" t="s">
@@ -10362,7 +10430,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" s="125"/>
       <c r="B106" s="36"/>
       <c r="C106" s="36" t="s">
@@ -10378,7 +10446,7 @@
       <c r="G106" s="154">
         <v>37129.94</v>
       </c>
-      <c r="H106" s="227">
+      <c r="H106" s="197">
         <v>20700.939999999999</v>
       </c>
       <c r="I106" s="60">
@@ -10413,7 +10481,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" s="125"/>
       <c r="B107" s="36"/>
       <c r="C107" s="36" t="s">
@@ -10462,7 +10530,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="125"/>
       <c r="B108" s="36"/>
       <c r="C108" s="180" t="s">
@@ -10508,7 +10576,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" s="125"/>
       <c r="B109" s="36"/>
       <c r="C109" s="36" t="s">
@@ -10557,7 +10625,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" s="125"/>
       <c r="B110" s="36"/>
       <c r="C110" s="36" t="s">
@@ -10606,7 +10674,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" s="125"/>
       <c r="B111" s="36"/>
       <c r="C111" s="36" t="s">
@@ -10655,7 +10723,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="125"/>
       <c r="B112" s="36"/>
       <c r="C112" s="36" t="s">
@@ -10704,7 +10772,7 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="147"/>
       <c r="B113" s="36"/>
       <c r="C113" s="36" t="s">
@@ -10753,7 +10821,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="147"/>
       <c r="B114" s="36"/>
       <c r="C114" s="36" t="s">
@@ -10802,7 +10870,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="147"/>
       <c r="B115" s="36"/>
       <c r="C115" s="36" t="s">
@@ -10851,7 +10919,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="147"/>
       <c r="B116" s="36"/>
       <c r="C116" s="36" t="s">
@@ -10900,7 +10968,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" s="147"/>
       <c r="B117" s="36"/>
       <c r="C117" s="36" t="s">
@@ -10949,7 +11017,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="147"/>
       <c r="B118" s="36"/>
       <c r="C118" s="36" t="s">
@@ -10998,7 +11066,7 @@
         <v>1.0600000000000007</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="147"/>
       <c r="B119" s="36"/>
       <c r="C119" s="36" t="s">
@@ -11047,7 +11115,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="147"/>
       <c r="B120" s="36"/>
       <c r="C120" s="36" t="s">
@@ -11096,7 +11164,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" s="147"/>
       <c r="B121" s="36"/>
       <c r="C121" s="36" t="s">
@@ -11145,7 +11213,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" s="147"/>
       <c r="B122" s="36"/>
       <c r="C122" s="36" t="s">
@@ -11194,7 +11262,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" s="147"/>
       <c r="B123" s="36"/>
       <c r="C123" s="36" t="s">
@@ -11243,7 +11311,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="147" t="s">
         <v>27</v>
       </c>
@@ -11294,7 +11362,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" s="147" t="s">
         <v>27</v>
       </c>
@@ -11345,7 +11413,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" s="56" t="s">
         <v>27</v>
       </c>
@@ -11363,7 +11431,7 @@
       <c r="M126" s="5"/>
       <c r="N126" s="9"/>
     </row>
-    <row r="127" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="28"/>
       <c r="B127" s="28"/>
       <c r="C127" s="28"/>
@@ -11404,41 +11472,41 @@
       </c>
       <c r="P127" s="64"/>
     </row>
-    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K128" s="66">
         <f>K127-L1</f>
         <v>1973730.177240001</v>
       </c>
     </row>
-    <row r="129" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C129" s="212"/>
-      <c r="D129" s="212"/>
-      <c r="E129" s="212"/>
-      <c r="F129" s="212"/>
-      <c r="G129" s="212"/>
-      <c r="H129" s="212"/>
-      <c r="I129" s="212"/>
-      <c r="J129" s="212"/>
-      <c r="K129" s="212"/>
-      <c r="L129" s="212"/>
-      <c r="M129" s="212"/>
-      <c r="N129" s="212"/>
-    </row>
-    <row r="130" spans="3:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C130" s="212"/>
-      <c r="D130" s="212"/>
-      <c r="E130" s="212"/>
-      <c r="F130" s="212"/>
-      <c r="G130" s="212"/>
-      <c r="H130" s="212"/>
-      <c r="I130" s="212"/>
-      <c r="J130" s="212"/>
-      <c r="K130" s="212"/>
-      <c r="L130" s="212"/>
-      <c r="M130" s="212"/>
-      <c r="N130" s="212"/>
-    </row>
-    <row r="131" spans="3:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C129" s="219"/>
+      <c r="D129" s="219"/>
+      <c r="E129" s="219"/>
+      <c r="F129" s="219"/>
+      <c r="G129" s="219"/>
+      <c r="H129" s="219"/>
+      <c r="I129" s="219"/>
+      <c r="J129" s="219"/>
+      <c r="K129" s="219"/>
+      <c r="L129" s="219"/>
+      <c r="M129" s="219"/>
+      <c r="N129" s="219"/>
+    </row>
+    <row r="130" spans="3:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C130" s="219"/>
+      <c r="D130" s="219"/>
+      <c r="E130" s="219"/>
+      <c r="F130" s="219"/>
+      <c r="G130" s="219"/>
+      <c r="H130" s="219"/>
+      <c r="I130" s="219"/>
+      <c r="J130" s="219"/>
+      <c r="K130" s="219"/>
+      <c r="L130" s="219"/>
+      <c r="M130" s="219"/>
+      <c r="N130" s="219"/>
+    </row>
+    <row r="131" spans="3:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C131" s="87"/>
       <c r="D131" s="87"/>
       <c r="E131" s="87"/>
@@ -11452,121 +11520,121 @@
       <c r="M131" s="87"/>
       <c r="N131" s="87"/>
     </row>
-    <row r="132" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C132" s="212" t="s">
+    <row r="132" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C132" s="219" t="s">
         <v>268</v>
       </c>
-      <c r="D132" s="212"/>
-      <c r="E132" s="212"/>
-      <c r="F132" s="212"/>
-      <c r="G132" s="212"/>
-      <c r="H132" s="212"/>
-      <c r="I132" s="212"/>
-      <c r="J132" s="212"/>
-      <c r="K132" s="212"/>
-      <c r="L132" s="212"/>
-      <c r="M132" s="212"/>
-      <c r="N132" s="212"/>
-    </row>
-    <row r="133" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C133" s="212"/>
-      <c r="D133" s="212"/>
-      <c r="E133" s="212"/>
-      <c r="F133" s="212"/>
-      <c r="G133" s="212"/>
-      <c r="H133" s="212"/>
-      <c r="I133" s="212"/>
-      <c r="J133" s="212"/>
-      <c r="K133" s="212"/>
-      <c r="L133" s="212"/>
-      <c r="M133" s="212"/>
-      <c r="N133" s="212"/>
-    </row>
-    <row r="134" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C134" s="212"/>
-      <c r="D134" s="212"/>
-      <c r="E134" s="212"/>
-      <c r="F134" s="212"/>
-      <c r="G134" s="212"/>
-      <c r="H134" s="212"/>
-      <c r="I134" s="212"/>
-      <c r="J134" s="212"/>
-      <c r="K134" s="212"/>
-      <c r="L134" s="212"/>
-      <c r="M134" s="212"/>
-      <c r="N134" s="212"/>
-    </row>
-    <row r="135" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C135" s="212"/>
-      <c r="D135" s="212"/>
-      <c r="E135" s="212"/>
-      <c r="F135" s="212"/>
-      <c r="G135" s="212"/>
-      <c r="H135" s="212"/>
-      <c r="I135" s="212"/>
-      <c r="J135" s="212"/>
-      <c r="K135" s="212"/>
-      <c r="L135" s="212"/>
-      <c r="M135" s="212"/>
-      <c r="N135" s="212"/>
-    </row>
-    <row r="136" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C136" s="212"/>
-      <c r="D136" s="212"/>
-      <c r="E136" s="212"/>
-      <c r="F136" s="212"/>
-      <c r="G136" s="212"/>
-      <c r="H136" s="212"/>
-      <c r="I136" s="212"/>
-      <c r="J136" s="212"/>
-      <c r="K136" s="212"/>
-      <c r="L136" s="212"/>
-      <c r="M136" s="212"/>
-      <c r="N136" s="212"/>
-    </row>
-    <row r="137" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C137" s="212"/>
-      <c r="D137" s="212"/>
-      <c r="E137" s="212"/>
-      <c r="F137" s="212"/>
-      <c r="G137" s="212"/>
-      <c r="H137" s="212"/>
-      <c r="I137" s="212"/>
-      <c r="J137" s="212"/>
-      <c r="K137" s="212"/>
-      <c r="L137" s="212"/>
-      <c r="M137" s="212"/>
-      <c r="N137" s="212"/>
-    </row>
-    <row r="138" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C138" s="212"/>
-      <c r="D138" s="212"/>
-      <c r="E138" s="212"/>
-      <c r="F138" s="212"/>
-      <c r="G138" s="212"/>
-      <c r="H138" s="212"/>
-      <c r="I138" s="212"/>
-      <c r="J138" s="212"/>
-      <c r="K138" s="212"/>
-      <c r="L138" s="212"/>
-      <c r="M138" s="212"/>
-      <c r="N138" s="212"/>
-    </row>
-    <row r="139" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C139" s="212"/>
-      <c r="D139" s="212"/>
-      <c r="E139" s="212"/>
-      <c r="F139" s="212"/>
-      <c r="G139" s="212"/>
-      <c r="H139" s="212"/>
-      <c r="I139" s="212"/>
-      <c r="J139" s="212"/>
-      <c r="K139" s="212"/>
-      <c r="L139" s="212"/>
-      <c r="M139" s="212"/>
-      <c r="N139" s="212"/>
-    </row>
-    <row r="140" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D132" s="219"/>
+      <c r="E132" s="219"/>
+      <c r="F132" s="219"/>
+      <c r="G132" s="219"/>
+      <c r="H132" s="219"/>
+      <c r="I132" s="219"/>
+      <c r="J132" s="219"/>
+      <c r="K132" s="219"/>
+      <c r="L132" s="219"/>
+      <c r="M132" s="219"/>
+      <c r="N132" s="219"/>
+    </row>
+    <row r="133" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C133" s="219"/>
+      <c r="D133" s="219"/>
+      <c r="E133" s="219"/>
+      <c r="F133" s="219"/>
+      <c r="G133" s="219"/>
+      <c r="H133" s="219"/>
+      <c r="I133" s="219"/>
+      <c r="J133" s="219"/>
+      <c r="K133" s="219"/>
+      <c r="L133" s="219"/>
+      <c r="M133" s="219"/>
+      <c r="N133" s="219"/>
+    </row>
+    <row r="134" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C134" s="219"/>
+      <c r="D134" s="219"/>
+      <c r="E134" s="219"/>
+      <c r="F134" s="219"/>
+      <c r="G134" s="219"/>
+      <c r="H134" s="219"/>
+      <c r="I134" s="219"/>
+      <c r="J134" s="219"/>
+      <c r="K134" s="219"/>
+      <c r="L134" s="219"/>
+      <c r="M134" s="219"/>
+      <c r="N134" s="219"/>
+    </row>
+    <row r="135" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C135" s="219"/>
+      <c r="D135" s="219"/>
+      <c r="E135" s="219"/>
+      <c r="F135" s="219"/>
+      <c r="G135" s="219"/>
+      <c r="H135" s="219"/>
+      <c r="I135" s="219"/>
+      <c r="J135" s="219"/>
+      <c r="K135" s="219"/>
+      <c r="L135" s="219"/>
+      <c r="M135" s="219"/>
+      <c r="N135" s="219"/>
+    </row>
+    <row r="136" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C136" s="219"/>
+      <c r="D136" s="219"/>
+      <c r="E136" s="219"/>
+      <c r="F136" s="219"/>
+      <c r="G136" s="219"/>
+      <c r="H136" s="219"/>
+      <c r="I136" s="219"/>
+      <c r="J136" s="219"/>
+      <c r="K136" s="219"/>
+      <c r="L136" s="219"/>
+      <c r="M136" s="219"/>
+      <c r="N136" s="219"/>
+    </row>
+    <row r="137" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C137" s="219"/>
+      <c r="D137" s="219"/>
+      <c r="E137" s="219"/>
+      <c r="F137" s="219"/>
+      <c r="G137" s="219"/>
+      <c r="H137" s="219"/>
+      <c r="I137" s="219"/>
+      <c r="J137" s="219"/>
+      <c r="K137" s="219"/>
+      <c r="L137" s="219"/>
+      <c r="M137" s="219"/>
+      <c r="N137" s="219"/>
+    </row>
+    <row r="138" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C138" s="219"/>
+      <c r="D138" s="219"/>
+      <c r="E138" s="219"/>
+      <c r="F138" s="219"/>
+      <c r="G138" s="219"/>
+      <c r="H138" s="219"/>
+      <c r="I138" s="219"/>
+      <c r="J138" s="219"/>
+      <c r="K138" s="219"/>
+      <c r="L138" s="219"/>
+      <c r="M138" s="219"/>
+      <c r="N138" s="219"/>
+    </row>
+    <row r="139" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C139" s="219"/>
+      <c r="D139" s="219"/>
+      <c r="E139" s="219"/>
+      <c r="F139" s="219"/>
+      <c r="G139" s="219"/>
+      <c r="H139" s="219"/>
+      <c r="I139" s="219"/>
+      <c r="J139" s="219"/>
+      <c r="K139" s="219"/>
+      <c r="L139" s="219"/>
+      <c r="M139" s="219"/>
+      <c r="N139" s="219"/>
+    </row>
+    <row r="140" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C140" s="87"/>
       <c r="D140" s="87"/>
       <c r="E140" s="87"/>
@@ -11580,7 +11648,7 @@
       <c r="M140" s="87"/>
       <c r="N140" s="87"/>
     </row>
-    <row r="141" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C141" s="87"/>
       <c r="D141" s="87"/>
       <c r="E141" s="87"/>
@@ -11594,109 +11662,109 @@
       <c r="M141" s="87"/>
       <c r="N141" s="87"/>
     </row>
-    <row r="142" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C142" s="211" t="s">
+    <row r="142" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C142" s="218" t="s">
         <v>267</v>
       </c>
-      <c r="D142" s="211"/>
-      <c r="E142" s="211"/>
-      <c r="F142" s="211"/>
-      <c r="G142" s="211"/>
-      <c r="H142" s="211"/>
-      <c r="I142" s="211"/>
-      <c r="J142" s="211"/>
-      <c r="K142" s="211"/>
-      <c r="L142" s="211"/>
-      <c r="M142" s="211"/>
-      <c r="N142" s="211"/>
-    </row>
-    <row r="143" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C143" s="211"/>
-      <c r="D143" s="211"/>
-      <c r="E143" s="211"/>
-      <c r="F143" s="211"/>
-      <c r="G143" s="211"/>
-      <c r="H143" s="211"/>
-      <c r="I143" s="211"/>
-      <c r="J143" s="211"/>
-      <c r="K143" s="211"/>
-      <c r="L143" s="211"/>
-      <c r="M143" s="211"/>
-      <c r="N143" s="211"/>
-    </row>
-    <row r="144" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C144" s="211"/>
-      <c r="D144" s="211"/>
-      <c r="E144" s="211"/>
-      <c r="F144" s="211"/>
-      <c r="G144" s="211"/>
-      <c r="H144" s="211"/>
-      <c r="I144" s="211"/>
-      <c r="J144" s="211"/>
-      <c r="K144" s="211"/>
-      <c r="L144" s="211"/>
-      <c r="M144" s="211"/>
-      <c r="N144" s="211"/>
+      <c r="D142" s="218"/>
+      <c r="E142" s="218"/>
+      <c r="F142" s="218"/>
+      <c r="G142" s="218"/>
+      <c r="H142" s="218"/>
+      <c r="I142" s="218"/>
+      <c r="J142" s="218"/>
+      <c r="K142" s="218"/>
+      <c r="L142" s="218"/>
+      <c r="M142" s="218"/>
+      <c r="N142" s="218"/>
+    </row>
+    <row r="143" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C143" s="218"/>
+      <c r="D143" s="218"/>
+      <c r="E143" s="218"/>
+      <c r="F143" s="218"/>
+      <c r="G143" s="218"/>
+      <c r="H143" s="218"/>
+      <c r="I143" s="218"/>
+      <c r="J143" s="218"/>
+      <c r="K143" s="218"/>
+      <c r="L143" s="218"/>
+      <c r="M143" s="218"/>
+      <c r="N143" s="218"/>
+    </row>
+    <row r="144" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C144" s="218"/>
+      <c r="D144" s="218"/>
+      <c r="E144" s="218"/>
+      <c r="F144" s="218"/>
+      <c r="G144" s="218"/>
+      <c r="H144" s="218"/>
+      <c r="I144" s="218"/>
+      <c r="J144" s="218"/>
+      <c r="K144" s="218"/>
+      <c r="L144" s="218"/>
+      <c r="M144" s="218"/>
+      <c r="N144" s="218"/>
       <c r="P144" s="95">
         <f>L1-K127</f>
         <v>-1973730.177240001</v>
       </c>
     </row>
-    <row r="145" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C145" s="211"/>
-      <c r="D145" s="211"/>
-      <c r="E145" s="211"/>
-      <c r="F145" s="211"/>
-      <c r="G145" s="211"/>
-      <c r="H145" s="211"/>
-      <c r="I145" s="211"/>
-      <c r="J145" s="211"/>
-      <c r="K145" s="211"/>
-      <c r="L145" s="211"/>
-      <c r="M145" s="211"/>
-      <c r="N145" s="211"/>
-    </row>
-    <row r="146" spans="3:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C146" s="211"/>
-      <c r="D146" s="211"/>
-      <c r="E146" s="211"/>
-      <c r="F146" s="211"/>
-      <c r="G146" s="211"/>
-      <c r="H146" s="211"/>
-      <c r="I146" s="211"/>
-      <c r="J146" s="211"/>
-      <c r="K146" s="211"/>
-      <c r="L146" s="211"/>
-      <c r="M146" s="211"/>
-      <c r="N146" s="211"/>
-    </row>
-    <row r="147" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C147" s="211"/>
-      <c r="D147" s="211"/>
-      <c r="E147" s="211"/>
-      <c r="F147" s="211"/>
-      <c r="G147" s="211"/>
-      <c r="H147" s="211"/>
-      <c r="I147" s="211"/>
-      <c r="J147" s="211"/>
-      <c r="K147" s="211"/>
-      <c r="L147" s="211"/>
-      <c r="M147" s="211"/>
-      <c r="N147" s="211"/>
-    </row>
-    <row r="148" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C148" s="211"/>
-      <c r="D148" s="211"/>
-      <c r="E148" s="211"/>
-      <c r="F148" s="211"/>
-      <c r="G148" s="211"/>
-      <c r="H148" s="211"/>
-      <c r="I148" s="211"/>
-      <c r="J148" s="211"/>
-      <c r="K148" s="211"/>
-      <c r="L148" s="211"/>
-      <c r="M148" s="211"/>
-      <c r="N148" s="211"/>
+    <row r="145" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C145" s="218"/>
+      <c r="D145" s="218"/>
+      <c r="E145" s="218"/>
+      <c r="F145" s="218"/>
+      <c r="G145" s="218"/>
+      <c r="H145" s="218"/>
+      <c r="I145" s="218"/>
+      <c r="J145" s="218"/>
+      <c r="K145" s="218"/>
+      <c r="L145" s="218"/>
+      <c r="M145" s="218"/>
+      <c r="N145" s="218"/>
+    </row>
+    <row r="146" spans="3:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C146" s="218"/>
+      <c r="D146" s="218"/>
+      <c r="E146" s="218"/>
+      <c r="F146" s="218"/>
+      <c r="G146" s="218"/>
+      <c r="H146" s="218"/>
+      <c r="I146" s="218"/>
+      <c r="J146" s="218"/>
+      <c r="K146" s="218"/>
+      <c r="L146" s="218"/>
+      <c r="M146" s="218"/>
+      <c r="N146" s="218"/>
+    </row>
+    <row r="147" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C147" s="218"/>
+      <c r="D147" s="218"/>
+      <c r="E147" s="218"/>
+      <c r="F147" s="218"/>
+      <c r="G147" s="218"/>
+      <c r="H147" s="218"/>
+      <c r="I147" s="218"/>
+      <c r="J147" s="218"/>
+      <c r="K147" s="218"/>
+      <c r="L147" s="218"/>
+      <c r="M147" s="218"/>
+      <c r="N147" s="218"/>
+    </row>
+    <row r="148" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C148" s="218"/>
+      <c r="D148" s="218"/>
+      <c r="E148" s="218"/>
+      <c r="F148" s="218"/>
+      <c r="G148" s="218"/>
+      <c r="H148" s="218"/>
+      <c r="I148" s="218"/>
+      <c r="J148" s="218"/>
+      <c r="K148" s="218"/>
+      <c r="L148" s="218"/>
+      <c r="M148" s="218"/>
+      <c r="N148" s="218"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -11730,9 +11798,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
   <dimension ref="B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" s="177"/>
     </row>
   </sheetData>
@@ -11741,20 +11809,312 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F915B89F-3C2A-48C0-BA2F-ED20D761760E}">
+  <dimension ref="A2:J26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C3" s="233" t="str">
+        <f>RESUMEN!C5</f>
+        <v>PERÍODO: AGOSTO</v>
+      </c>
+      <c r="D3" s="234"/>
+      <c r="E3" s="234"/>
+      <c r="F3" s="234" t="str">
+        <f>[1]RESUMEN!A22</f>
+        <v xml:space="preserve">Sueldo encargada Sonia Arzamendia Galeano </v>
+      </c>
+      <c r="G3" s="234"/>
+      <c r="H3" s="234"/>
+      <c r="I3" s="234"/>
+      <c r="J3" s="235"/>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="1"/>
+      <c r="J4" s="198"/>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="1" t="str">
+        <f>RESUMEN!A26</f>
+        <v xml:space="preserve">Haberes </v>
+      </c>
+      <c r="G5" s="44">
+        <f>RESUMEN!D26</f>
+        <v>977372</v>
+      </c>
+      <c r="H5" s="236" t="s">
+        <v>339</v>
+      </c>
+      <c r="I5" s="236"/>
+      <c r="J5" s="237"/>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="1" t="str">
+        <f>RESUMEN!A27</f>
+        <v>Plus pileta</v>
+      </c>
+      <c r="G6" s="44">
+        <f>RESUMEN!D27</f>
+        <v>34111</v>
+      </c>
+      <c r="H6" s="236" t="s">
+        <v>340</v>
+      </c>
+      <c r="I6" s="236"/>
+      <c r="J6" s="237"/>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="1" t="str">
+        <f>RESUMEN!A28</f>
+        <v>Plus retiro de basura</v>
+      </c>
+      <c r="G7" s="44">
+        <f>RESUMEN!D28</f>
+        <v>111256.4</v>
+      </c>
+      <c r="H7" s="236"/>
+      <c r="I7" s="236"/>
+      <c r="J7" s="237"/>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="1" t="str">
+        <f>RESUMEN!A29</f>
+        <v>Plus cochera</v>
+      </c>
+      <c r="G8" s="44">
+        <f>RESUMEN!D29</f>
+        <v>20777</v>
+      </c>
+      <c r="J8" s="198"/>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="1" t="str">
+        <f>RESUMEN!A30</f>
+        <v>Adicional remuneracion</v>
+      </c>
+      <c r="G9" s="44">
+        <f>RESUMEN!D30</f>
+        <v>50000</v>
+      </c>
+      <c r="H9" s="236" t="s">
+        <v>341</v>
+      </c>
+      <c r="I9" s="236"/>
+      <c r="J9" s="237"/>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="1"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="236" t="s">
+        <v>340</v>
+      </c>
+      <c r="I10" s="236"/>
+      <c r="J10" s="237"/>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="1"/>
+      <c r="H11" s="236"/>
+      <c r="I11" s="236"/>
+      <c r="J11" s="237"/>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="199" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="200">
+        <f>SUM(G5:G11)</f>
+        <v>1193516.3999999999</v>
+      </c>
+      <c r="J12" s="198"/>
+    </row>
+    <row r="13" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="201"/>
+      <c r="D13" s="202"/>
+      <c r="E13" s="202"/>
+      <c r="F13" s="202"/>
+      <c r="G13" s="202"/>
+      <c r="H13" s="202"/>
+      <c r="I13" s="202"/>
+      <c r="J13" s="203"/>
+    </row>
+    <row r="15" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="233" t="str">
+        <f>C3</f>
+        <v>PERÍODO: AGOSTO</v>
+      </c>
+      <c r="D16" s="234"/>
+      <c r="E16" s="234"/>
+      <c r="F16" s="234" t="str">
+        <f>[1]RESUMEN!A30</f>
+        <v>Sueldo encargada Miriam</v>
+      </c>
+      <c r="G16" s="234"/>
+      <c r="H16" s="234"/>
+      <c r="I16" s="234"/>
+      <c r="J16" s="235"/>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C17" s="1"/>
+      <c r="J17" s="198"/>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C18" s="1"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="236" t="s">
+        <v>339</v>
+      </c>
+      <c r="I18" s="236"/>
+      <c r="J18" s="237"/>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="1" t="str">
+        <f>RESUMEN!A33</f>
+        <v xml:space="preserve">Haberes </v>
+      </c>
+      <c r="G19" s="44">
+        <f>RESUMEN!D33</f>
+        <v>488686</v>
+      </c>
+      <c r="H19" s="236" t="s">
+        <v>340</v>
+      </c>
+      <c r="I19" s="236"/>
+      <c r="J19" s="237"/>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="1" t="str">
+        <f>RESUMEN!A34</f>
+        <v>Horas extras</v>
+      </c>
+      <c r="G20" s="44">
+        <f>RESUMEN!D34</f>
+        <v>38500</v>
+      </c>
+      <c r="H20" s="236"/>
+      <c r="I20" s="236"/>
+      <c r="J20" s="237"/>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="1" t="str">
+        <f>RESUMEN!A35</f>
+        <v>Plus pileta</v>
+      </c>
+      <c r="G21" s="44">
+        <f>RESUMEN!D35</f>
+        <v>34111</v>
+      </c>
+      <c r="J21" s="198"/>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="1" t="str">
+        <f>RESUMEN!A36</f>
+        <v>Plus retiro de basura</v>
+      </c>
+      <c r="G22" s="44">
+        <f>RESUMEN!D36</f>
+        <v>111256.4</v>
+      </c>
+      <c r="H22" s="236" t="s">
+        <v>341</v>
+      </c>
+      <c r="I22" s="236"/>
+      <c r="J22" s="237"/>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="1" t="str">
+        <f>RESUMEN!A37</f>
+        <v>Plus cochera</v>
+      </c>
+      <c r="G23" s="44">
+        <f>RESUMEN!D37</f>
+        <v>20777</v>
+      </c>
+      <c r="H23" s="236" t="s">
+        <v>340</v>
+      </c>
+      <c r="I23" s="236"/>
+      <c r="J23" s="237"/>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="1" t="str">
+        <f>RESUMEN!A38</f>
+        <v>Adicional remuneracion</v>
+      </c>
+      <c r="G24" s="44">
+        <f>RESUMEN!D38</f>
+        <v>50000</v>
+      </c>
+      <c r="H24" s="236"/>
+      <c r="I24" s="236"/>
+      <c r="J24" s="237"/>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="199" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="200">
+        <f>SUM(G18:G24)</f>
+        <v>743330.4</v>
+      </c>
+      <c r="J25" s="198"/>
+    </row>
+    <row r="26" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C26" s="201"/>
+      <c r="D26" s="202"/>
+      <c r="E26" s="202"/>
+      <c r="F26" s="202"/>
+      <c r="G26" s="202"/>
+      <c r="H26" s="202"/>
+      <c r="I26" s="202"/>
+      <c r="J26" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="H23:J24"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H6:J7"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="H10:J11"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J20"/>
+    <mergeCell ref="H22:J22"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A8B3D07-243A-48F3-942B-AB44D486DEC8}">
   <dimension ref="C4:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C4" s="226" t="s">
+    <row r="4" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C4" s="238" t="s">
         <v>293</v>
       </c>
-      <c r="D4" s="226"/>
-    </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D4" s="238"/>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C5" s="175">
         <v>52141.08</v>
       </c>
@@ -11762,7 +12122,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C6" s="175">
         <v>67140.100000000006</v>
       </c>
@@ -11770,7 +12130,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C7" s="175">
         <v>52121.11</v>
       </c>
@@ -11778,7 +12138,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C8" s="175">
         <v>67885.119999999995</v>
       </c>
@@ -11786,7 +12146,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C9" s="175">
         <v>67140.160000000003</v>
       </c>
@@ -11794,7 +12154,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C10" s="175">
         <v>62141.17</v>
       </c>
@@ -11802,7 +12162,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C11" s="175">
         <v>67855.179999999993</v>
       </c>
@@ -11810,7 +12170,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C12" s="175">
         <v>62141.23</v>
       </c>
@@ -11818,7 +12178,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C13" s="175">
         <v>67855.240000000005</v>
       </c>
@@ -11826,7 +12186,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C14" s="175">
         <f>SUM(C5:C13)</f>
         <v>566420.39</v>
